--- a/data_clean/data_merged.xlsx
+++ b/data_clean/data_merged.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Documents\All Work Files\1. PE New Report\data_clean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A152BA-22EA-484A-A22F-9661A003C24E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1589DE59-18C2-40E3-9430-03B80D580DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3548,7 +3548,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -3587,9 +3587,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -3601,15 +3599,61 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3620,6 +3664,40 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F38F7656-86CA-4821-ADA1-5488F5CEC9A1}" name="Table1" displayName="Table1" ref="A1:Y314" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="2" tableBorderDxfId="3">
+  <autoFilter ref="A1:Y314" xr:uid="{F38F7656-86CA-4821-ADA1-5488F5CEC9A1}"/>
+  <tableColumns count="25">
+    <tableColumn id="1" xr3:uid="{039698E2-019D-4AFA-8ACB-10939541A822}" name="Email"/>
+    <tableColumn id="2" xr3:uid="{F0B53F50-E27A-4C90-AA9D-A84B1E0DB011}" name="Nama"/>
+    <tableColumn id="3" xr3:uid="{A8718DD6-247B-4B12-B9ED-02413F488A3F}" name="No WhatsApp"/>
+    <tableColumn id="4" xr3:uid="{002BD4EC-270A-41BE-89D6-EEC30CD8EBBE}" name="Kota - Provinsi"/>
+    <tableColumn id="5" xr3:uid="{9AF223A0-30B9-412E-BD34-0749345E1DC5}" name="Tempat Kegiatan"/>
+    <tableColumn id="6" xr3:uid="{B965C319-E859-4E80-ADCE-D9D868EE3DF4}" name="Tanggal" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{0764D467-1E41-4062-8E3F-57ABBC25DEFF}" name="Sesi"/>
+    <tableColumn id="8" xr3:uid="{48B11DBE-00E1-4C18-9924-E853A00EE4EE}" name="Jumlah Sesi"/>
+    <tableColumn id="9" xr3:uid="{2036A2E3-9C96-4DF7-B233-DE478FEFB31C}" name="Tahun"/>
+    <tableColumn id="10" xr3:uid="{4011E0EC-0619-4904-BD0B-1F81E701860D}" name="Bulan"/>
+    <tableColumn id="11" xr3:uid="{CF821166-36F2-4E60-935C-7243AF8FFB7A}" name="Kategori"/>
+    <tableColumn id="12" xr3:uid="{3E8AAF3D-314E-4163-80BE-4B8128C65FBC}" name="Nama Event"/>
+    <tableColumn id="13" xr3:uid="{421CFBC9-4A8C-457C-8A2E-48541C4D2F52}" name="Lokasi Event"/>
+    <tableColumn id="14" xr3:uid="{7D76B757-FD8E-492E-8808-D6DD7A2F4960}" name="Gender"/>
+    <tableColumn id="15" xr3:uid="{82C967A4-9796-44F3-9C18-48AB06C138CC}" name="Kota"/>
+    <tableColumn id="16" xr3:uid="{7B5DD4E8-61EB-443E-9AA5-CE3C5C9DD53D}" name="Provinsi"/>
+    <tableColumn id="17" xr3:uid="{4771CA65-6E51-4436-802D-284D20111AE7}" name="Usia"/>
+    <tableColumn id="18" xr3:uid="{2B7692F7-6692-4662-B210-8342ACB84741}" name="Kelompok Usia"/>
+    <tableColumn id="19" xr3:uid="{3EBFD3FE-8AA6-4F32-B6BC-D5CA2B1141FB}" name="Profesi (Asli)"/>
+    <tableColumn id="20" xr3:uid="{1D3B455E-FDC7-45A5-9B0B-89232ABBA013}" name="Kategori Profesi"/>
+    <tableColumn id="21" xr3:uid="{90BA8C37-E4C3-4FD0-813B-7AA8C7023455}" name="Harapan (Asli)"/>
+    <tableColumn id="22" xr3:uid="{02FA6104-8D44-4757-8BB5-203B4AED2B4D}" name="Topik Harapan"/>
+    <tableColumn id="23" xr3:uid="{41A5D24A-2F9C-43B9-9DCE-26AA34BBD6B4}" name="Keluhan (Asli)"/>
+    <tableColumn id="24" xr3:uid="{1D70B43B-886D-4226-B4BB-0D2D55DC4290}" name="Topik Keluhan"/>
+    <tableColumn id="25" xr3:uid="{6E684841-431B-4E90-BFE4-93684C9B6CFF}" name="Wilayah"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3909,81 +3987,101 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y314"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.90625" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" customWidth="1"/>
+    <col min="8" max="8" width="12.36328125" customWidth="1"/>
+    <col min="11" max="11" width="9.81640625" customWidth="1"/>
+    <col min="12" max="12" width="12.90625" customWidth="1"/>
+    <col min="13" max="13" width="13.1796875" customWidth="1"/>
+    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="16" max="16" width="9.453125" customWidth="1"/>
+    <col min="18" max="18" width="15.26953125" customWidth="1"/>
+    <col min="19" max="19" width="13.26953125" customWidth="1"/>
+    <col min="20" max="20" width="16.08984375" customWidth="1"/>
+    <col min="21" max="21" width="14.6328125" customWidth="1"/>
+    <col min="22" max="22" width="15.08984375" customWidth="1"/>
+    <col min="23" max="23" width="14.26953125" customWidth="1"/>
+    <col min="24" max="24" width="14.7265625" customWidth="1"/>
+    <col min="25" max="25" width="9.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -4003,7 +4101,7 @@
       <c r="E2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>45515</v>
       </c>
       <c r="G2" t="s">
@@ -4056,7 +4154,7 @@
       <c r="E3" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>45515</v>
       </c>
       <c r="G3" t="s">
@@ -4109,7 +4207,7 @@
       <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>45515</v>
       </c>
       <c r="G4" t="s">
@@ -4162,7 +4260,7 @@
       <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>45515</v>
       </c>
       <c r="G5" t="s">
@@ -4215,7 +4313,7 @@
       <c r="E6" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>45515</v>
       </c>
       <c r="G6" t="s">
@@ -4268,7 +4366,7 @@
       <c r="E7" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>45515</v>
       </c>
       <c r="G7" t="s">
@@ -4321,7 +4419,7 @@
       <c r="E8" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>45515</v>
       </c>
       <c r="G8" t="s">
@@ -4374,7 +4472,7 @@
       <c r="E9" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>45515</v>
       </c>
       <c r="G9" t="s">
@@ -4427,7 +4525,7 @@
       <c r="E10" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>45515</v>
       </c>
       <c r="G10" t="s">
@@ -4480,7 +4578,7 @@
       <c r="E11" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>45515</v>
       </c>
       <c r="G11" t="s">
@@ -4533,7 +4631,7 @@
       <c r="E12" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>45515</v>
       </c>
       <c r="G12" t="s">
@@ -4586,7 +4684,7 @@
       <c r="E13" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>45515</v>
       </c>
       <c r="G13" t="s">
@@ -4639,7 +4737,7 @@
       <c r="E14" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <v>45515</v>
       </c>
       <c r="G14" t="s">
@@ -4692,7 +4790,7 @@
       <c r="E15" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <v>45515</v>
       </c>
       <c r="G15" t="s">
@@ -4745,7 +4843,7 @@
       <c r="E16" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <v>45515</v>
       </c>
       <c r="G16" t="s">
@@ -4798,7 +4896,7 @@
       <c r="E17" t="s">
         <v>29</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>45515</v>
       </c>
       <c r="G17" t="s">
@@ -4851,7 +4949,7 @@
       <c r="E18" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="1">
         <v>45515</v>
       </c>
       <c r="G18" t="s">
@@ -4904,7 +5002,7 @@
       <c r="E19" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="1">
         <v>45515</v>
       </c>
       <c r="G19" t="s">
@@ -4957,7 +5055,7 @@
       <c r="E20" t="s">
         <v>98</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="1">
         <v>45564</v>
       </c>
       <c r="G20" t="s">
@@ -5010,7 +5108,7 @@
       <c r="E21" t="s">
         <v>98</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="1">
         <v>45564</v>
       </c>
       <c r="G21" t="s">
@@ -5075,7 +5173,7 @@
       <c r="E22" t="s">
         <v>98</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="1">
         <v>45564</v>
       </c>
       <c r="G22" t="s">
@@ -5128,7 +5226,7 @@
       <c r="E23" t="s">
         <v>98</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="1">
         <v>45564</v>
       </c>
       <c r="G23" t="s">
@@ -5181,7 +5279,7 @@
       <c r="E24" t="s">
         <v>98</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="1">
         <v>45564</v>
       </c>
       <c r="G24" t="s">
@@ -5234,7 +5332,7 @@
       <c r="E25" t="s">
         <v>98</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="1">
         <v>45564</v>
       </c>
       <c r="G25" t="s">
@@ -5287,7 +5385,7 @@
       <c r="E26" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="1">
         <v>45564</v>
       </c>
       <c r="G26" t="s">
@@ -5340,7 +5438,7 @@
       <c r="E27" t="s">
         <v>98</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="1">
         <v>45564</v>
       </c>
       <c r="G27" t="s">
@@ -5393,7 +5491,7 @@
       <c r="E28" t="s">
         <v>98</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="1">
         <v>45564</v>
       </c>
       <c r="G28" t="s">
@@ -5446,7 +5544,7 @@
       <c r="E29" t="s">
         <v>98</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="1">
         <v>45564</v>
       </c>
       <c r="G29" t="s">
@@ -5499,7 +5597,7 @@
       <c r="E30" t="s">
         <v>98</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="1">
         <v>45564</v>
       </c>
       <c r="G30" t="s">
@@ -5552,7 +5650,7 @@
       <c r="E31" t="s">
         <v>98</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="1">
         <v>45564</v>
       </c>
       <c r="G31" t="s">
@@ -5605,7 +5703,7 @@
       <c r="E32" t="s">
         <v>98</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="1">
         <v>45564</v>
       </c>
       <c r="G32" t="s">
@@ -5658,7 +5756,7 @@
       <c r="E33" t="s">
         <v>98</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="1">
         <v>45564</v>
       </c>
       <c r="G33" t="s">
@@ -5711,7 +5809,7 @@
       <c r="E34" t="s">
         <v>98</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="1">
         <v>45564</v>
       </c>
       <c r="G34" t="s">
@@ -5764,7 +5862,7 @@
       <c r="E35" t="s">
         <v>98</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="1">
         <v>45564</v>
       </c>
       <c r="G35" t="s">
@@ -5817,7 +5915,7 @@
       <c r="E36" t="s">
         <v>98</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="1">
         <v>45564</v>
       </c>
       <c r="G36" t="s">
@@ -5870,7 +5968,7 @@
       <c r="E37" t="s">
         <v>98</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="1">
         <v>45564</v>
       </c>
       <c r="G37" t="s">
@@ -5923,7 +6021,7 @@
       <c r="E38" t="s">
         <v>98</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="1">
         <v>45564</v>
       </c>
       <c r="G38" t="s">
@@ -5976,7 +6074,7 @@
       <c r="E39" t="s">
         <v>98</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="1">
         <v>45564</v>
       </c>
       <c r="G39" t="s">
@@ -6029,7 +6127,7 @@
       <c r="E40" t="s">
         <v>98</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="1">
         <v>45564</v>
       </c>
       <c r="G40" t="s">
@@ -6082,7 +6180,7 @@
       <c r="E41" t="s">
         <v>98</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="1">
         <v>45564</v>
       </c>
       <c r="G41" t="s">
@@ -6135,7 +6233,7 @@
       <c r="E42" t="s">
         <v>98</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="1">
         <v>45564</v>
       </c>
       <c r="G42" t="s">
@@ -6188,7 +6286,7 @@
       <c r="E43" t="s">
         <v>98</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="1">
         <v>45564</v>
       </c>
       <c r="G43" t="s">
@@ -6241,7 +6339,7 @@
       <c r="E44" t="s">
         <v>98</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="1">
         <v>45564</v>
       </c>
       <c r="G44" t="s">
@@ -6294,7 +6392,7 @@
       <c r="E45" t="s">
         <v>98</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="1">
         <v>45564</v>
       </c>
       <c r="G45" t="s">
@@ -6347,7 +6445,7 @@
       <c r="E46" t="s">
         <v>98</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="1">
         <v>45564</v>
       </c>
       <c r="G46" t="s">
@@ -6400,7 +6498,7 @@
       <c r="E47" t="s">
         <v>200</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="1">
         <v>45592</v>
       </c>
       <c r="G47" t="s">
@@ -6453,7 +6551,7 @@
       <c r="E48" t="s">
         <v>200</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="1">
         <v>45592</v>
       </c>
       <c r="G48" t="s">
@@ -6506,7 +6604,7 @@
       <c r="E49" t="s">
         <v>200</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="1">
         <v>45592</v>
       </c>
       <c r="G49" t="s">
@@ -6559,7 +6657,7 @@
       <c r="E50" t="s">
         <v>200</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="1">
         <v>45592</v>
       </c>
       <c r="G50" t="s">
@@ -6612,7 +6710,7 @@
       <c r="E51" t="s">
         <v>200</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="1">
         <v>45592</v>
       </c>
       <c r="G51" t="s">
@@ -6665,7 +6763,7 @@
       <c r="E52" t="s">
         <v>200</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="1">
         <v>45592</v>
       </c>
       <c r="G52" t="s">
@@ -6718,7 +6816,7 @@
       <c r="E53" t="s">
         <v>200</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="1">
         <v>45592</v>
       </c>
       <c r="G53" t="s">
@@ -6771,7 +6869,7 @@
       <c r="E54" t="s">
         <v>200</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="1">
         <v>45592</v>
       </c>
       <c r="G54" t="s">
@@ -6824,7 +6922,7 @@
       <c r="E55" t="s">
         <v>200</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="1">
         <v>45592</v>
       </c>
       <c r="G55" t="s">
@@ -6877,7 +6975,7 @@
       <c r="E56" t="s">
         <v>200</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="1">
         <v>45592</v>
       </c>
       <c r="G56" t="s">
@@ -6930,7 +7028,7 @@
       <c r="E57" t="s">
         <v>200</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="1">
         <v>45592</v>
       </c>
       <c r="G57" t="s">
@@ -6983,7 +7081,7 @@
       <c r="E58" t="s">
         <v>200</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="1">
         <v>45592</v>
       </c>
       <c r="G58" t="s">
@@ -7036,7 +7134,7 @@
       <c r="E59" t="s">
         <v>200</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="1">
         <v>45592</v>
       </c>
       <c r="G59" t="s">
@@ -7089,7 +7187,7 @@
       <c r="E60" t="s">
         <v>200</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="1">
         <v>45592</v>
       </c>
       <c r="G60" t="s">
@@ -7142,7 +7240,7 @@
       <c r="E61" t="s">
         <v>200</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="1">
         <v>45592</v>
       </c>
       <c r="G61" t="s">
@@ -7195,7 +7293,7 @@
       <c r="E62" t="s">
         <v>200</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="1">
         <v>45592</v>
       </c>
       <c r="G62" t="s">
@@ -7248,7 +7346,7 @@
       <c r="E63" t="s">
         <v>29</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="1">
         <v>45626</v>
       </c>
       <c r="G63" t="s">
@@ -7301,7 +7399,7 @@
       <c r="E64" t="s">
         <v>29</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="1">
         <v>45626</v>
       </c>
       <c r="G64" t="s">
@@ -7354,7 +7452,7 @@
       <c r="E65" t="s">
         <v>29</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="1">
         <v>45626</v>
       </c>
       <c r="G65" t="s">
@@ -7407,7 +7505,7 @@
       <c r="E66" t="s">
         <v>29</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="1">
         <v>45626</v>
       </c>
       <c r="G66" t="s">
@@ -7460,7 +7558,7 @@
       <c r="E67" t="s">
         <v>29</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="1">
         <v>45626</v>
       </c>
       <c r="G67" t="s">
@@ -7513,7 +7611,7 @@
       <c r="E68" t="s">
         <v>29</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="1">
         <v>45626</v>
       </c>
       <c r="G68" t="s">
@@ -7566,7 +7664,7 @@
       <c r="E69" t="s">
         <v>29</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="1">
         <v>45626</v>
       </c>
       <c r="G69" t="s">
@@ -7619,7 +7717,7 @@
       <c r="E70" t="s">
         <v>29</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="1">
         <v>45626</v>
       </c>
       <c r="G70" t="s">
@@ -7672,7 +7770,7 @@
       <c r="E71" t="s">
         <v>29</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="1">
         <v>45626</v>
       </c>
       <c r="G71" t="s">
@@ -7725,7 +7823,7 @@
       <c r="E72" t="s">
         <v>29</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="1">
         <v>45626</v>
       </c>
       <c r="G72" t="s">
@@ -7778,7 +7876,7 @@
       <c r="E73" t="s">
         <v>29</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="1">
         <v>45626</v>
       </c>
       <c r="G73" t="s">
@@ -7831,7 +7929,7 @@
       <c r="E74" t="s">
         <v>29</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="1">
         <v>45626</v>
       </c>
       <c r="G74" t="s">
@@ -7884,7 +7982,7 @@
       <c r="E75" t="s">
         <v>29</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="1">
         <v>45626</v>
       </c>
       <c r="G75" t="s">
@@ -7937,7 +8035,7 @@
       <c r="E76" t="s">
         <v>29</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="1">
         <v>45626</v>
       </c>
       <c r="G76" t="s">
@@ -7990,7 +8088,7 @@
       <c r="E77" t="s">
         <v>29</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="1">
         <v>45626</v>
       </c>
       <c r="G77" t="s">
@@ -8043,7 +8141,7 @@
       <c r="E78" t="s">
         <v>29</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="1">
         <v>45626</v>
       </c>
       <c r="G78" t="s">
@@ -8096,7 +8194,7 @@
       <c r="E79" t="s">
         <v>29</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="1">
         <v>45626</v>
       </c>
       <c r="G79" t="s">
@@ -8149,7 +8247,7 @@
       <c r="E80" t="s">
         <v>29</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="1">
         <v>45626</v>
       </c>
       <c r="G80" t="s">
@@ -8202,7 +8300,7 @@
       <c r="E81" t="s">
         <v>29</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="1">
         <v>45626</v>
       </c>
       <c r="G81" t="s">
@@ -8255,7 +8353,7 @@
       <c r="E82" t="s">
         <v>29</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="1">
         <v>45626</v>
       </c>
       <c r="G82" t="s">
@@ -8308,7 +8406,7 @@
       <c r="E83" t="s">
         <v>29</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="1">
         <v>45626</v>
       </c>
       <c r="G83" t="s">
@@ -8361,7 +8459,7 @@
       <c r="E84" t="s">
         <v>29</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="1">
         <v>45626</v>
       </c>
       <c r="G84" t="s">
@@ -8414,7 +8512,7 @@
       <c r="E85" t="s">
         <v>29</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="1">
         <v>45626</v>
       </c>
       <c r="G85" t="s">
@@ -8467,7 +8565,7 @@
       <c r="E86" t="s">
         <v>29</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="1">
         <v>45807</v>
       </c>
       <c r="G86" t="s">
@@ -8532,7 +8630,7 @@
       <c r="E87" t="s">
         <v>29</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="1">
         <v>45807</v>
       </c>
       <c r="G87" t="s">
@@ -8597,7 +8695,7 @@
       <c r="E88" t="s">
         <v>29</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="1">
         <v>45807</v>
       </c>
       <c r="G88" t="s">
@@ -8671,7 +8769,7 @@
       <c r="E89" t="s">
         <v>29</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="1">
         <v>45807</v>
       </c>
       <c r="G89" t="s">
@@ -8736,7 +8834,7 @@
       <c r="E90" t="s">
         <v>29</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="1">
         <v>45807</v>
       </c>
       <c r="G90" t="s">
@@ -8810,7 +8908,7 @@
       <c r="E91" t="s">
         <v>29</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="1">
         <v>45808</v>
       </c>
       <c r="G91" t="s">
@@ -8884,7 +8982,7 @@
       <c r="E92" t="s">
         <v>29</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="1">
         <v>45808</v>
       </c>
       <c r="G92" t="s">
@@ -8958,7 +9056,7 @@
       <c r="E93" t="s">
         <v>29</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="1">
         <v>45808</v>
       </c>
       <c r="G93" t="s">
@@ -9023,7 +9121,7 @@
       <c r="E94" t="s">
         <v>29</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="1">
         <v>45808</v>
       </c>
       <c r="G94" t="s">
@@ -9097,7 +9195,7 @@
       <c r="E95" t="s">
         <v>29</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="1">
         <v>45808</v>
       </c>
       <c r="G95" t="s">
@@ -9171,7 +9269,7 @@
       <c r="E96" t="s">
         <v>29</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="1">
         <v>45808</v>
       </c>
       <c r="G96" t="s">
@@ -9245,7 +9343,7 @@
       <c r="E97" t="s">
         <v>29</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="1">
         <v>45808</v>
       </c>
       <c r="G97" t="s">
@@ -9310,7 +9408,7 @@
       <c r="E98" t="s">
         <v>29</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="1">
         <v>45808</v>
       </c>
       <c r="G98" t="s">
@@ -9384,7 +9482,7 @@
       <c r="E99" t="s">
         <v>29</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="1">
         <v>45808</v>
       </c>
       <c r="G99" t="s">
@@ -9458,7 +9556,7 @@
       <c r="E100" t="s">
         <v>29</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="1">
         <v>45808</v>
       </c>
       <c r="G100" t="s">
@@ -9523,7 +9621,7 @@
       <c r="E101" t="s">
         <v>29</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F101" s="1">
         <v>45808</v>
       </c>
       <c r="G101" t="s">
@@ -9597,7 +9695,7 @@
       <c r="E102" t="s">
         <v>403</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="1">
         <v>45844</v>
       </c>
       <c r="G102" t="s">
@@ -9650,7 +9748,7 @@
       <c r="E103" t="s">
         <v>403</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="1">
         <v>45844</v>
       </c>
       <c r="G103" t="s">
@@ -9703,7 +9801,7 @@
       <c r="E104" t="s">
         <v>403</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="1">
         <v>45844</v>
       </c>
       <c r="G104" t="s">
@@ -9753,7 +9851,7 @@
       <c r="E105" t="s">
         <v>403</v>
       </c>
-      <c r="F105" s="2">
+      <c r="F105" s="1">
         <v>45844</v>
       </c>
       <c r="G105" t="s">
@@ -9803,7 +9901,7 @@
       <c r="E106" t="s">
         <v>403</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="1">
         <v>45844</v>
       </c>
       <c r="G106" t="s">
@@ -9853,7 +9951,7 @@
       <c r="E107" t="s">
         <v>403</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="1">
         <v>45844</v>
       </c>
       <c r="G107" t="s">
@@ -9903,7 +10001,7 @@
       <c r="E108" t="s">
         <v>403</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="1">
         <v>45844</v>
       </c>
       <c r="G108" t="s">
@@ -9953,7 +10051,7 @@
       <c r="E109" t="s">
         <v>403</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="1">
         <v>45844</v>
       </c>
       <c r="G109" t="s">
@@ -10003,7 +10101,7 @@
       <c r="E110" t="s">
         <v>403</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="1">
         <v>45844</v>
       </c>
       <c r="G110" t="s">
@@ -10056,7 +10154,7 @@
       <c r="E111" t="s">
         <v>200</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="1">
         <v>45858</v>
       </c>
       <c r="G111" t="s">
@@ -10130,7 +10228,7 @@
       <c r="E112" t="s">
         <v>200</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="1">
         <v>45858</v>
       </c>
       <c r="G112" t="s">
@@ -10204,7 +10302,7 @@
       <c r="E113" t="s">
         <v>200</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="1">
         <v>45858</v>
       </c>
       <c r="G113" t="s">
@@ -10278,7 +10376,7 @@
       <c r="E114" t="s">
         <v>200</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="1">
         <v>45858</v>
       </c>
       <c r="G114" t="s">
@@ -10352,7 +10450,7 @@
       <c r="E115" t="s">
         <v>200</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="1">
         <v>45858</v>
       </c>
       <c r="G115" t="s">
@@ -10426,7 +10524,7 @@
       <c r="E116" t="s">
         <v>200</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="1">
         <v>45858</v>
       </c>
       <c r="G116" t="s">
@@ -10491,7 +10589,7 @@
       <c r="E117" t="s">
         <v>200</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="1">
         <v>45858</v>
       </c>
       <c r="G117" t="s">
@@ -10556,7 +10654,7 @@
       <c r="E118" t="s">
         <v>200</v>
       </c>
-      <c r="F118" s="2">
+      <c r="F118" s="1">
         <v>45858</v>
       </c>
       <c r="G118" t="s">
@@ -10630,7 +10728,7 @@
       <c r="E119" t="s">
         <v>200</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="1">
         <v>45858</v>
       </c>
       <c r="G119" t="s">
@@ -10704,7 +10802,7 @@
       <c r="E120" t="s">
         <v>200</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="1">
         <v>45858</v>
       </c>
       <c r="G120" t="s">
@@ -10778,7 +10876,7 @@
       <c r="E121" t="s">
         <v>200</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="1">
         <v>45858</v>
       </c>
       <c r="G121" t="s">
@@ -10849,7 +10947,7 @@
       <c r="E122" t="s">
         <v>403</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="1">
         <v>45879</v>
       </c>
       <c r="G122" t="s">
@@ -10899,7 +10997,7 @@
       <c r="E123" t="s">
         <v>403</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="1">
         <v>45879</v>
       </c>
       <c r="G123" t="s">
@@ -10949,7 +11047,7 @@
       <c r="E124" t="s">
         <v>403</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="1">
         <v>45879</v>
       </c>
       <c r="G124" t="s">
@@ -10999,7 +11097,7 @@
       <c r="E125" t="s">
         <v>403</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="1">
         <v>45879</v>
       </c>
       <c r="G125" t="s">
@@ -11049,7 +11147,7 @@
       <c r="E126" t="s">
         <v>403</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="1">
         <v>45879</v>
       </c>
       <c r="G126" t="s">
@@ -11099,7 +11197,7 @@
       <c r="E127" t="s">
         <v>403</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="1">
         <v>45879</v>
       </c>
       <c r="G127" t="s">
@@ -11149,7 +11247,7 @@
       <c r="E128" t="s">
         <v>403</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="1">
         <v>45879</v>
       </c>
       <c r="G128" t="s">
@@ -11199,7 +11297,7 @@
       <c r="E129" t="s">
         <v>403</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="1">
         <v>45879</v>
       </c>
       <c r="G129" t="s">
@@ -11249,7 +11347,7 @@
       <c r="E130" t="s">
         <v>403</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="1">
         <v>45879</v>
       </c>
       <c r="G130" t="s">
@@ -11299,7 +11397,7 @@
       <c r="E131" t="s">
         <v>403</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="1">
         <v>45914</v>
       </c>
       <c r="G131" t="s">
@@ -11349,7 +11447,7 @@
       <c r="E132" t="s">
         <v>403</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="1">
         <v>45914</v>
       </c>
       <c r="G132" t="s">
@@ -11399,7 +11497,7 @@
       <c r="E133" t="s">
         <v>403</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="1">
         <v>45914</v>
       </c>
       <c r="G133" t="s">
@@ -11449,7 +11547,7 @@
       <c r="E134" t="s">
         <v>403</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="1">
         <v>45914</v>
       </c>
       <c r="G134" t="s">
@@ -11499,7 +11597,7 @@
       <c r="E135" t="s">
         <v>403</v>
       </c>
-      <c r="F135" s="2">
+      <c r="F135" s="1">
         <v>45914</v>
       </c>
       <c r="G135" t="s">
@@ -11549,7 +11647,7 @@
       <c r="E136" t="s">
         <v>403</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="1">
         <v>45914</v>
       </c>
       <c r="G136" t="s">
@@ -11599,7 +11697,7 @@
       <c r="E137" t="s">
         <v>403</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="1">
         <v>45914</v>
       </c>
       <c r="G137" t="s">
@@ -11649,7 +11747,7 @@
       <c r="E138" t="s">
         <v>403</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="1">
         <v>45914</v>
       </c>
       <c r="G138" t="s">
@@ -11699,7 +11797,7 @@
       <c r="E139" t="s">
         <v>403</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="1">
         <v>45914</v>
       </c>
       <c r="G139" t="s">
@@ -11749,7 +11847,7 @@
       <c r="E140" t="s">
         <v>403</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="1">
         <v>45914</v>
       </c>
       <c r="G140" t="s">
@@ -11799,7 +11897,7 @@
       <c r="E141" t="s">
         <v>403</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="1">
         <v>45914</v>
       </c>
       <c r="G141" t="s">
@@ -11849,7 +11947,7 @@
       <c r="E142" t="s">
         <v>403</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="1">
         <v>45914</v>
       </c>
       <c r="G142" t="s">
@@ -11899,7 +11997,7 @@
       <c r="E143" t="s">
         <v>403</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="1">
         <v>45914</v>
       </c>
       <c r="G143" t="s">
@@ -11949,7 +12047,7 @@
       <c r="E144" t="s">
         <v>403</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="1">
         <v>45914</v>
       </c>
       <c r="G144" t="s">
@@ -11999,7 +12097,7 @@
       <c r="E145" t="s">
         <v>403</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="1">
         <v>45914</v>
       </c>
       <c r="G145" t="s">
@@ -12049,7 +12147,7 @@
       <c r="E146" t="s">
         <v>403</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="1">
         <v>45914</v>
       </c>
       <c r="G146" t="s">
@@ -12099,7 +12197,7 @@
       <c r="E147" t="s">
         <v>403</v>
       </c>
-      <c r="F147" s="2">
+      <c r="F147" s="1">
         <v>45914</v>
       </c>
       <c r="G147" t="s">
@@ -12149,7 +12247,7 @@
       <c r="E148" t="s">
         <v>403</v>
       </c>
-      <c r="F148" s="2">
+      <c r="F148" s="1">
         <v>45914</v>
       </c>
       <c r="G148" t="s">
@@ -12202,7 +12300,7 @@
       <c r="E149" t="s">
         <v>29</v>
       </c>
-      <c r="F149" s="2">
+      <c r="F149" s="1">
         <v>45920</v>
       </c>
       <c r="G149" t="s">
@@ -12255,7 +12353,7 @@
       <c r="E150" t="s">
         <v>29</v>
       </c>
-      <c r="F150" s="2">
+      <c r="F150" s="1">
         <v>45920</v>
       </c>
       <c r="G150" t="s">
@@ -12308,7 +12406,7 @@
       <c r="E151" t="s">
         <v>29</v>
       </c>
-      <c r="F151" s="2">
+      <c r="F151" s="1">
         <v>45920</v>
       </c>
       <c r="G151" t="s">
@@ -12373,7 +12471,7 @@
       <c r="E152" t="s">
         <v>29</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="1">
         <v>45920</v>
       </c>
       <c r="G152" t="s">
@@ -12438,7 +12536,7 @@
       <c r="E153" t="s">
         <v>29</v>
       </c>
-      <c r="F153" s="2">
+      <c r="F153" s="1">
         <v>45920</v>
       </c>
       <c r="G153" t="s">
@@ -12512,7 +12610,7 @@
       <c r="E154" t="s">
         <v>29</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="1">
         <v>45920</v>
       </c>
       <c r="G154" t="s">
@@ -12574,7 +12672,7 @@
       <c r="E155" t="s">
         <v>29</v>
       </c>
-      <c r="F155" s="2">
+      <c r="F155" s="1">
         <v>45920</v>
       </c>
       <c r="G155" t="s">
@@ -12636,7 +12734,7 @@
       <c r="E156" t="s">
         <v>29</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="1">
         <v>45920</v>
       </c>
       <c r="G156" t="s">
@@ -12698,7 +12796,7 @@
       <c r="E157" t="s">
         <v>29</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="1">
         <v>45920</v>
       </c>
       <c r="G157" t="s">
@@ -12769,7 +12867,7 @@
       <c r="E158" t="s">
         <v>29</v>
       </c>
-      <c r="F158" s="2">
+      <c r="F158" s="1">
         <v>45920</v>
       </c>
       <c r="G158" t="s">
@@ -12822,7 +12920,7 @@
       <c r="E159" t="s">
         <v>403</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="1">
         <v>45935</v>
       </c>
       <c r="G159" t="s">
@@ -12887,7 +12985,7 @@
       <c r="E160" t="s">
         <v>403</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="1">
         <v>45935</v>
       </c>
       <c r="G160" t="s">
@@ -12961,7 +13059,7 @@
       <c r="E161" t="s">
         <v>403</v>
       </c>
-      <c r="F161" s="2">
+      <c r="F161" s="1">
         <v>45935</v>
       </c>
       <c r="G161" t="s">
@@ -13035,7 +13133,7 @@
       <c r="E162" t="s">
         <v>403</v>
       </c>
-      <c r="F162" s="2">
+      <c r="F162" s="1">
         <v>45935</v>
       </c>
       <c r="G162" t="s">
@@ -13109,7 +13207,7 @@
       <c r="E163" t="s">
         <v>403</v>
       </c>
-      <c r="F163" s="2">
+      <c r="F163" s="1">
         <v>45935</v>
       </c>
       <c r="G163" t="s">
@@ -13183,7 +13281,7 @@
       <c r="E164" t="s">
         <v>403</v>
       </c>
-      <c r="F164" s="2">
+      <c r="F164" s="1">
         <v>45935</v>
       </c>
       <c r="G164" t="s">
@@ -13257,7 +13355,7 @@
       <c r="E165" t="s">
         <v>403</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="1">
         <v>45935</v>
       </c>
       <c r="G165" t="s">
@@ -13331,7 +13429,7 @@
       <c r="E166" t="s">
         <v>403</v>
       </c>
-      <c r="F166" s="2">
+      <c r="F166" s="1">
         <v>45935</v>
       </c>
       <c r="G166" t="s">
@@ -13405,7 +13503,7 @@
       <c r="E167" t="s">
         <v>403</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="1">
         <v>45935</v>
       </c>
       <c r="G167" t="s">
@@ -13479,7 +13577,7 @@
       <c r="E168" t="s">
         <v>403</v>
       </c>
-      <c r="F168" s="2">
+      <c r="F168" s="1">
         <v>45935</v>
       </c>
       <c r="G168" t="s">
@@ -13553,7 +13651,7 @@
       <c r="E169" t="s">
         <v>29</v>
       </c>
-      <c r="F169" s="2">
+      <c r="F169" s="1">
         <v>45951</v>
       </c>
       <c r="G169" t="s">
@@ -13618,7 +13716,7 @@
       <c r="E170" t="s">
         <v>29</v>
       </c>
-      <c r="F170" s="2">
+      <c r="F170" s="1">
         <v>45951</v>
       </c>
       <c r="G170" t="s">
@@ -13683,7 +13781,7 @@
       <c r="E171" t="s">
         <v>29</v>
       </c>
-      <c r="F171" s="2">
+      <c r="F171" s="1">
         <v>45951</v>
       </c>
       <c r="G171" t="s">
@@ -13757,11 +13855,11 @@
       <c r="E172" t="s">
         <v>29</v>
       </c>
-      <c r="F172" s="2">
+      <c r="F172" s="1">
         <v>45951</v>
       </c>
       <c r="G172" t="s">
-        <v>418</v>
+        <v>625</v>
       </c>
       <c r="H172">
         <v>1</v>
@@ -13776,7 +13874,7 @@
         <v>346</v>
       </c>
       <c r="L172" t="s">
-        <v>418</v>
+        <v>625</v>
       </c>
       <c r="M172" t="s">
         <v>29</v>
@@ -13822,7 +13920,7 @@
       <c r="E173" t="s">
         <v>29</v>
       </c>
-      <c r="F173" s="2">
+      <c r="F173" s="1">
         <v>45951</v>
       </c>
       <c r="G173" t="s">
@@ -13896,7 +13994,7 @@
       <c r="E174" t="s">
         <v>29</v>
       </c>
-      <c r="F174" s="2">
+      <c r="F174" s="1">
         <v>45951</v>
       </c>
       <c r="G174" t="s">
@@ -13970,7 +14068,7 @@
       <c r="E175" t="s">
         <v>29</v>
       </c>
-      <c r="F175" s="2">
+      <c r="F175" s="1">
         <v>45951</v>
       </c>
       <c r="G175" t="s">
@@ -14047,7 +14145,7 @@
       <c r="E176" t="s">
         <v>29</v>
       </c>
-      <c r="F176" s="2">
+      <c r="F176" s="1">
         <v>45951</v>
       </c>
       <c r="G176" t="s">
@@ -14118,7 +14216,7 @@
       <c r="E177" t="s">
         <v>403</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F177" s="1">
         <v>45956</v>
       </c>
       <c r="G177" t="s">
@@ -14168,7 +14266,7 @@
       <c r="E178" t="s">
         <v>403</v>
       </c>
-      <c r="F178" s="2">
+      <c r="F178" s="1">
         <v>45956</v>
       </c>
       <c r="G178" t="s">
@@ -14218,7 +14316,7 @@
       <c r="E179" t="s">
         <v>403</v>
       </c>
-      <c r="F179" s="2">
+      <c r="F179" s="1">
         <v>45956</v>
       </c>
       <c r="G179" t="s">
@@ -14268,7 +14366,7 @@
       <c r="E180" t="s">
         <v>403</v>
       </c>
-      <c r="F180" s="2">
+      <c r="F180" s="1">
         <v>45956</v>
       </c>
       <c r="G180" t="s">
@@ -14318,7 +14416,7 @@
       <c r="E181" t="s">
         <v>403</v>
       </c>
-      <c r="F181" s="2">
+      <c r="F181" s="1">
         <v>45956</v>
       </c>
       <c r="G181" t="s">
@@ -14368,7 +14466,7 @@
       <c r="E182" t="s">
         <v>403</v>
       </c>
-      <c r="F182" s="2">
+      <c r="F182" s="1">
         <v>45956</v>
       </c>
       <c r="G182" t="s">
@@ -14418,7 +14516,7 @@
       <c r="E183" t="s">
         <v>403</v>
       </c>
-      <c r="F183" s="2">
+      <c r="F183" s="1">
         <v>45956</v>
       </c>
       <c r="G183" t="s">
@@ -14468,7 +14566,7 @@
       <c r="E184" t="s">
         <v>403</v>
       </c>
-      <c r="F184" s="2">
+      <c r="F184" s="1">
         <v>45956</v>
       </c>
       <c r="G184" t="s">
@@ -14518,7 +14616,7 @@
       <c r="E185" t="s">
         <v>403</v>
       </c>
-      <c r="F185" s="2">
+      <c r="F185" s="1">
         <v>45956</v>
       </c>
       <c r="G185" t="s">
@@ -14568,7 +14666,7 @@
       <c r="E186" t="s">
         <v>403</v>
       </c>
-      <c r="F186" s="2">
+      <c r="F186" s="1">
         <v>45956</v>
       </c>
       <c r="G186" t="s">
@@ -14618,7 +14716,7 @@
       <c r="E187" t="s">
         <v>403</v>
       </c>
-      <c r="F187" s="2">
+      <c r="F187" s="1">
         <v>45956</v>
       </c>
       <c r="G187" t="s">
@@ -14668,7 +14766,7 @@
       <c r="E188" t="s">
         <v>403</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="1">
         <v>45956</v>
       </c>
       <c r="G188" t="s">
@@ -14721,7 +14819,7 @@
       <c r="E189" t="s">
         <v>403</v>
       </c>
-      <c r="F189" s="2">
+      <c r="F189" s="1">
         <v>45956</v>
       </c>
       <c r="G189" t="s">
@@ -14786,7 +14884,7 @@
       <c r="E190" t="s">
         <v>403</v>
       </c>
-      <c r="F190" s="2">
+      <c r="F190" s="1">
         <v>45956</v>
       </c>
       <c r="G190" t="s">
@@ -14857,7 +14955,7 @@
       <c r="E191" t="s">
         <v>403</v>
       </c>
-      <c r="F191" s="2">
+      <c r="F191" s="1">
         <v>45956</v>
       </c>
       <c r="G191" t="s">
@@ -14907,7 +15005,7 @@
       <c r="E192" t="s">
         <v>403</v>
       </c>
-      <c r="F192" s="2">
+      <c r="F192" s="1">
         <v>45956</v>
       </c>
       <c r="G192" t="s">
@@ -14969,7 +15067,7 @@
       <c r="E193" t="s">
         <v>403</v>
       </c>
-      <c r="F193" s="2">
+      <c r="F193" s="1">
         <v>45956</v>
       </c>
       <c r="G193" t="s">
@@ -15022,7 +15120,7 @@
       <c r="E194" t="s">
         <v>403</v>
       </c>
-      <c r="F194" s="2">
+      <c r="F194" s="1">
         <v>45956</v>
       </c>
       <c r="G194" t="s">
@@ -15087,7 +15185,7 @@
       <c r="E195" t="s">
         <v>403</v>
       </c>
-      <c r="F195" s="2">
+      <c r="F195" s="1">
         <v>45956</v>
       </c>
       <c r="G195" t="s">
@@ -15158,7 +15256,7 @@
       <c r="E196" t="s">
         <v>403</v>
       </c>
-      <c r="F196" s="2">
+      <c r="F196" s="1">
         <v>45956</v>
       </c>
       <c r="G196" t="s">
@@ -15208,7 +15306,7 @@
       <c r="E197" t="s">
         <v>403</v>
       </c>
-      <c r="F197" s="2">
+      <c r="F197" s="1">
         <v>45956</v>
       </c>
       <c r="G197" t="s">
@@ -15258,7 +15356,7 @@
       <c r="E198" t="s">
         <v>403</v>
       </c>
-      <c r="F198" s="2">
+      <c r="F198" s="1">
         <v>45956</v>
       </c>
       <c r="G198" t="s">
@@ -15308,7 +15406,7 @@
       <c r="E199" t="s">
         <v>403</v>
       </c>
-      <c r="F199" s="2">
+      <c r="F199" s="1">
         <v>45956</v>
       </c>
       <c r="G199" t="s">
@@ -15361,7 +15459,7 @@
       <c r="E200" t="s">
         <v>29</v>
       </c>
-      <c r="F200" s="2">
+      <c r="F200" s="1">
         <v>45962</v>
       </c>
       <c r="G200" t="s">
@@ -15414,7 +15512,7 @@
       <c r="E201" t="s">
         <v>29</v>
       </c>
-      <c r="F201" s="2">
+      <c r="F201" s="1">
         <v>45962</v>
       </c>
       <c r="G201" t="s">
@@ -15467,7 +15565,7 @@
       <c r="E202" t="s">
         <v>29</v>
       </c>
-      <c r="F202" s="2">
+      <c r="F202" s="1">
         <v>45962</v>
       </c>
       <c r="G202" t="s">
@@ -15520,7 +15618,7 @@
       <c r="E203" t="s">
         <v>29</v>
       </c>
-      <c r="F203" s="2">
+      <c r="F203" s="1">
         <v>45962</v>
       </c>
       <c r="G203" t="s">
@@ -15585,7 +15683,7 @@
       <c r="E204" t="s">
         <v>29</v>
       </c>
-      <c r="F204" s="2">
+      <c r="F204" s="1">
         <v>45962</v>
       </c>
       <c r="G204" t="s">
@@ -15659,7 +15757,7 @@
       <c r="E205" t="s">
         <v>29</v>
       </c>
-      <c r="F205" s="2">
+      <c r="F205" s="1">
         <v>45962</v>
       </c>
       <c r="G205" t="s">
@@ -15733,7 +15831,7 @@
       <c r="E206" t="s">
         <v>29</v>
       </c>
-      <c r="F206" s="2">
+      <c r="F206" s="1">
         <v>45962</v>
       </c>
       <c r="G206" t="s">
@@ -15786,7 +15884,7 @@
       <c r="E207" t="s">
         <v>29</v>
       </c>
-      <c r="F207" s="2">
+      <c r="F207" s="1">
         <v>45963</v>
       </c>
       <c r="G207" t="s">
@@ -15860,7 +15958,7 @@
       <c r="E208" t="s">
         <v>29</v>
       </c>
-      <c r="F208" s="2">
+      <c r="F208" s="1">
         <v>45963</v>
       </c>
       <c r="G208" t="s">
@@ -15937,7 +16035,7 @@
       <c r="E209" t="s">
         <v>29</v>
       </c>
-      <c r="F209" s="2">
+      <c r="F209" s="1">
         <v>45963</v>
       </c>
       <c r="G209" t="s">
@@ -16014,7 +16112,7 @@
       <c r="E210" t="s">
         <v>29</v>
       </c>
-      <c r="F210" s="2">
+      <c r="F210" s="1">
         <v>45963</v>
       </c>
       <c r="G210" t="s">
@@ -16091,7 +16189,7 @@
       <c r="E211" t="s">
         <v>29</v>
       </c>
-      <c r="F211" s="2">
+      <c r="F211" s="1">
         <v>45963</v>
       </c>
       <c r="G211" t="s">
@@ -16168,7 +16266,7 @@
       <c r="E212" t="s">
         <v>29</v>
       </c>
-      <c r="F212" s="2">
+      <c r="F212" s="1">
         <v>45963</v>
       </c>
       <c r="G212" t="s">
@@ -16245,7 +16343,7 @@
       <c r="E213" t="s">
         <v>29</v>
       </c>
-      <c r="F213" s="2">
+      <c r="F213" s="1">
         <v>45963</v>
       </c>
       <c r="G213" t="s">
@@ -16322,7 +16420,7 @@
       <c r="E214" t="s">
         <v>29</v>
       </c>
-      <c r="F214" s="2">
+      <c r="F214" s="1">
         <v>45963</v>
       </c>
       <c r="G214" t="s">
@@ -16399,7 +16497,7 @@
       <c r="E215" t="s">
         <v>29</v>
       </c>
-      <c r="F215" s="2">
+      <c r="F215" s="1">
         <v>45963</v>
       </c>
       <c r="G215" t="s">
@@ -16476,7 +16574,7 @@
       <c r="E216" t="s">
         <v>29</v>
       </c>
-      <c r="F216" s="2">
+      <c r="F216" s="1">
         <v>45963</v>
       </c>
       <c r="G216" t="s">
@@ -16553,7 +16651,7 @@
       <c r="E217" t="s">
         <v>29</v>
       </c>
-      <c r="F217" s="2">
+      <c r="F217" s="1">
         <v>45963</v>
       </c>
       <c r="G217" t="s">
@@ -16627,7 +16725,7 @@
       <c r="E218" t="s">
         <v>29</v>
       </c>
-      <c r="F218" s="2">
+      <c r="F218" s="1">
         <v>45963</v>
       </c>
       <c r="G218" t="s">
@@ -16701,7 +16799,7 @@
       <c r="E219" t="s">
         <v>29</v>
       </c>
-      <c r="F219" s="2">
+      <c r="F219" s="1">
         <v>45963</v>
       </c>
       <c r="G219" t="s">
@@ -16778,7 +16876,7 @@
       <c r="E220" t="s">
         <v>29</v>
       </c>
-      <c r="F220" s="2">
+      <c r="F220" s="1">
         <v>45963</v>
       </c>
       <c r="G220" t="s">
@@ -16852,7 +16950,7 @@
       <c r="E221" t="s">
         <v>29</v>
       </c>
-      <c r="F221" s="2">
+      <c r="F221" s="1">
         <v>45963</v>
       </c>
       <c r="G221" t="s">
@@ -16929,7 +17027,7 @@
       <c r="E222" t="s">
         <v>29</v>
       </c>
-      <c r="F222" s="2">
+      <c r="F222" s="1">
         <v>45963</v>
       </c>
       <c r="G222" t="s">
@@ -17006,7 +17104,7 @@
       <c r="E223" t="s">
         <v>29</v>
       </c>
-      <c r="F223" s="2">
+      <c r="F223" s="1">
         <v>45963</v>
       </c>
       <c r="G223" t="s">
@@ -17080,7 +17178,7 @@
       <c r="E224" t="s">
         <v>29</v>
       </c>
-      <c r="F224" s="2">
+      <c r="F224" s="1">
         <v>45963</v>
       </c>
       <c r="G224" t="s">
@@ -17142,7 +17240,7 @@
       <c r="E225" t="s">
         <v>29</v>
       </c>
-      <c r="F225" s="2">
+      <c r="F225" s="1">
         <v>45963</v>
       </c>
       <c r="G225" t="s">
@@ -17216,7 +17314,7 @@
       <c r="E226" t="s">
         <v>403</v>
       </c>
-      <c r="F226" s="2">
+      <c r="F226" s="1">
         <v>45970</v>
       </c>
       <c r="G226" t="s">
@@ -17266,7 +17364,7 @@
       <c r="E227" t="s">
         <v>403</v>
       </c>
-      <c r="F227" s="2">
+      <c r="F227" s="1">
         <v>45970</v>
       </c>
       <c r="G227" t="s">
@@ -17316,7 +17414,7 @@
       <c r="E228" t="s">
         <v>403</v>
       </c>
-      <c r="F228" s="2">
+      <c r="F228" s="1">
         <v>45970</v>
       </c>
       <c r="G228" t="s">
@@ -17366,7 +17464,7 @@
       <c r="E229" t="s">
         <v>403</v>
       </c>
-      <c r="F229" s="2">
+      <c r="F229" s="1">
         <v>45970</v>
       </c>
       <c r="G229" t="s">
@@ -17419,7 +17517,7 @@
       <c r="E230" t="s">
         <v>403</v>
       </c>
-      <c r="F230" s="2">
+      <c r="F230" s="1">
         <v>45970</v>
       </c>
       <c r="G230" t="s">
@@ -17484,7 +17582,7 @@
       <c r="E231" t="s">
         <v>403</v>
       </c>
-      <c r="F231" s="2">
+      <c r="F231" s="1">
         <v>45970</v>
       </c>
       <c r="G231" t="s">
@@ -17555,7 +17653,7 @@
       <c r="E232" t="s">
         <v>403</v>
       </c>
-      <c r="F232" s="2">
+      <c r="F232" s="1">
         <v>45970</v>
       </c>
       <c r="G232" t="s">
@@ -17605,7 +17703,7 @@
       <c r="E233" t="s">
         <v>403</v>
       </c>
-      <c r="F233" s="2">
+      <c r="F233" s="1">
         <v>45970</v>
       </c>
       <c r="G233" t="s">
@@ -17655,7 +17753,7 @@
       <c r="E234" t="s">
         <v>403</v>
       </c>
-      <c r="F234" s="2">
+      <c r="F234" s="1">
         <v>45970</v>
       </c>
       <c r="G234" t="s">
@@ -17708,7 +17806,7 @@
       <c r="E235" t="s">
         <v>642</v>
       </c>
-      <c r="F235" s="2">
+      <c r="F235" s="1">
         <v>45991</v>
       </c>
       <c r="G235" t="s">
@@ -17782,7 +17880,7 @@
       <c r="E236" t="s">
         <v>642</v>
       </c>
-      <c r="F236" s="2">
+      <c r="F236" s="1">
         <v>45991</v>
       </c>
       <c r="G236" t="s">
@@ -17859,7 +17957,7 @@
       <c r="E237" t="s">
         <v>642</v>
       </c>
-      <c r="F237" s="2">
+      <c r="F237" s="1">
         <v>45991</v>
       </c>
       <c r="G237" t="s">
@@ -17936,7 +18034,7 @@
       <c r="E238" t="s">
         <v>642</v>
       </c>
-      <c r="F238" s="2">
+      <c r="F238" s="1">
         <v>45991</v>
       </c>
       <c r="G238" t="s">
@@ -18013,7 +18111,7 @@
       <c r="E239" t="s">
         <v>642</v>
       </c>
-      <c r="F239" s="2">
+      <c r="F239" s="1">
         <v>45991</v>
       </c>
       <c r="G239" t="s">
@@ -18090,7 +18188,7 @@
       <c r="E240" t="s">
         <v>642</v>
       </c>
-      <c r="F240" s="2">
+      <c r="F240" s="1">
         <v>45991</v>
       </c>
       <c r="G240" t="s">
@@ -18167,7 +18265,7 @@
       <c r="E241" t="s">
         <v>642</v>
       </c>
-      <c r="F241" s="2">
+      <c r="F241" s="1">
         <v>45991</v>
       </c>
       <c r="G241" t="s">
@@ -18244,7 +18342,7 @@
       <c r="E242" t="s">
         <v>642</v>
       </c>
-      <c r="F242" s="2">
+      <c r="F242" s="1">
         <v>45991</v>
       </c>
       <c r="G242" t="s">
@@ -18321,7 +18419,7 @@
       <c r="E243" t="s">
         <v>642</v>
       </c>
-      <c r="F243" s="2">
+      <c r="F243" s="1">
         <v>45991</v>
       </c>
       <c r="G243" t="s">
@@ -18398,7 +18496,7 @@
       <c r="E244" t="s">
         <v>642</v>
       </c>
-      <c r="F244" s="2">
+      <c r="F244" s="1">
         <v>45991</v>
       </c>
       <c r="G244" t="s">
@@ -18475,7 +18573,7 @@
       <c r="E245" t="s">
         <v>642</v>
       </c>
-      <c r="F245" s="2">
+      <c r="F245" s="1">
         <v>45991</v>
       </c>
       <c r="G245" t="s">
@@ -18552,7 +18650,7 @@
       <c r="E246" t="s">
         <v>642</v>
       </c>
-      <c r="F246" s="2">
+      <c r="F246" s="1">
         <v>45991</v>
       </c>
       <c r="G246" t="s">
@@ -18629,7 +18727,7 @@
       <c r="E247" t="s">
         <v>642</v>
       </c>
-      <c r="F247" s="2">
+      <c r="F247" s="1">
         <v>45991</v>
       </c>
       <c r="G247" t="s">
@@ -18706,7 +18804,7 @@
       <c r="E248" t="s">
         <v>642</v>
       </c>
-      <c r="F248" s="2">
+      <c r="F248" s="1">
         <v>45991</v>
       </c>
       <c r="G248" t="s">
@@ -18783,7 +18881,7 @@
       <c r="E249" t="s">
         <v>642</v>
       </c>
-      <c r="F249" s="2">
+      <c r="F249" s="1">
         <v>45991</v>
       </c>
       <c r="G249" t="s">
@@ -18860,7 +18958,7 @@
       <c r="E250" t="s">
         <v>642</v>
       </c>
-      <c r="F250" s="2">
+      <c r="F250" s="1">
         <v>45991</v>
       </c>
       <c r="G250" t="s">
@@ -18937,7 +19035,7 @@
       <c r="E251" t="s">
         <v>642</v>
       </c>
-      <c r="F251" s="2">
+      <c r="F251" s="1">
         <v>45991</v>
       </c>
       <c r="G251" t="s">
@@ -19014,7 +19112,7 @@
       <c r="E252" t="s">
         <v>642</v>
       </c>
-      <c r="F252" s="2">
+      <c r="F252" s="1">
         <v>45991</v>
       </c>
       <c r="G252" t="s">
@@ -19091,7 +19189,7 @@
       <c r="E253" t="s">
         <v>922</v>
       </c>
-      <c r="F253" s="2">
+      <c r="F253" s="1">
         <v>46012</v>
       </c>
       <c r="G253" t="s">
@@ -19168,7 +19266,7 @@
       <c r="E254" t="s">
         <v>922</v>
       </c>
-      <c r="F254" s="2">
+      <c r="F254" s="1">
         <v>46012</v>
       </c>
       <c r="G254" t="s">
@@ -19245,7 +19343,7 @@
       <c r="E255" t="s">
         <v>922</v>
       </c>
-      <c r="F255" s="2">
+      <c r="F255" s="1">
         <v>46012</v>
       </c>
       <c r="G255" t="s">
@@ -19322,7 +19420,7 @@
       <c r="E256" t="s">
         <v>922</v>
       </c>
-      <c r="F256" s="2">
+      <c r="F256" s="1">
         <v>46012</v>
       </c>
       <c r="G256" t="s">
@@ -19396,7 +19494,7 @@
       <c r="E257" t="s">
         <v>922</v>
       </c>
-      <c r="F257" s="2">
+      <c r="F257" s="1">
         <v>46012</v>
       </c>
       <c r="G257" t="s">
@@ -19473,7 +19571,7 @@
       <c r="E258" t="s">
         <v>922</v>
       </c>
-      <c r="F258" s="2">
+      <c r="F258" s="1">
         <v>46012</v>
       </c>
       <c r="G258" t="s">
@@ -19550,7 +19648,7 @@
       <c r="E259" t="s">
         <v>922</v>
       </c>
-      <c r="F259" s="2">
+      <c r="F259" s="1">
         <v>46012</v>
       </c>
       <c r="G259" t="s">
@@ -19627,7 +19725,7 @@
       <c r="E260" t="s">
         <v>922</v>
       </c>
-      <c r="F260" s="2">
+      <c r="F260" s="1">
         <v>46012</v>
       </c>
       <c r="G260" t="s">
@@ -19704,7 +19802,7 @@
       <c r="E261" t="s">
         <v>922</v>
       </c>
-      <c r="F261" s="2">
+      <c r="F261" s="1">
         <v>46012</v>
       </c>
       <c r="G261" t="s">
@@ -19781,7 +19879,7 @@
       <c r="E262" t="s">
         <v>922</v>
       </c>
-      <c r="F262" s="2">
+      <c r="F262" s="1">
         <v>46012</v>
       </c>
       <c r="G262" t="s">
@@ -19858,7 +19956,7 @@
       <c r="E263" t="s">
         <v>922</v>
       </c>
-      <c r="F263" s="2">
+      <c r="F263" s="1">
         <v>46012</v>
       </c>
       <c r="G263" t="s">
@@ -19935,7 +20033,7 @@
       <c r="E264" t="s">
         <v>922</v>
       </c>
-      <c r="F264" s="2">
+      <c r="F264" s="1">
         <v>46012</v>
       </c>
       <c r="G264" t="s">
@@ -20012,7 +20110,7 @@
       <c r="E265" t="s">
         <v>922</v>
       </c>
-      <c r="F265" s="2">
+      <c r="F265" s="1">
         <v>46012</v>
       </c>
       <c r="G265" t="s">
@@ -20089,7 +20187,7 @@
       <c r="E266" t="s">
         <v>922</v>
       </c>
-      <c r="F266" s="2">
+      <c r="F266" s="1">
         <v>46012</v>
       </c>
       <c r="G266" t="s">
@@ -20166,7 +20264,7 @@
       <c r="E267" t="s">
         <v>922</v>
       </c>
-      <c r="F267" s="2">
+      <c r="F267" s="1">
         <v>46012</v>
       </c>
       <c r="G267" t="s">
@@ -20243,7 +20341,7 @@
       <c r="E268" t="s">
         <v>922</v>
       </c>
-      <c r="F268" s="2">
+      <c r="F268" s="1">
         <v>46012</v>
       </c>
       <c r="G268" t="s">
@@ -20320,7 +20418,7 @@
       <c r="E269" t="s">
         <v>922</v>
       </c>
-      <c r="F269" s="2">
+      <c r="F269" s="1">
         <v>46012</v>
       </c>
       <c r="G269" t="s">
@@ -20397,7 +20495,7 @@
       <c r="E270" t="s">
         <v>922</v>
       </c>
-      <c r="F270" s="2">
+      <c r="F270" s="1">
         <v>46012</v>
       </c>
       <c r="G270" t="s">
@@ -20474,7 +20572,7 @@
       <c r="E271" t="s">
         <v>403</v>
       </c>
-      <c r="F271" s="2">
+      <c r="F271" s="1">
         <v>46040</v>
       </c>
       <c r="G271" t="s">
@@ -20539,7 +20637,7 @@
       <c r="E272" t="s">
         <v>403</v>
       </c>
-      <c r="F272" s="2">
+      <c r="F272" s="1">
         <v>46040</v>
       </c>
       <c r="G272" t="s">
@@ -20604,7 +20702,7 @@
       <c r="E273" t="s">
         <v>403</v>
       </c>
-      <c r="F273" s="2">
+      <c r="F273" s="1">
         <v>46040</v>
       </c>
       <c r="G273" t="s">
@@ -20669,7 +20767,7 @@
       <c r="E274" t="s">
         <v>403</v>
       </c>
-      <c r="F274" s="2">
+      <c r="F274" s="1">
         <v>46040</v>
       </c>
       <c r="G274" t="s">
@@ -20734,7 +20832,7 @@
       <c r="E275" t="s">
         <v>403</v>
       </c>
-      <c r="F275" s="2">
+      <c r="F275" s="1">
         <v>46040</v>
       </c>
       <c r="G275" t="s">
@@ -20799,7 +20897,7 @@
       <c r="E276" t="s">
         <v>403</v>
       </c>
-      <c r="F276" s="2">
+      <c r="F276" s="1">
         <v>46040</v>
       </c>
       <c r="G276" t="s">
@@ -20864,7 +20962,7 @@
       <c r="E277" t="s">
         <v>403</v>
       </c>
-      <c r="F277" s="2">
+      <c r="F277" s="1">
         <v>46040</v>
       </c>
       <c r="G277" t="s">
@@ -20929,7 +21027,7 @@
       <c r="E278" t="s">
         <v>403</v>
       </c>
-      <c r="F278" s="2">
+      <c r="F278" s="1">
         <v>46040</v>
       </c>
       <c r="G278" t="s">
@@ -20994,7 +21092,7 @@
       <c r="E279" t="s">
         <v>403</v>
       </c>
-      <c r="F279" s="2">
+      <c r="F279" s="1">
         <v>46040</v>
       </c>
       <c r="G279" t="s">
@@ -21059,7 +21157,7 @@
       <c r="E280" t="s">
         <v>403</v>
       </c>
-      <c r="F280" s="2">
+      <c r="F280" s="1">
         <v>46040</v>
       </c>
       <c r="G280" t="s">
@@ -21124,7 +21222,7 @@
       <c r="E281" t="s">
         <v>403</v>
       </c>
-      <c r="F281" s="2">
+      <c r="F281" s="1">
         <v>46040</v>
       </c>
       <c r="G281" t="s">
@@ -21189,7 +21287,7 @@
       <c r="E282" t="s">
         <v>403</v>
       </c>
-      <c r="F282" s="2">
+      <c r="F282" s="1">
         <v>46040</v>
       </c>
       <c r="G282" t="s">
@@ -21254,7 +21352,7 @@
       <c r="E283" t="s">
         <v>403</v>
       </c>
-      <c r="F283" s="2">
+      <c r="F283" s="1">
         <v>46040</v>
       </c>
       <c r="G283" t="s">
@@ -21319,7 +21417,7 @@
       <c r="E284" t="s">
         <v>403</v>
       </c>
-      <c r="F284" s="2">
+      <c r="F284" s="1">
         <v>46040</v>
       </c>
       <c r="G284" t="s">
@@ -21384,7 +21482,7 @@
       <c r="E285" t="s">
         <v>403</v>
       </c>
-      <c r="F285" s="2">
+      <c r="F285" s="1">
         <v>46040</v>
       </c>
       <c r="G285" t="s">
@@ -21458,7 +21556,7 @@
       <c r="E286" t="s">
         <v>403</v>
       </c>
-      <c r="F286" s="2">
+      <c r="F286" s="1">
         <v>46040</v>
       </c>
       <c r="G286" t="s">
@@ -21523,7 +21621,7 @@
       <c r="E287" t="s">
         <v>403</v>
       </c>
-      <c r="F287" s="2">
+      <c r="F287" s="1">
         <v>46040</v>
       </c>
       <c r="G287" t="s">
@@ -21588,7 +21686,7 @@
       <c r="E288" t="s">
         <v>403</v>
       </c>
-      <c r="F288" s="2">
+      <c r="F288" s="1">
         <v>46040</v>
       </c>
       <c r="G288" t="s">
@@ -21653,7 +21751,7 @@
       <c r="E289" t="s">
         <v>403</v>
       </c>
-      <c r="F289" s="2">
+      <c r="F289" s="1">
         <v>46040</v>
       </c>
       <c r="G289" t="s">
@@ -21718,7 +21816,7 @@
       <c r="E290" t="s">
         <v>403</v>
       </c>
-      <c r="F290" s="2">
+      <c r="F290" s="1">
         <v>46040</v>
       </c>
       <c r="G290" t="s">
@@ -21783,7 +21881,7 @@
       <c r="E291" t="s">
         <v>403</v>
       </c>
-      <c r="F291" s="2">
+      <c r="F291" s="1">
         <v>46040</v>
       </c>
       <c r="G291" t="s">
@@ -21848,7 +21946,7 @@
       <c r="E292" t="s">
         <v>403</v>
       </c>
-      <c r="F292" s="2">
+      <c r="F292" s="1">
         <v>46040</v>
       </c>
       <c r="G292" t="s">
@@ -21913,7 +22011,7 @@
       <c r="E293" t="s">
         <v>403</v>
       </c>
-      <c r="F293" s="2">
+      <c r="F293" s="1">
         <v>46040</v>
       </c>
       <c r="G293" t="s">
@@ -21978,7 +22076,7 @@
       <c r="E294" t="s">
         <v>403</v>
       </c>
-      <c r="F294" s="2">
+      <c r="F294" s="1">
         <v>46040</v>
       </c>
       <c r="G294" t="s">
@@ -22043,7 +22141,7 @@
       <c r="E295" t="s">
         <v>403</v>
       </c>
-      <c r="F295" s="2">
+      <c r="F295" s="1">
         <v>46040</v>
       </c>
       <c r="G295" t="s">
@@ -22108,7 +22206,7 @@
       <c r="E296" t="s">
         <v>403</v>
       </c>
-      <c r="F296" s="2">
+      <c r="F296" s="1">
         <v>46040</v>
       </c>
       <c r="G296" t="s">
@@ -22173,7 +22271,7 @@
       <c r="E297" t="s">
         <v>403</v>
       </c>
-      <c r="F297" s="2">
+      <c r="F297" s="1">
         <v>46040</v>
       </c>
       <c r="G297" t="s">
@@ -22238,7 +22336,7 @@
       <c r="E298" t="s">
         <v>403</v>
       </c>
-      <c r="F298" s="2">
+      <c r="F298" s="1">
         <v>46040</v>
       </c>
       <c r="G298" t="s">
@@ -22303,7 +22401,7 @@
       <c r="E299" t="s">
         <v>403</v>
       </c>
-      <c r="F299" s="2">
+      <c r="F299" s="1">
         <v>46040</v>
       </c>
       <c r="G299" t="s">
@@ -22368,7 +22466,7 @@
       <c r="E300" t="s">
         <v>403</v>
       </c>
-      <c r="F300" s="2">
+      <c r="F300" s="1">
         <v>46040</v>
       </c>
       <c r="G300" t="s">
@@ -22433,7 +22531,7 @@
       <c r="E301" t="s">
         <v>403</v>
       </c>
-      <c r="F301" s="2">
+      <c r="F301" s="1">
         <v>46040</v>
       </c>
       <c r="G301" t="s">
@@ -22498,7 +22596,7 @@
       <c r="E302" t="s">
         <v>403</v>
       </c>
-      <c r="F302" s="2">
+      <c r="F302" s="1">
         <v>46040</v>
       </c>
       <c r="G302" t="s">
@@ -22563,7 +22661,7 @@
       <c r="E303" t="s">
         <v>29</v>
       </c>
-      <c r="F303" s="2">
+      <c r="F303" s="1">
         <v>46047</v>
       </c>
       <c r="G303" t="s">
@@ -22640,7 +22738,7 @@
       <c r="E304" t="s">
         <v>29</v>
       </c>
-      <c r="F304" s="2">
+      <c r="F304" s="1">
         <v>46047</v>
       </c>
       <c r="G304" t="s">
@@ -22717,7 +22815,7 @@
       <c r="E305" t="s">
         <v>29</v>
       </c>
-      <c r="F305" s="2">
+      <c r="F305" s="1">
         <v>46047</v>
       </c>
       <c r="G305" t="s">
@@ -22782,7 +22880,7 @@
       <c r="E306" t="s">
         <v>29</v>
       </c>
-      <c r="F306" s="2">
+      <c r="F306" s="1">
         <v>46047</v>
       </c>
       <c r="G306" t="s">
@@ -22847,7 +22945,7 @@
       <c r="E307" t="s">
         <v>29</v>
       </c>
-      <c r="F307" s="2">
+      <c r="F307" s="1">
         <v>46047</v>
       </c>
       <c r="G307" t="s">
@@ -22912,7 +23010,7 @@
       <c r="E308" t="s">
         <v>29</v>
       </c>
-      <c r="F308" s="2">
+      <c r="F308" s="1">
         <v>46047</v>
       </c>
       <c r="G308" t="s">
@@ -22986,7 +23084,7 @@
       <c r="E309" t="s">
         <v>29</v>
       </c>
-      <c r="F309" s="2">
+      <c r="F309" s="1">
         <v>46047</v>
       </c>
       <c r="G309" t="s">
@@ -23063,7 +23161,7 @@
       <c r="E310" t="s">
         <v>29</v>
       </c>
-      <c r="F310" s="2">
+      <c r="F310" s="1">
         <v>46047</v>
       </c>
       <c r="G310" t="s">
@@ -23140,7 +23238,7 @@
       <c r="E311" t="s">
         <v>29</v>
       </c>
-      <c r="F311" s="2">
+      <c r="F311" s="1">
         <v>46047</v>
       </c>
       <c r="G311" t="s">
@@ -23217,7 +23315,7 @@
       <c r="E312" t="s">
         <v>29</v>
       </c>
-      <c r="F312" s="2">
+      <c r="F312" s="1">
         <v>46047</v>
       </c>
       <c r="G312" t="s">
@@ -23294,7 +23392,7 @@
       <c r="E313" t="s">
         <v>29</v>
       </c>
-      <c r="F313" s="2">
+      <c r="F313" s="1">
         <v>46047</v>
       </c>
       <c r="G313" t="s">
@@ -23371,7 +23469,7 @@
       <c r="E314" t="s">
         <v>29</v>
       </c>
-      <c r="F314" s="2">
+      <c r="F314" s="1">
         <v>46047</v>
       </c>
       <c r="G314" t="s">
@@ -23434,5 +23532,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data_clean/data_merged.xlsx
+++ b/data_clean/data_merged.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Documents\All Work Files\1. PE New Report\data_clean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1589DE59-18C2-40E3-9430-03B80D580DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9443D9D5-D5DF-4343-A659-D61C994BC1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4809" uniqueCount="1172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5073" uniqueCount="1207">
   <si>
     <t>Email</t>
   </si>
@@ -100,7 +100,7 @@
     <t>listyay@yahoo.com</t>
   </si>
   <si>
-    <t>yulia listya</t>
+    <t>Yulia listya</t>
   </si>
   <si>
     <t>6281228636388</t>
@@ -127,7 +127,7 @@
     <t>vine.marcelin@gmail.com</t>
   </si>
   <si>
-    <t>vine marcelin</t>
+    <t>Vine marcelin</t>
   </si>
   <si>
     <t>6281802418188</t>
@@ -136,7 +136,7 @@
     <t>lianlian@gmail.com</t>
   </si>
   <si>
-    <t>lian</t>
+    <t>Lian</t>
   </si>
   <si>
     <t>6289504166061</t>
@@ -145,7 +145,7 @@
     <t>trisuwarni9741@gmail.com</t>
   </si>
   <si>
-    <t>tri suwarni</t>
+    <t>Tri suwarni</t>
   </si>
   <si>
     <t>6281225766343</t>
@@ -160,7 +160,7 @@
     <t>ikha.rasti@gmail.com</t>
   </si>
   <si>
-    <t>ikha</t>
+    <t>Ikha</t>
   </si>
   <si>
     <t>628122802535</t>
@@ -169,7 +169,7 @@
     <t>loli_cute2002@yahoo.com</t>
   </si>
   <si>
-    <t>lolita</t>
+    <t>Lolita</t>
   </si>
   <si>
     <t>6281329088688</t>
@@ -184,7 +184,7 @@
     <t>nirmala.tan@gmail.com</t>
   </si>
   <si>
-    <t>nirmala tan</t>
+    <t>Nirmala tan</t>
   </si>
   <si>
     <t>6281931921777</t>
@@ -193,7 +193,7 @@
     <t>rikakurnia@gmail.com</t>
   </si>
   <si>
-    <t>rika kurnia</t>
+    <t>Rika kurnia</t>
   </si>
   <si>
     <t>628122566817</t>
@@ -202,7 +202,7 @@
     <t>me.lindakurnia85@gmail.com</t>
   </si>
   <si>
-    <t>linda kurnia</t>
+    <t>Linda kurnia</t>
   </si>
   <si>
     <t>6281325470000</t>
@@ -211,7 +211,7 @@
     <t>ririnabl7@gmail.com</t>
   </si>
   <si>
-    <t>ririn lastyarini</t>
+    <t>Ririn lastyarini</t>
   </si>
   <si>
     <t>62811279787</t>
@@ -220,7 +220,7 @@
     <t>shellymarlina@gmail.com</t>
   </si>
   <si>
-    <t>shelly marlina</t>
+    <t>Shelly marlina</t>
   </si>
   <si>
     <t>6281805955055</t>
@@ -229,7 +229,7 @@
     <t>goliennio@gmail.com</t>
   </si>
   <si>
-    <t>lien</t>
+    <t>Lien</t>
   </si>
   <si>
     <t>62895423000000</t>
@@ -238,7 +238,7 @@
     <t>susisusiel85@gmail.com</t>
   </si>
   <si>
-    <t>susi</t>
+    <t>Susi</t>
   </si>
   <si>
     <t>6281229877399</t>
@@ -253,7 +253,7 @@
     <t>khembaliyoga@gmail.com</t>
   </si>
   <si>
-    <t>merry khembali</t>
+    <t>Merry khembali</t>
   </si>
   <si>
     <t>62816772151</t>
@@ -271,7 +271,7 @@
     <t>ikaellyana88@gmail.com</t>
   </si>
   <si>
-    <t>verena ika</t>
+    <t>Verena ika</t>
   </si>
   <si>
     <t>628112789198</t>
@@ -280,7 +280,7 @@
     <t>eruta.91@gmail.com</t>
   </si>
   <si>
-    <t>tanti</t>
+    <t>Tanti</t>
   </si>
   <si>
     <t>6285602005189</t>
@@ -289,7 +289,7 @@
     <t>healsasyalala@gmail.com</t>
   </si>
   <si>
-    <t>hellen</t>
+    <t>Hellen</t>
   </si>
   <si>
     <t>6282136585756</t>
@@ -298,7 +298,7 @@
     <t>annagusiwi@gmail.com</t>
   </si>
   <si>
-    <t>anna agusiwi</t>
+    <t>Anna agusiwi</t>
   </si>
   <si>
     <t>6281215027031</t>
@@ -307,7 +307,7 @@
     <t>ervinneyshia@gmail.com</t>
   </si>
   <si>
-    <t>ervin nurvitasari</t>
+    <t>Ervin nurvitasari</t>
   </si>
   <si>
     <t>6285655501113</t>
@@ -328,7 +328,7 @@
     <t>yunisetiyaningsih123@gmail.com</t>
   </si>
   <si>
-    <t>yuni setiyaningsih</t>
+    <t>Yuni setiyaningsih</t>
   </si>
   <si>
     <t>628112888442</t>
@@ -352,7 +352,7 @@
     <t>nineezyoga12@gmail.com</t>
   </si>
   <si>
-    <t>ninez</t>
+    <t>Ninez</t>
   </si>
   <si>
     <t>6282231033238</t>
@@ -367,7 +367,7 @@
     <t>marriee23@gmail.com</t>
   </si>
   <si>
-    <t>ming ming</t>
+    <t>Ming ming</t>
   </si>
   <si>
     <t>628122582010</t>
@@ -376,7 +376,7 @@
     <t>mey_msco@yahoo.com</t>
   </si>
   <si>
-    <t>tanty megawati</t>
+    <t>Tanty megawati</t>
   </si>
   <si>
     <t>6289507348565</t>
@@ -385,7 +385,7 @@
     <t>end.setiawati253@gmail.com</t>
   </si>
   <si>
-    <t>endang setiawati</t>
+    <t>Endang setiawati</t>
   </si>
   <si>
     <t>6283869695700</t>
@@ -394,7 +394,7 @@
     <t>devinadrsolo@gmail.com</t>
   </si>
   <si>
-    <t>devina</t>
+    <t>Devina</t>
   </si>
   <si>
     <t>6282227456520</t>
@@ -403,7 +403,7 @@
     <t>yuniarap@gmail.com</t>
   </si>
   <si>
-    <t>yuniar apriyanti</t>
+    <t>Yuniar apriyanti</t>
   </si>
   <si>
     <t>6283891068700</t>
@@ -418,7 +418,7 @@
     <t>rianacandrasari@yahoo.com</t>
   </si>
   <si>
-    <t>riana</t>
+    <t>Riana</t>
   </si>
   <si>
     <t>628112559393</t>
@@ -427,7 +427,7 @@
     <t>christina.mdh@gmail.com</t>
   </si>
   <si>
-    <t>christina mariani</t>
+    <t>Christina mariani</t>
   </si>
   <si>
     <t>6282139643234</t>
@@ -436,7 +436,7 @@
     <t>shezamila83@gmail.com</t>
   </si>
   <si>
-    <t>mila</t>
+    <t>Mila</t>
   </si>
   <si>
     <t>6281809434406</t>
@@ -445,7 +445,7 @@
     <t>santi.studi@gmail.com</t>
   </si>
   <si>
-    <t>santi s. l</t>
+    <t>Santi s. l</t>
   </si>
   <si>
     <t>6282137502904</t>
@@ -454,7 +454,7 @@
     <t>amilinov2000@gmail.com</t>
   </si>
   <si>
-    <t>listyaning</t>
+    <t>Listyaning</t>
   </si>
   <si>
     <t>6282223833700</t>
@@ -463,7 +463,7 @@
     <t>bless.eliz99@gmail.com</t>
   </si>
   <si>
-    <t>elizabet sally</t>
+    <t>Elizabet sally</t>
   </si>
   <si>
     <t>628115221950</t>
@@ -472,7 +472,7 @@
     <t>mamanuno2@gmail.com</t>
   </si>
   <si>
-    <t>galih titis</t>
+    <t>Galih titis</t>
   </si>
   <si>
     <t>628995389484</t>
@@ -481,7 +481,7 @@
     <t>notarisppat.emy@gmail.com</t>
   </si>
   <si>
-    <t>emy rachmawati</t>
+    <t>Emy rachmawati</t>
   </si>
   <si>
     <t>6287722487952</t>
@@ -496,7 +496,7 @@
     <t>viola_kakashi@yahoo.com</t>
   </si>
   <si>
-    <t>christine viola</t>
+    <t>Christine viola</t>
   </si>
   <si>
     <t>6285728680314</t>
@@ -505,7 +505,7 @@
     <t>nenengrdewi78@gmail.com</t>
   </si>
   <si>
-    <t>neneng r dewi</t>
+    <t>Neneng r dewi</t>
   </si>
   <si>
     <t>6281277176691</t>
@@ -514,7 +514,7 @@
     <t>santosohandayani0@gmail.com</t>
   </si>
   <si>
-    <t>handayani</t>
+    <t>Handayani</t>
   </si>
   <si>
     <t>62895327000000</t>
@@ -529,7 +529,7 @@
     <t>palmsfarei123@gmail.com</t>
   </si>
   <si>
-    <t>santi farei</t>
+    <t>Santi farei</t>
   </si>
   <si>
     <t>6289620694329</t>
@@ -538,7 +538,7 @@
     <t>toscaconey10@gmail.com</t>
   </si>
   <si>
-    <t>kunik retnoningsih</t>
+    <t>Kunik retnoningsih</t>
   </si>
   <si>
     <t>6281216238775</t>
@@ -553,7 +553,7 @@
     <t>erninchandra@gmail.com</t>
   </si>
   <si>
-    <t>ernin chandra</t>
+    <t>Ernin chandra</t>
   </si>
   <si>
     <t>628122986788</t>
@@ -562,7 +562,7 @@
     <t>tauf_riz@yahoo.com</t>
   </si>
   <si>
-    <t>taufiq rizal</t>
+    <t>Taufiq rizal</t>
   </si>
   <si>
     <t>6285876164340</t>
@@ -571,7 +571,7 @@
     <t>syifaiftitah26@gmail.com</t>
   </si>
   <si>
-    <t>syifa i febrianti</t>
+    <t>Syifa i febrianti</t>
   </si>
   <si>
     <t>6281221316530</t>
@@ -580,7 +580,7 @@
     <t>ninawati1971@gmail.com</t>
   </si>
   <si>
-    <t>ninawati</t>
+    <t>Ninawati</t>
   </si>
   <si>
     <t>6287836116511</t>
@@ -589,7 +589,7 @@
     <t>tiwuktiwuk@gmail.com</t>
   </si>
   <si>
-    <t>tiwuk</t>
+    <t>Tiwuk</t>
   </si>
   <si>
     <t>628121542963</t>
@@ -598,7 +598,7 @@
     <t>deedessy090@gmail.com</t>
   </si>
   <si>
-    <t>dessy ary santi</t>
+    <t>Dessy ary santi</t>
   </si>
   <si>
     <t>6281335522872</t>
@@ -613,7 +613,7 @@
     <t>srijatilinda@gmail.com</t>
   </si>
   <si>
-    <t>gunawan</t>
+    <t>Gunawan</t>
   </si>
   <si>
     <t>6281802741972</t>
@@ -634,7 +634,7 @@
     <t>iradias913@gmail.com</t>
   </si>
   <si>
-    <t>ira widiastuti</t>
+    <t>Ira widiastuti</t>
   </si>
   <si>
     <t>6282226601976</t>
@@ -649,7 +649,7 @@
     <t>serafin.adhita@gmail.com</t>
   </si>
   <si>
-    <t>dhita</t>
+    <t>Dhita</t>
   </si>
   <si>
     <t>62817274366</t>
@@ -664,7 +664,7 @@
     <t>ayambakaroten@gmail.com</t>
   </si>
   <si>
-    <t>siti/ami</t>
+    <t>Siti/ami</t>
   </si>
   <si>
     <t>6285729686498</t>
@@ -673,7 +673,7 @@
     <t>andraega123456@gmail.com</t>
   </si>
   <si>
-    <t>christina murni yuliastuti</t>
+    <t>Christina murni yuliastuti</t>
   </si>
   <si>
     <t>6282226897015</t>
@@ -688,7 +688,7 @@
     <t>emmyratna@gmail.com</t>
   </si>
   <si>
-    <t>emmy ratna herawaty</t>
+    <t>Emmy ratna herawaty</t>
   </si>
   <si>
     <t>62818271019</t>
@@ -697,7 +697,7 @@
     <t>tirsasanti2395@gmail.com</t>
   </si>
   <si>
-    <t>tirsa santi</t>
+    <t>Tirsa santi</t>
   </si>
   <si>
     <t>6281215605330</t>
@@ -706,7 +706,7 @@
     <t>indah_ones@yahoo.com</t>
   </si>
   <si>
-    <t>indah pujiastuti</t>
+    <t>Indah pujiastuti</t>
   </si>
   <si>
     <t>62811805636</t>
@@ -715,7 +715,7 @@
     <t>inanamusailimah29@gmail.com</t>
   </si>
   <si>
-    <t>inana m</t>
+    <t>Inana m</t>
   </si>
   <si>
     <t>6285244787788</t>
@@ -724,7 +724,7 @@
     <t>cik.dona@gmail.com</t>
   </si>
   <si>
-    <t>dona</t>
+    <t>Dona</t>
   </si>
   <si>
     <t>6281804328688</t>
@@ -733,7 +733,7 @@
     <t>s.rahayusophie80@gmail.com</t>
   </si>
   <si>
-    <t>sri rahayu</t>
+    <t>Sri rahayu</t>
   </si>
   <si>
     <t>6285325430881</t>
@@ -742,7 +742,7 @@
     <t>indriyantiwiwik56@gmail.com</t>
   </si>
   <si>
-    <t>wiwik indriyanti</t>
+    <t>Wiwik indriyanti</t>
   </si>
   <si>
     <t>6282138623533</t>
@@ -751,7 +751,7 @@
     <t>lusimargiyani.lm@gmail.com</t>
   </si>
   <si>
-    <t>lusi margiyani</t>
+    <t>Lusi margiyani</t>
   </si>
   <si>
     <t>628111033074</t>
@@ -760,13 +760,13 @@
     <t>sita.sitaresmi@gmail.com</t>
   </si>
   <si>
-    <t>sitaresmi</t>
+    <t>Sitaresmi</t>
   </si>
   <si>
     <t>6287880786706</t>
   </si>
   <si>
-    <t>aswin</t>
+    <t>Aswin</t>
   </si>
   <si>
     <t>628121089484</t>
@@ -784,7 +784,7 @@
     <t>lisantini63@gmail.com</t>
   </si>
   <si>
-    <t>lisa (lisantini hadiwidjajati)</t>
+    <t>Lisa (lisantini hadiwidjajati)</t>
   </si>
   <si>
     <t>6281219746618</t>
@@ -802,7 +802,7 @@
     <t>tutifruity80@gmail.com</t>
   </si>
   <si>
-    <t>retna ambarwati</t>
+    <t>Retna ambarwati</t>
   </si>
   <si>
     <t>628165417335</t>
@@ -814,7 +814,7 @@
     <t>mariacici78@gmail.com</t>
   </si>
   <si>
-    <t>maria cicilia dini hendriatmaja</t>
+    <t>Maria cicilia dini hendriatmaja</t>
   </si>
   <si>
     <t>6281225058799</t>
@@ -823,7 +823,7 @@
     <t>dw_mia@proton.me</t>
   </si>
   <si>
-    <t>mia windarti</t>
+    <t>Mia windarti</t>
   </si>
   <si>
     <t>6281328623207</t>
@@ -832,7 +832,7 @@
     <t>erikjoslydie@gmail.com</t>
   </si>
   <si>
-    <t>erik de winne</t>
+    <t>Erik de winne</t>
   </si>
   <si>
     <t>62816658507</t>
@@ -841,7 +841,7 @@
     <t>astuti2021wid@gmail.com</t>
   </si>
   <si>
-    <t>erna widiastuti</t>
+    <t>Erna widiastuti</t>
   </si>
   <si>
     <t>6287810196054</t>
@@ -850,7 +850,7 @@
     <t>listiawati123@gmail.com</t>
   </si>
   <si>
-    <t>listiawati</t>
+    <t>Listiawati</t>
   </si>
   <si>
     <t>6287730614588</t>
@@ -859,7 +859,7 @@
     <t>meyta.w.p@gmail.com</t>
   </si>
   <si>
-    <t>meyta wahyu prima</t>
+    <t>Meyta wahyu prima</t>
   </si>
   <si>
     <t>628157777191</t>
@@ -868,7 +868,7 @@
     <t>naninggemilang@gmail.com</t>
   </si>
   <si>
-    <t>prihasnaningsih</t>
+    <t>Prihasnaningsih</t>
   </si>
   <si>
     <t>6282137678904</t>
@@ -877,7 +877,7 @@
     <t>sukestini@gmail.com</t>
   </si>
   <si>
-    <t>ni luh sukestini</t>
+    <t>Ni luh sukestini</t>
   </si>
   <si>
     <t>62817104969</t>
@@ -886,7 +886,7 @@
     <t>drg.tayya@gmail.com</t>
   </si>
   <si>
-    <t>tristiarina</t>
+    <t>Tristiarina</t>
   </si>
   <si>
     <t>6282220100494</t>
@@ -895,7 +895,7 @@
     <t>chantychanty@gmail.com</t>
   </si>
   <si>
-    <t>chanty</t>
+    <t>Chanty</t>
   </si>
   <si>
     <t>6281229433389</t>
@@ -904,7 +904,7 @@
     <t>yatikyatik@gmail.com</t>
   </si>
   <si>
-    <t>yatik</t>
+    <t>Yatik</t>
   </si>
   <si>
     <t>6281477100083</t>
@@ -919,7 +919,7 @@
     <t>auliarafika14@gmail.com</t>
   </si>
   <si>
-    <t>yanti</t>
+    <t>Yanti</t>
   </si>
   <si>
     <t>6281227729025</t>
@@ -928,7 +928,7 @@
     <t>anunganindita@gmail.com</t>
   </si>
   <si>
-    <t>anung anindita</t>
+    <t>Anung anindita</t>
   </si>
   <si>
     <t>6281328221111</t>
@@ -943,7 +943,7 @@
     <t>mayasari.dita@ymail.com</t>
   </si>
   <si>
-    <t>ditaa</t>
+    <t>Ditaa</t>
   </si>
   <si>
     <t>628563257268</t>
@@ -952,7 +952,7 @@
     <t>indraashoka@gmail.com</t>
   </si>
   <si>
-    <t>indra ashoka</t>
+    <t>Indra ashoka</t>
   </si>
   <si>
     <t>6281806800156</t>
@@ -961,7 +961,7 @@
     <t>akunlita2018@gmail.com</t>
   </si>
   <si>
-    <t>lita</t>
+    <t>Lita</t>
   </si>
   <si>
     <t>6281568353425</t>
@@ -970,7 +970,7 @@
     <t>dahlankhanifah75@gmail.com</t>
   </si>
   <si>
-    <t>khanifah</t>
+    <t>Khanifah</t>
   </si>
   <si>
     <t>6281228675867</t>
@@ -979,7 +979,7 @@
     <t>erminagustinp@gmail.com</t>
   </si>
   <si>
-    <t>ermin agustin pondah</t>
+    <t>Ermin agustin pondah</t>
   </si>
   <si>
     <t>6285641218109</t>
@@ -988,7 +988,7 @@
     <t>ardiyuda0simpati@gmail.com</t>
   </si>
   <si>
-    <t>dimas ardi</t>
+    <t>Dimas ardi</t>
   </si>
   <si>
     <t>6285713098250</t>
@@ -997,7 +997,7 @@
     <t>iskandaryoben@gmail.com</t>
   </si>
   <si>
-    <t>iskandar</t>
+    <t>Iskandar</t>
   </si>
   <si>
     <t>6281326005003</t>
@@ -1006,7 +1006,7 @@
     <t>rizkyvrean02@gmail.com</t>
   </si>
   <si>
-    <t>eni handayani</t>
+    <t>Eni handayani</t>
   </si>
   <si>
     <t>6281390842444</t>
@@ -1033,7 +1033,7 @@
     <t>gustav.blacksweet@gmail.com</t>
   </si>
   <si>
-    <t>agus suprijatno</t>
+    <t>Agus suprijatno</t>
   </si>
   <si>
     <t>6281390841444</t>
@@ -1048,7 +1048,7 @@
     <t>errasalmaa0216@gmail.com</t>
   </si>
   <si>
-    <t>erna puji erawati</t>
+    <t>Erna puji erawati</t>
   </si>
   <si>
     <t>6281228128338</t>
@@ -1081,7 +1081,7 @@
     <t>mashasaadah@gmail.com</t>
   </si>
   <si>
-    <t>masadah</t>
+    <t>Masadah</t>
   </si>
   <si>
     <t>6285803697185</t>
@@ -1105,7 +1105,7 @@
     <t>best.eristy@gmail.com</t>
   </si>
   <si>
-    <t>endang ristiyowati</t>
+    <t>Endang ristiyowati</t>
   </si>
   <si>
     <t>6282242987466</t>
@@ -1123,7 +1123,7 @@
     <t>menik.poenya@gmail.com</t>
   </si>
   <si>
-    <t>suyati menik</t>
+    <t>Suyati menik</t>
   </si>
   <si>
     <t>6285226040026</t>
@@ -1144,7 +1144,7 @@
     <t>yeyespdt@gmail.com</t>
   </si>
   <si>
-    <t>yayuk supriyati</t>
+    <t>Yayuk supriyati</t>
   </si>
   <si>
     <t>628122555480</t>
@@ -1162,7 +1162,7 @@
     <t>dwiyanirespati@gmail.com</t>
   </si>
   <si>
-    <t>dyani respati</t>
+    <t>Dyani respati</t>
   </si>
   <si>
     <t>6282328771976</t>
@@ -1177,7 +1177,7 @@
     <t>nathaliaw1dy4@gmail.com</t>
   </si>
   <si>
-    <t>widya nathalia</t>
+    <t>Widya nathalia</t>
   </si>
   <si>
     <t>6289670734070</t>
@@ -1201,7 +1201,7 @@
     <t>ettyrose13@gmail.com</t>
   </si>
   <si>
-    <t>ety roesmawati</t>
+    <t>Ety roesmawati</t>
   </si>
   <si>
     <t>6282136114343</t>
@@ -1222,7 +1222,7 @@
     <t>bintabee@gmail.com</t>
   </si>
   <si>
-    <t>binta nadhila</t>
+    <t>Binta nadhila</t>
   </si>
   <si>
     <t>087884640172</t>
@@ -1258,7 +1258,7 @@
     <t>astri.r.faizal@gmail.com</t>
   </si>
   <si>
-    <t>Astri Rahmasari</t>
+    <t>Astri rahmasari</t>
   </si>
   <si>
     <t>08111119251</t>
@@ -1270,7 +1270,7 @@
     <t>Depok</t>
   </si>
   <si>
-    <t>AGIOR AKBAR</t>
+    <t>Agior akbar</t>
   </si>
   <si>
     <t>TANJUNG PINANG</t>
@@ -1285,22 +1285,22 @@
     <t>Kepulauan Riau</t>
   </si>
   <si>
-    <t>ING/SYAFIRA MARDANI PUTRI</t>
-  </si>
-  <si>
-    <t>FX DWI RAHARJANI</t>
+    <t>Ing/syafira mardani putri</t>
+  </si>
+  <si>
+    <t>Fx dwi raharjani</t>
   </si>
   <si>
     <t>JAKARTA</t>
   </si>
   <si>
-    <t>IIK/NURHIKMAH</t>
+    <t>Iik/nurhikmah</t>
   </si>
   <si>
     <t>SAWANGAN DEPOK</t>
   </si>
   <si>
-    <t>HESTI PUSPANINGRUM</t>
+    <t>Hesti puspaningrum</t>
   </si>
   <si>
     <t>BANDUNG</t>
@@ -1309,7 +1309,7 @@
     <t>Bandung</t>
   </si>
   <si>
-    <t>AGUSTINA SITI RAHAYU</t>
+    <t>Agustina siti rahayu</t>
   </si>
   <si>
     <t>SOLO</t>
@@ -1318,7 +1318,7 @@
     <t>rantikusuma08@gmail.com</t>
   </si>
   <si>
-    <t>Ranti Kusuma</t>
+    <t>Ranti kusuma</t>
   </si>
   <si>
     <t>081229096979</t>
@@ -1342,7 +1342,7 @@
     <t>srinoerlestari@gmail.com</t>
   </si>
   <si>
-    <t>Sri Nur Lestari</t>
+    <t>Sri nur lestari</t>
   </si>
   <si>
     <t>08122964860</t>
@@ -1360,7 +1360,7 @@
     <t>pujimulyati51@gmail.com</t>
   </si>
   <si>
-    <t>Margaretha Puji</t>
+    <t>Margaretha puji</t>
   </si>
   <si>
     <t>085802524684</t>
@@ -1399,7 +1399,7 @@
     <t xml:space="preserve">triamugitama@gmail.com </t>
   </si>
   <si>
-    <t>GAMA TRI UTAMI</t>
+    <t>Gama tri utami</t>
   </si>
   <si>
     <t>081215559464</t>
@@ -1423,7 +1423,7 @@
     <t>tri.nugraha32@yahoo.com</t>
   </si>
   <si>
-    <t>Yenni Toar</t>
+    <t>Yenni toar</t>
   </si>
   <si>
     <t>081392776683</t>
@@ -1453,7 +1453,7 @@
     <t>ekaswatiyusnitaa@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Yusnita Tias Ekaswaati </t>
+    <t xml:space="preserve">Yusnita tias ekaswaati </t>
   </si>
   <si>
     <t>08122789954</t>
@@ -1474,7 +1474,7 @@
     <t>Ziecoll18@gmail.com</t>
   </si>
   <si>
-    <t>Hazizah, S.Sos</t>
+    <t>Hazizah, s.sos</t>
   </si>
   <si>
     <t>082118700063</t>
@@ -1495,7 +1495,7 @@
     <t>Adriani.sutanto@gmail.com</t>
   </si>
   <si>
-    <t>Adriani Sutanto</t>
+    <t>Adriani sutanto</t>
   </si>
   <si>
     <t>08122969480</t>
@@ -1507,13 +1507,13 @@
     <t>Dpt membantu saudara / orang lain dlm mengatasi keluhan2 krn saraf kejepit</t>
   </si>
   <si>
-    <t>DWI LELANDARI</t>
-  </si>
-  <si>
-    <t>SWANDARI RUKMIDANTI</t>
-  </si>
-  <si>
-    <t>ROFIN ROFIANO</t>
+    <t>Dwi lelandari</t>
+  </si>
+  <si>
+    <t>Swandari rukmidanti</t>
+  </si>
+  <si>
+    <t>Rofin rofiano</t>
   </si>
   <si>
     <t>BOGOR</t>
@@ -1522,58 +1522,58 @@
     <t>Bogor</t>
   </si>
   <si>
-    <t>BIANKA MULIAWAN</t>
-  </si>
-  <si>
-    <t>HETTY</t>
-  </si>
-  <si>
-    <t>PETRA ANGGRAENI</t>
+    <t>Bianka muliawan</t>
+  </si>
+  <si>
+    <t>Hetty</t>
+  </si>
+  <si>
+    <t>Petra anggraeni</t>
   </si>
   <si>
     <t>DEPOK</t>
   </si>
   <si>
-    <t>HETI RISMAWATI</t>
-  </si>
-  <si>
-    <t>REINNY WIDYASARI</t>
+    <t>Heti rismawati</t>
+  </si>
+  <si>
+    <t>Reinny widyasari</t>
   </si>
   <si>
     <t>CIKARANG</t>
   </si>
   <si>
-    <t>STEFANIE BASUKI</t>
-  </si>
-  <si>
-    <t>URAY RINI AGUSTINA</t>
-  </si>
-  <si>
-    <t>SUMINARTI</t>
+    <t>Stefanie basuki</t>
+  </si>
+  <si>
+    <t>Uray rini agustina</t>
+  </si>
+  <si>
+    <t>Suminarti</t>
   </si>
   <si>
     <t>TANGERANG</t>
   </si>
   <si>
-    <t>YOSEPH KUSNO</t>
-  </si>
-  <si>
-    <t>TJHIN AI YEN</t>
-  </si>
-  <si>
-    <t>TYAS AYU WIGATI</t>
-  </si>
-  <si>
-    <t>REGINA THANIA HAMIM</t>
-  </si>
-  <si>
-    <t>LASMI ANITA</t>
-  </si>
-  <si>
-    <t>DIAN ISMIAZIS</t>
-  </si>
-  <si>
-    <t>RUBY YANA</t>
+    <t>Yoseph kusno</t>
+  </si>
+  <si>
+    <t>Tjhin ai yen</t>
+  </si>
+  <si>
+    <t>Tyas ayu wigati</t>
+  </si>
+  <si>
+    <t>Regina thania hamim</t>
+  </si>
+  <si>
+    <t>Lasmi anita</t>
+  </si>
+  <si>
+    <t>Dian ismiazis</t>
+  </si>
+  <si>
+    <t>Ruby yana</t>
   </si>
   <si>
     <t>BANDUNG BARAT</t>
@@ -1582,25 +1582,25 @@
     <t>Bandung Barat</t>
   </si>
   <si>
-    <t>YUSTY ARUBADEWI</t>
-  </si>
-  <si>
-    <t>CONNIE VERANICA</t>
-  </si>
-  <si>
-    <t>IGNACIA BENEDICTA M.U</t>
-  </si>
-  <si>
-    <t>ARLAN RIDFAN FARID</t>
-  </si>
-  <si>
-    <t>MERY SUSANTI</t>
-  </si>
-  <si>
-    <t>SYAHIRA AULIA FIRDAUS</t>
-  </si>
-  <si>
-    <t>MARIA EMITANTY</t>
+    <t>Yusty arubadewi</t>
+  </si>
+  <si>
+    <t>Connie veranica</t>
+  </si>
+  <si>
+    <t>Ignacia benedicta m.u</t>
+  </si>
+  <si>
+    <t>Arlan ridfan farid</t>
+  </si>
+  <si>
+    <t>Mery susanti</t>
+  </si>
+  <si>
+    <t>Syahira aulia firdaus</t>
+  </si>
+  <si>
+    <t>Maria emitanty</t>
   </si>
   <si>
     <t>SAMARINDA</t>
@@ -1612,10 +1612,10 @@
     <t>Kalimantan Timur</t>
   </si>
   <si>
-    <t>SARI YAGUSTIARINI</t>
-  </si>
-  <si>
-    <t>NATALIA LIE</t>
+    <t>Sari yagustiarini</t>
+  </si>
+  <si>
+    <t>Natalia lie</t>
   </si>
   <si>
     <t>BEKASI</t>
@@ -1624,7 +1624,7 @@
     <t>widisety@gmail.com</t>
   </si>
   <si>
-    <t>widi setyaningsih</t>
+    <t>Widi setyaningsih</t>
   </si>
   <si>
     <t>6285702609120</t>
@@ -1636,7 +1636,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>tuty kalis purwanti</t>
+    <t>Tuty kalis purwanti</t>
   </si>
   <si>
     <t>6285727085700</t>
@@ -1651,7 +1651,7 @@
     <t>oppoaulia2f@gmail.com</t>
   </si>
   <si>
-    <t>suzana ernawati</t>
+    <t>Suzana ernawati</t>
   </si>
   <si>
     <t>6282133675805</t>
@@ -1672,7 +1672,7 @@
     <t>shelly_imtz@yahoo.com</t>
   </si>
   <si>
-    <t>shelly surjaatmadja</t>
+    <t>Shelly surjaatmadja</t>
   </si>
   <si>
     <t>6282138051919</t>
@@ -1681,7 +1681,7 @@
     <t>Rendiliauw@gmail.com</t>
   </si>
   <si>
-    <t>Rendi Liauw</t>
+    <t>Rendi liauw</t>
   </si>
   <si>
     <t>Jakarta Barat</t>
@@ -1717,7 +1717,7 @@
     <t>saptawidyawatiariewcp@gmail.com</t>
   </si>
   <si>
-    <t>Saptawidyawati Arie WCP</t>
+    <t>Saptawidyawati arie wcp</t>
   </si>
   <si>
     <t>08157013693</t>
@@ -1735,7 +1735,7 @@
     <t>Vita.eridhanny@gmail.com</t>
   </si>
   <si>
-    <t>Vita Pricilla Eridhany Saptenno</t>
+    <t>Vita pricilla eridhany saptenno</t>
   </si>
   <si>
     <t>082124341385</t>
@@ -1768,7 +1768,7 @@
     <t>andifachrahs@gmail.com</t>
   </si>
   <si>
-    <t>Andi Fachrah Savitri</t>
+    <t>Andi fachrah savitri</t>
   </si>
   <si>
     <t>081294770550</t>
@@ -1855,12 +1855,15 @@
     <t>rozikaamalia16@gmail.com</t>
   </si>
   <si>
-    <t>rozika amalia</t>
+    <t>Rozika amalia</t>
   </si>
   <si>
     <t>0811694567</t>
   </si>
   <si>
+    <t>Workshop Terapi Scoliosis</t>
+  </si>
+  <si>
     <t>instruktur pilates freelancer</t>
   </si>
   <si>
@@ -1873,7 +1876,7 @@
     <t>nichlahisnaily@gmail.com</t>
   </si>
   <si>
-    <t>Nichlah Isnaily Baroroh</t>
+    <t>Nichlah isnaily baroroh</t>
   </si>
   <si>
     <t>08170017477</t>
@@ -1897,9 +1900,6 @@
     <t>Workshop Terapi Scoliosis Semarang</t>
   </si>
   <si>
-    <t>Workshop Terapi Scoliosis</t>
-  </si>
-  <si>
     <t>Bisa mengetahui langkah, gerakan yoga yg bisa diterapkan kepada klien</t>
   </si>
   <si>
@@ -1918,13 +1918,13 @@
     <t>Menambah Pengetahuan &amp; Wawasan, Anatomi, Gerak &amp; Postur Tubuh</t>
   </si>
   <si>
-    <t>MONICA BOENTARAN</t>
-  </si>
-  <si>
-    <t>DJULITA JAPRI</t>
-  </si>
-  <si>
-    <t>drh DWI MUTIARA S</t>
+    <t>Monica boentaran</t>
+  </si>
+  <si>
+    <t>Djulita japri</t>
+  </si>
+  <si>
+    <t>Drh dwi mutiara s</t>
   </si>
   <si>
     <t>INDRAMAYU</t>
@@ -1933,16 +1933,16 @@
     <t>Indramayu</t>
   </si>
   <si>
-    <t>INGE WIDIYANTI</t>
-  </si>
-  <si>
-    <t>IVANA ANGEL</t>
-  </si>
-  <si>
-    <t>EVA FITRIA A</t>
-  </si>
-  <si>
-    <t>SYANDRA KWAN</t>
+    <t>Inge widiyanti</t>
+  </si>
+  <si>
+    <t>Ivana angel</t>
+  </si>
+  <si>
+    <t>Eva fitria a</t>
+  </si>
+  <si>
+    <t>Syandra kwan</t>
   </si>
   <si>
     <t>SURABAYA</t>
@@ -1951,10 +1951,10 @@
     <t>Surabaya</t>
   </si>
   <si>
-    <t>KARINA SALIM</t>
-  </si>
-  <si>
-    <t>VITA CIPTA NINGRUM</t>
+    <t>Karina salim</t>
+  </si>
+  <si>
+    <t>Vita cipta ningrum</t>
   </si>
   <si>
     <t>MALANG</t>
@@ -1963,34 +1963,34 @@
     <t>Malang</t>
   </si>
   <si>
-    <t>NINING JUANINGSIH</t>
-  </si>
-  <si>
-    <t>DESTY</t>
-  </si>
-  <si>
-    <t>RINI MARIANA</t>
+    <t>Nining juaningsih</t>
+  </si>
+  <si>
+    <t>Desty</t>
+  </si>
+  <si>
+    <t>Rini mariana</t>
   </si>
   <si>
     <t>rizaninataya@gmail.com</t>
   </si>
   <si>
-    <t>NATAYA CHAROONSRI RIZANI</t>
+    <t>Nataya charoonsri rizani</t>
   </si>
   <si>
     <t>Bisa membantu menangani saraf kejepit</t>
   </si>
   <si>
-    <t>FELICIA JOVITA</t>
+    <t>Felicia jovita</t>
   </si>
   <si>
     <t>TANGSEL</t>
   </si>
   <si>
-    <t>RIKA RATNA JUWITA</t>
-  </si>
-  <si>
-    <t>SEVIA MINDRIYATI</t>
+    <t>Rika ratna juwita</t>
+  </si>
+  <si>
+    <t>Sevia mindriyati</t>
   </si>
   <si>
     <t>SUKABUMI</t>
@@ -2002,7 +2002,7 @@
     <t>anggiamulyani@gmail.com</t>
   </si>
   <si>
-    <t>ANGGIA VIDYANA MULYANI</t>
+    <t>Anggia vidyana mulyani</t>
   </si>
   <si>
     <t>Guru Yoga &amp; Pilates</t>
@@ -2014,16 +2014,16 @@
     <t>Penanganan Cedera &amp; Keluhan, Anatomi, Gerak &amp; Postur Tubuh, Pengembangan Profesi &amp; Berbagi Ilmu</t>
   </si>
   <si>
-    <t>ANNY MARIANI</t>
-  </si>
-  <si>
-    <t>FERIAL GHITA</t>
-  </si>
-  <si>
-    <t>ERVINA</t>
-  </si>
-  <si>
-    <t>WAHYUNI SHINTA KRAMADIBRATA</t>
+    <t>Anny mariani</t>
+  </si>
+  <si>
+    <t>Ferial ghita</t>
+  </si>
+  <si>
+    <t>Ervina</t>
+  </si>
+  <si>
+    <t>Wahyuni shinta kramadibrata</t>
   </si>
   <si>
     <t>airinapriyani8@gmail.com</t>
@@ -2043,7 +2043,7 @@
     <t>melissa.wongkar@gmail.com</t>
   </si>
   <si>
-    <t>Melissa Wongkar</t>
+    <t>Melissa wongkar</t>
   </si>
   <si>
     <t>081938688632</t>
@@ -2055,7 +2055,7 @@
     <t>shizuka36@gmail.com</t>
   </si>
   <si>
-    <t>Dean Hangga Kristian Putra</t>
+    <t>Dean hangga kristian putra</t>
   </si>
   <si>
     <t>081225221959</t>
@@ -2067,7 +2067,7 @@
     <t>Littletania.forher@gmail.com</t>
   </si>
   <si>
-    <t>Tania Hoo</t>
+    <t>Tania hoo</t>
   </si>
   <si>
     <t>0811283600</t>
@@ -2145,7 +2145,7 @@
     <t>nesia_ira@yahoo.com</t>
   </si>
   <si>
-    <t>IRANESIA</t>
+    <t>Iranesia</t>
   </si>
   <si>
     <t>082394734703</t>
@@ -2165,7 +2165,7 @@
     <t>larasatialsdy@gmail.com</t>
   </si>
   <si>
-    <t>Alsa Ayudya Larasati</t>
+    <t>Alsa ayudya larasati</t>
   </si>
   <si>
     <t>087734238958</t>
@@ -2192,7 +2192,7 @@
     <t>irenesiauw84@gmail.com</t>
   </si>
   <si>
-    <t>Irene Kartika Sari</t>
+    <t>Irene kartika sari</t>
   </si>
   <si>
     <t>082138754144</t>
@@ -2210,7 +2210,7 @@
     <t>melisanatalia88@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">MELISA NATALIA </t>
+    <t xml:space="preserve">Melisa natalia </t>
   </si>
   <si>
     <t>087838432411</t>
@@ -2231,7 +2231,7 @@
     <t>andropromosi@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Aryo Wicaksono </t>
+    <t xml:space="preserve">Aryo wicaksono </t>
   </si>
   <si>
     <t>082221118845</t>
@@ -2252,7 +2252,7 @@
     <t>fatwaninurul@gmail.com</t>
   </si>
   <si>
-    <t>Nurul Fatwani</t>
+    <t>Nurul fatwani</t>
   </si>
   <si>
     <t>082116610764</t>
@@ -2291,7 +2291,7 @@
     <t>Iinoctaviaa@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">IIN OCTAVIA </t>
+    <t xml:space="preserve">Iin octavia </t>
   </si>
   <si>
     <t>081339891959</t>
@@ -2336,7 +2336,7 @@
     <t>gemahosana@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Santoso Hartono </t>
+    <t xml:space="preserve">Santoso hartono </t>
   </si>
   <si>
     <t>081215458600</t>
@@ -2351,7 +2351,7 @@
     <t>cielvandezz@gmail.com</t>
   </si>
   <si>
-    <t>Sandys Silfana</t>
+    <t>Sandys silfana</t>
   </si>
   <si>
     <t>081246098947</t>
@@ -2375,7 +2375,7 @@
     <t>nok.diana@gmail.com</t>
   </si>
   <si>
-    <t>DIANA KRISTINA</t>
+    <t>Diana kristina</t>
   </si>
   <si>
     <t>081229194313</t>
@@ -2390,7 +2390,7 @@
     <t>Ruthaurelia38@gmail.com</t>
   </si>
   <si>
-    <t>Ruth Aurelia</t>
+    <t>Ruth aurelia</t>
   </si>
   <si>
     <t>082211878732</t>
@@ -2402,22 +2402,22 @@
     <t>Memahami skolio dan solusinya.</t>
   </si>
   <si>
-    <t>ADAM ABDULLAH B</t>
-  </si>
-  <si>
-    <t>DEWI INTAN PERTIWI</t>
-  </si>
-  <si>
-    <t>TIWI NOERHAYATI</t>
-  </si>
-  <si>
-    <t>AUDREY HARNOV</t>
+    <t>Adam abdullah b</t>
+  </si>
+  <si>
+    <t>Dewi intan pertiwi</t>
+  </si>
+  <si>
+    <t>Tiwi noerhayati</t>
+  </si>
+  <si>
+    <t>Audrey harnov</t>
   </si>
   <si>
     <t>Susanharnov@gmail.com</t>
   </si>
   <si>
-    <t>SUSAN NOVITA</t>
+    <t>Susan novita</t>
   </si>
   <si>
     <t>Teacher yoga</t>
@@ -2426,19 +2426,19 @@
     <t>Menambah skill dan movitaai</t>
   </si>
   <si>
-    <t>DEWI SEPTRINA</t>
-  </si>
-  <si>
-    <t>YUNIATI EUNIKE</t>
-  </si>
-  <si>
-    <t>INDHI LATIF HANIK</t>
+    <t>Dewi septrina</t>
+  </si>
+  <si>
+    <t>Yuniati eunike</t>
+  </si>
+  <si>
+    <t>Indhi latif hanik</t>
   </si>
   <si>
     <t>nsulistyoasih@gmail.com</t>
   </si>
   <si>
-    <t>NANING SULISTYOASIH</t>
+    <t>Naning sulistyoasih</t>
   </si>
   <si>
     <t>081231705744</t>
@@ -2462,7 +2462,7 @@
     <t>casiahaan15@gmail.com</t>
   </si>
   <si>
-    <t>christie angelika siahaan</t>
+    <t>Christie angelika siahaan</t>
   </si>
   <si>
     <t>087853136434</t>
@@ -2486,7 +2486,7 @@
     <t>ratnasulistyowati71@gmail.com</t>
   </si>
   <si>
-    <t>Ratna Sulistyowati</t>
+    <t>Ratna sulistyowati</t>
   </si>
   <si>
     <t>085606910531</t>
@@ -2505,7 +2505,7 @@
     <t>evelyne_tj.yi@yahoo.com</t>
   </si>
   <si>
-    <t>Evelyne Tjendrawan</t>
+    <t>Evelyne tjendrawan</t>
   </si>
   <si>
     <t>081808395335</t>
@@ -2538,7 +2538,7 @@
     <t>ummukda2020@gmail.com</t>
   </si>
   <si>
-    <t>Arinda A Widayu</t>
+    <t>Arinda a widayu</t>
   </si>
   <si>
     <t>085840839451</t>
@@ -2559,7 +2559,7 @@
     <t>nursiyahdewi4@gmail.com</t>
   </si>
   <si>
-    <t>Dewi Nursiyah</t>
+    <t>Dewi nursiyah</t>
   </si>
   <si>
     <t>081703700789</t>
@@ -2574,7 +2574,7 @@
     <t>shizuka.iphone04@gmail.com</t>
   </si>
   <si>
-    <t>Tri Puji Pangesti</t>
+    <t>Tri puji pangesti</t>
   </si>
   <si>
     <t>081391969169</t>
@@ -2592,7 +2592,7 @@
     <t>ibnucaturmustofa@gmail.com</t>
   </si>
   <si>
-    <t>Ibnu Catur Mustofa</t>
+    <t>Ibnu catur mustofa</t>
   </si>
   <si>
     <t>081359056553</t>
@@ -2613,7 +2613,7 @@
     <t>camelliaa.blooms@gmail.com</t>
   </si>
   <si>
-    <t>Lia Eunike</t>
+    <t>Lia eunike</t>
   </si>
   <si>
     <t>089678836018</t>
@@ -2649,7 +2649,7 @@
     <t>chiaratiara@gmail.com</t>
   </si>
   <si>
-    <t>tiara widjaja</t>
+    <t>Tiara widjaja</t>
   </si>
   <si>
     <t>081335321388</t>
@@ -2667,7 +2667,7 @@
     <t>pussphit81@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Anggia Puspita Dewi </t>
+    <t xml:space="preserve">Anggia puspita dewi </t>
   </si>
   <si>
     <t>085186815545</t>
@@ -2685,7 +2685,7 @@
     <t>dianv046@gmail.com</t>
   </si>
   <si>
-    <t>Valentina Dian Indriani</t>
+    <t>Valentina dian indriani</t>
   </si>
   <si>
     <t>085784144000</t>
@@ -2739,7 +2739,7 @@
     <t>Emma.property19@gmail.com</t>
   </si>
   <si>
-    <t>Aurell Nabila</t>
+    <t>Aurell nabila</t>
   </si>
   <si>
     <t>081232714586</t>
@@ -2763,7 +2763,7 @@
     <t>enysulistyowati@unesa.ac.id</t>
   </si>
   <si>
-    <t>Eny Sulistyowati</t>
+    <t>Eny sulistyowati</t>
   </si>
   <si>
     <t>08121786850</t>
@@ -2787,7 +2787,7 @@
     <t>Juliasudjana@gmail.com</t>
   </si>
   <si>
-    <t>Julia Sudjana</t>
+    <t>Julia sudjana</t>
   </si>
   <si>
     <t>08121997673</t>
@@ -2805,7 +2805,7 @@
     <t>febrianti.nila@gmail.com</t>
   </si>
   <si>
-    <t>Ni Made Nila Febrianti</t>
+    <t>Ni made nila febrianti</t>
   </si>
   <si>
     <t>085339880567</t>
@@ -2826,7 +2826,7 @@
     <t>indiramaheswari3008@gmail.com</t>
   </si>
   <si>
-    <t>Indira Maheswari</t>
+    <t>Indira maheswari</t>
   </si>
   <si>
     <t>081339670102</t>
@@ -2844,7 +2844,7 @@
     <t>putualit@ymail.com</t>
   </si>
   <si>
-    <t>Putu Erlambang</t>
+    <t>Putu erlambang</t>
   </si>
   <si>
     <t>087860747437</t>
@@ -2859,7 +2859,7 @@
     <t>agusssuwiddnyana@gmail.com</t>
   </si>
   <si>
-    <t>I Putu Agus Suwidnyana</t>
+    <t>I putu agus suwidnyana</t>
   </si>
   <si>
     <t>081239172976</t>
@@ -2886,7 +2886,7 @@
     <t>Laudza.ug@gmail.com</t>
   </si>
   <si>
-    <t>Laudza Ulayya Ghani</t>
+    <t>Laudza ulayya ghani</t>
   </si>
   <si>
     <t>085161608097</t>
@@ -2907,7 +2907,7 @@
     <t>brindilrandd@gmail.com</t>
   </si>
   <si>
-    <t>Maria Setiya Rini</t>
+    <t>Maria setiya rini</t>
   </si>
   <si>
     <t>082266484836</t>
@@ -2919,7 +2919,7 @@
     <t>luhyoani@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">NI Luh gede Yowani </t>
+    <t xml:space="preserve">Ni luh gede yowani </t>
   </si>
   <si>
     <t>081338736218</t>
@@ -2934,7 +2934,7 @@
     <t>idad612@gmail.com</t>
   </si>
   <si>
-    <t>Ida Trini</t>
+    <t>Ida trini</t>
   </si>
   <si>
     <t>Badung, Bali</t>
@@ -2952,7 +2952,7 @@
     <t xml:space="preserve">Inggridtawika80@gmail.com </t>
   </si>
   <si>
-    <t xml:space="preserve">Inggrid Tawika </t>
+    <t xml:space="preserve">Inggrid tawika </t>
   </si>
   <si>
     <t>081558001829</t>
@@ -2967,7 +2967,7 @@
     <t>nanachankd@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Luh putu Krisna Darmayanti </t>
+    <t xml:space="preserve">Luh putu krisna darmayanti </t>
   </si>
   <si>
     <t>08970192599</t>
@@ -2982,7 +2982,7 @@
     <t>damayanti.herni28@gmail.com</t>
   </si>
   <si>
-    <t>Herni Damayanti</t>
+    <t>Herni damayanti</t>
   </si>
   <si>
     <t>08172832137</t>
@@ -3000,7 +3000,7 @@
     <t>mirabalgis94@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Amirah Balgis </t>
+    <t xml:space="preserve">Amirah balgis </t>
   </si>
   <si>
     <t>081138212228</t>
@@ -3027,7 +3027,7 @@
     <t>marianisuwirya82@gmail.com</t>
   </si>
   <si>
-    <t>Mariani Suwirya</t>
+    <t>Mariani suwirya</t>
   </si>
   <si>
     <t>081310133456</t>
@@ -3054,7 +3054,7 @@
     <t>septadian21c@gmail.com</t>
   </si>
   <si>
-    <t>Septa Dian Pertiwi</t>
+    <t>Septa dian pertiwi</t>
   </si>
   <si>
     <t>08118751443</t>
@@ -3072,7 +3072,7 @@
     <t>dianniko821@gmail.com</t>
   </si>
   <si>
-    <t>Ni Komang ayu Diantari</t>
+    <t>Ni komang ayu diantari</t>
   </si>
   <si>
     <t>087857173251</t>
@@ -3090,7 +3090,7 @@
     <t>ennyrosidaa@gmail.com</t>
   </si>
   <si>
-    <t>Enny Rosida</t>
+    <t>Enny rosida</t>
   </si>
   <si>
     <t>081290172229</t>
@@ -3129,7 +3129,7 @@
     <t>lestari.telpro@gmail.com</t>
   </si>
   <si>
-    <t>Yanti Lestari</t>
+    <t>Yanti lestari</t>
   </si>
   <si>
     <t>0811656464</t>
@@ -3138,7 +3138,7 @@
     <t>liu.sherly@gmail.com</t>
   </si>
   <si>
-    <t>Sherly Liu</t>
+    <t>Sherly liu</t>
   </si>
   <si>
     <t>082260888093</t>
@@ -3147,7 +3147,7 @@
     <t>stefieandjeanne@gmail.com</t>
   </si>
   <si>
-    <t>Stefie Himawan</t>
+    <t>Stefie himawan</t>
   </si>
   <si>
     <t>085693082212</t>
@@ -3177,7 +3177,7 @@
     <t>gtjokinin@gmail.com</t>
   </si>
   <si>
-    <t>Grace Tjokinin</t>
+    <t>Grace tjokinin</t>
   </si>
   <si>
     <t>08128981989</t>
@@ -3189,7 +3189,7 @@
     <t>indah.chitchat@gmail.com</t>
   </si>
   <si>
-    <t>Indah Prameswari W</t>
+    <t>Indah prameswari w</t>
   </si>
   <si>
     <t>0811109594</t>
@@ -3201,7 +3201,7 @@
     <t>charmelyioda@yahoo.com</t>
   </si>
   <si>
-    <t>Charmel Yioda</t>
+    <t>Charmel yioda</t>
   </si>
   <si>
     <t>081384123334</t>
@@ -3225,7 +3225,7 @@
     <t>ariyatinurlitasari@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Ariyati Nurlitasari </t>
+    <t xml:space="preserve">Ariyati nurlitasari </t>
   </si>
   <si>
     <t>085650952455</t>
@@ -3240,7 +3240,7 @@
     <t>sherlypryahana@gmail.com</t>
   </si>
   <si>
-    <t>Sherly Pryahana</t>
+    <t>Sherly pryahana</t>
   </si>
   <si>
     <t>085775357130</t>
@@ -3261,7 +3261,7 @@
     <t>oktavia.yesi2014@gmail.com</t>
   </si>
   <si>
-    <t>Yesi Oktavia</t>
+    <t>Yesi oktavia</t>
   </si>
   <si>
     <t>081289107833</t>
@@ -3273,7 +3273,7 @@
     <t>monalisa.sandi.ramamosa@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Monalisa Sakarias </t>
+    <t xml:space="preserve">Monalisa sakarias </t>
   </si>
   <si>
     <t>08117408398</t>
@@ -3285,7 +3285,7 @@
     <t>uliekurniawan1@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Siti Julaiha </t>
+    <t xml:space="preserve">Siti julaiha </t>
   </si>
   <si>
     <t>0895360333097</t>
@@ -3345,7 +3345,7 @@
     <t>kdewid33@gmail.com</t>
   </si>
   <si>
-    <t>Dewi Komalasari</t>
+    <t>Dewi komalasari</t>
   </si>
   <si>
     <t>+6281311335848</t>
@@ -3369,7 +3369,7 @@
     <t>arie.w738@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Prihati Wulandari </t>
+    <t xml:space="preserve">Prihati wulandari </t>
   </si>
   <si>
     <t>08128414134</t>
@@ -3381,7 +3381,7 @@
     <t>reginariva2013@gmail.com</t>
   </si>
   <si>
-    <t>Regina Riva</t>
+    <t>Regina riva</t>
   </si>
   <si>
     <t>08111332619</t>
@@ -3408,7 +3408,7 @@
     <t>chandrawatiwidya@gmail.com</t>
   </si>
   <si>
-    <t>Chandrawati Widya</t>
+    <t>Chandrawati widya</t>
   </si>
   <si>
     <t>Workshop Metabolic</t>
@@ -3426,7 +3426,7 @@
     <t>nanix.mulyani@gmail.com</t>
   </si>
   <si>
-    <t>Nanik Mulyani</t>
+    <t>Nanik mulyani</t>
   </si>
   <si>
     <t>Akuntan</t>
@@ -3462,7 +3462,7 @@
     <t>bistiannaarthagia@gmail.com</t>
   </si>
   <si>
-    <t>Bistianna Arthagia</t>
+    <t>Bistianna arthagia</t>
   </si>
   <si>
     <t>6281338510445</t>
@@ -3495,7 +3495,7 @@
     <t>eldewi2014@gmail.com</t>
   </si>
   <si>
-    <t>Emmy Liana Dewi</t>
+    <t>Emmy liana dewi</t>
   </si>
   <si>
     <t>66+</t>
@@ -3541,6 +3541,111 @@
   </si>
   <si>
     <t>Angka yg tinggi</t>
+  </si>
+  <si>
+    <t>manajemenup@gmail.com</t>
+  </si>
+  <si>
+    <t>Rahman arief dewantara</t>
+  </si>
+  <si>
+    <t>yogyakarta</t>
+  </si>
+  <si>
+    <t>Workshop Metabolic Semarang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">direktur </t>
+  </si>
+  <si>
+    <t>saya memiliki produk yg bisa membantu penderita diabetes, di workshop iini saya ingin upgrade ilmu</t>
+  </si>
+  <si>
+    <t>dianayp29@gmail.com</t>
+  </si>
+  <si>
+    <t>Diana yulis priyati</t>
+  </si>
+  <si>
+    <t>eviidaputri@gmail.com</t>
+  </si>
+  <si>
+    <t>Evi ida purwani</t>
+  </si>
+  <si>
+    <t>Perum. Mayangan Baru no 42.Rt 21/Rw07.kecamatan Wiradesa, kab. Pekalongan</t>
+  </si>
+  <si>
+    <t>hanee0507@gmail.com</t>
+  </si>
+  <si>
+    <t>Rakhma nugrahani</t>
+  </si>
+  <si>
+    <t>Kebumen</t>
+  </si>
+  <si>
+    <t>Yoga practitioner</t>
+  </si>
+  <si>
+    <t>Erna puji errawati</t>
+  </si>
+  <si>
+    <t>Coach yoga</t>
+  </si>
+  <si>
+    <t>Nisfah elfulaila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">George santoso </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leader personal trainer </t>
+  </si>
+  <si>
+    <t>Workshop Metabolic Jakarta</t>
+  </si>
+  <si>
+    <t>Penyakit Metabolik; Kolestrol tinggi</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Puji</t>
+  </si>
+  <si>
+    <t>Prihati wulandari</t>
+  </si>
+  <si>
+    <t>Hypnotherapist, Posture Improvement Therapist &amp; Hydrotherapist</t>
+  </si>
+  <si>
+    <t>Penyakit Metabolik; Hipertensi dan Kolesterol</t>
+  </si>
+  <si>
+    <t>Jatibening Bekasi</t>
+  </si>
+  <si>
+    <t>ratnatika31@gmail.com</t>
+  </si>
+  <si>
+    <t>Ratna tika sari</t>
+  </si>
+  <si>
+    <t>Pontianak</t>
+  </si>
+  <si>
+    <t>Kalimantan Barat</t>
+  </si>
+  <si>
+    <t>Guru yoga .pilates.barre</t>
+  </si>
+  <si>
+    <t>jepara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">menambah ilmu untuk bisa berbagi dengan para member yoga yang memiliki keluhan tentang syaraf kejepit. </t>
   </si>
 </sst>
 </file>
@@ -3548,7 +3653,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -3599,7 +3704,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -3637,7 +3742,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+      <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -3667,34 +3772,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F38F7656-86CA-4821-ADA1-5488F5CEC9A1}" name="Table1" displayName="Table1" ref="A1:Y314" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="2" tableBorderDxfId="3">
-  <autoFilter ref="A1:Y314" xr:uid="{F38F7656-86CA-4821-ADA1-5488F5CEC9A1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1FEC11E-D3BA-4A29-8078-C55E67B1880B}" name="Table1" displayName="Table1" ref="A1:Y329" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="2" tableBorderDxfId="3">
+  <autoFilter ref="A1:Y329" xr:uid="{B1FEC11E-D3BA-4A29-8078-C55E67B1880B}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Workshop Metabolic"/>
+        <filter val="Workshop Metabolic Semarang"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{039698E2-019D-4AFA-8ACB-10939541A822}" name="Email"/>
-    <tableColumn id="2" xr3:uid="{F0B53F50-E27A-4C90-AA9D-A84B1E0DB011}" name="Nama"/>
-    <tableColumn id="3" xr3:uid="{A8718DD6-247B-4B12-B9ED-02413F488A3F}" name="No WhatsApp"/>
-    <tableColumn id="4" xr3:uid="{002BD4EC-270A-41BE-89D6-EEC30CD8EBBE}" name="Kota - Provinsi"/>
-    <tableColumn id="5" xr3:uid="{9AF223A0-30B9-412E-BD34-0749345E1DC5}" name="Tempat Kegiatan"/>
-    <tableColumn id="6" xr3:uid="{B965C319-E859-4E80-ADCE-D9D868EE3DF4}" name="Tanggal" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{0764D467-1E41-4062-8E3F-57ABBC25DEFF}" name="Sesi"/>
-    <tableColumn id="8" xr3:uid="{48B11DBE-00E1-4C18-9924-E853A00EE4EE}" name="Jumlah Sesi"/>
-    <tableColumn id="9" xr3:uid="{2036A2E3-9C96-4DF7-B233-DE478FEFB31C}" name="Tahun"/>
-    <tableColumn id="10" xr3:uid="{4011E0EC-0619-4904-BD0B-1F81E701860D}" name="Bulan"/>
-    <tableColumn id="11" xr3:uid="{CF821166-36F2-4E60-935C-7243AF8FFB7A}" name="Kategori"/>
-    <tableColumn id="12" xr3:uid="{3E8AAF3D-314E-4163-80BE-4B8128C65FBC}" name="Nama Event"/>
-    <tableColumn id="13" xr3:uid="{421CFBC9-4A8C-457C-8A2E-48541C4D2F52}" name="Lokasi Event"/>
-    <tableColumn id="14" xr3:uid="{7D76B757-FD8E-492E-8808-D6DD7A2F4960}" name="Gender"/>
-    <tableColumn id="15" xr3:uid="{82C967A4-9796-44F3-9C18-48AB06C138CC}" name="Kota"/>
-    <tableColumn id="16" xr3:uid="{7B5DD4E8-61EB-443E-9AA5-CE3C5C9DD53D}" name="Provinsi"/>
-    <tableColumn id="17" xr3:uid="{4771CA65-6E51-4436-802D-284D20111AE7}" name="Usia"/>
-    <tableColumn id="18" xr3:uid="{2B7692F7-6692-4662-B210-8342ACB84741}" name="Kelompok Usia"/>
-    <tableColumn id="19" xr3:uid="{3EBFD3FE-8AA6-4F32-B6BC-D5CA2B1141FB}" name="Profesi (Asli)"/>
-    <tableColumn id="20" xr3:uid="{1D3B455E-FDC7-45A5-9B0B-89232ABBA013}" name="Kategori Profesi"/>
-    <tableColumn id="21" xr3:uid="{90BA8C37-E4C3-4FD0-813B-7AA8C7023455}" name="Harapan (Asli)"/>
-    <tableColumn id="22" xr3:uid="{02FA6104-8D44-4757-8BB5-203B4AED2B4D}" name="Topik Harapan"/>
-    <tableColumn id="23" xr3:uid="{41A5D24A-2F9C-43B9-9DCE-26AA34BBD6B4}" name="Keluhan (Asli)"/>
-    <tableColumn id="24" xr3:uid="{1D70B43B-886D-4226-B4BB-0D2D55DC4290}" name="Topik Keluhan"/>
-    <tableColumn id="25" xr3:uid="{6E684841-431B-4E90-BFE4-93684C9B6CFF}" name="Wilayah"/>
+    <tableColumn id="1" xr3:uid="{EA585163-F1F2-4F30-8ED1-A555BC239611}" name="Email"/>
+    <tableColumn id="2" xr3:uid="{DCC1A6A3-5827-4923-8AF7-ABEE0C6FD304}" name="Nama"/>
+    <tableColumn id="3" xr3:uid="{63061C45-E91E-4C23-8076-E25A30A1B3DC}" name="No WhatsApp"/>
+    <tableColumn id="4" xr3:uid="{324AD86D-A8D4-48E1-B73A-C29695BAD991}" name="Kota - Provinsi"/>
+    <tableColumn id="5" xr3:uid="{D3606A7C-C97B-4E9D-9B6C-32331A1E2745}" name="Tempat Kegiatan"/>
+    <tableColumn id="6" xr3:uid="{F35F162C-92F2-4C07-8447-70AD9B2ABB10}" name="Tanggal" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{C4DA2298-94F2-46E3-B723-2E4EAD3178B0}" name="Sesi"/>
+    <tableColumn id="8" xr3:uid="{E0083422-FF72-44A1-BB4D-263B051D6DE4}" name="Jumlah Sesi"/>
+    <tableColumn id="9" xr3:uid="{D1FF56DF-DE65-489A-9637-2D66DA05A2B8}" name="Tahun"/>
+    <tableColumn id="10" xr3:uid="{16A034B9-7F3C-4251-B217-44540F82EA28}" name="Bulan"/>
+    <tableColumn id="11" xr3:uid="{CDA81616-C5A7-4BAC-997F-F3E23458AA82}" name="Kategori"/>
+    <tableColumn id="12" xr3:uid="{045B83C6-CAF2-4E1B-92DA-5A7AA1AED3BC}" name="Nama Event"/>
+    <tableColumn id="13" xr3:uid="{E35F261D-D27A-43C0-9470-4A103C9B8A1C}" name="Lokasi Event"/>
+    <tableColumn id="14" xr3:uid="{597F6C76-0264-401D-A937-252E5FC9B2B6}" name="Gender"/>
+    <tableColumn id="15" xr3:uid="{17D348B4-ED85-4BBB-AA36-227EE774FA11}" name="Kota"/>
+    <tableColumn id="16" xr3:uid="{F42C8CB8-EFB4-4B40-AA46-D557C01B485C}" name="Provinsi"/>
+    <tableColumn id="17" xr3:uid="{B2432FC2-625A-4F94-8856-4C353E31D4E6}" name="Usia"/>
+    <tableColumn id="18" xr3:uid="{73440C77-A6BF-455B-A373-07E0B5A687E3}" name="Kelompok Usia"/>
+    <tableColumn id="19" xr3:uid="{2603988A-AECA-43DE-AB70-449A4BE98D45}" name="Profesi (Asli)"/>
+    <tableColumn id="20" xr3:uid="{9AB07D52-89FC-4C4A-A5EF-038391BBD7DF}" name="Kategori Profesi"/>
+    <tableColumn id="21" xr3:uid="{C9AC3470-275C-4CDC-8806-A9C2EC28A0FD}" name="Harapan (Asli)"/>
+    <tableColumn id="22" xr3:uid="{D8EAA4D7-0E36-4ACE-BB29-29E9DF6E653E}" name="Topik Harapan"/>
+    <tableColumn id="23" xr3:uid="{AA8E2D21-6847-4E1A-ADE6-054E407D45CE}" name="Keluhan (Asli)"/>
+    <tableColumn id="24" xr3:uid="{B4903E4C-909D-459A-A5BD-894DA3ED7E42}" name="Topik Keluhan"/>
+    <tableColumn id="25" xr3:uid="{BCA29B92-B444-43CB-B676-79C6462435F3}" name="Wilayah"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3985,13 +4097,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y314"/>
+  <dimension ref="A1:Y329"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="14.453125" customWidth="1"/>
     <col min="4" max="4" width="14.90625" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.36328125" customWidth="1"/>
     <col min="11" max="11" width="9.81640625" customWidth="1"/>
     <col min="12" max="12" width="12.90625" customWidth="1"/>
@@ -4085,7 +4198,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -4138,7 +4251,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -4191,7 +4304,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -4244,7 +4357,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -4297,7 +4410,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -4350,7 +4463,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -4403,7 +4516,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -4456,7 +4569,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -4509,7 +4622,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>59</v>
       </c>
@@ -4562,7 +4675,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -4615,7 +4728,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -4668,7 +4781,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>68</v>
       </c>
@@ -4721,7 +4834,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>71</v>
       </c>
@@ -4774,7 +4887,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -4827,7 +4940,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -4880,7 +4993,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>85</v>
       </c>
@@ -4933,7 +5046,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -4986,7 +5099,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>91</v>
       </c>
@@ -5039,7 +5152,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>94</v>
       </c>
@@ -5092,7 +5205,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>101</v>
       </c>
@@ -5157,7 +5270,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>109</v>
       </c>
@@ -5210,7 +5323,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>114</v>
       </c>
@@ -5263,7 +5376,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -5316,7 +5429,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>120</v>
       </c>
@@ -5369,7 +5482,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>123</v>
       </c>
@@ -5422,7 +5535,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>126</v>
       </c>
@@ -5475,7 +5588,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>131</v>
       </c>
@@ -5528,7 +5641,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>134</v>
       </c>
@@ -5581,7 +5694,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>137</v>
       </c>
@@ -5634,7 +5747,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>140</v>
       </c>
@@ -5687,7 +5800,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>143</v>
       </c>
@@ -5740,7 +5853,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>146</v>
       </c>
@@ -5793,7 +5906,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>149</v>
       </c>
@@ -5846,7 +5959,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>152</v>
       </c>
@@ -5899,7 +6012,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>157</v>
       </c>
@@ -5952,7 +6065,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>160</v>
       </c>
@@ -6005,7 +6118,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>163</v>
       </c>
@@ -6058,7 +6171,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>168</v>
       </c>
@@ -6111,7 +6224,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>171</v>
       </c>
@@ -6164,7 +6277,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>176</v>
       </c>
@@ -6217,7 +6330,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>179</v>
       </c>
@@ -6270,7 +6383,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>182</v>
       </c>
@@ -6323,7 +6436,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>185</v>
       </c>
@@ -6376,7 +6489,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>188</v>
       </c>
@@ -6429,7 +6542,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>191</v>
       </c>
@@ -6482,7 +6595,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>196</v>
       </c>
@@ -6535,7 +6648,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>203</v>
       </c>
@@ -6588,7 +6701,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>208</v>
       </c>
@@ -6641,7 +6754,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>213</v>
       </c>
@@ -6694,7 +6807,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>216</v>
       </c>
@@ -6747,7 +6860,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>221</v>
       </c>
@@ -6800,7 +6913,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>224</v>
       </c>
@@ -6853,7 +6966,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>227</v>
       </c>
@@ -6906,7 +7019,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>230</v>
       </c>
@@ -6959,7 +7072,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>233</v>
       </c>
@@ -7012,7 +7125,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>236</v>
       </c>
@@ -7065,7 +7178,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>239</v>
       </c>
@@ -7118,7 +7231,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>242</v>
       </c>
@@ -7171,7 +7284,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>245</v>
       </c>
@@ -7224,7 +7337,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>245</v>
       </c>
@@ -7277,7 +7390,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>253</v>
       </c>
@@ -7330,7 +7443,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>259</v>
       </c>
@@ -7383,7 +7496,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>259</v>
       </c>
@@ -7436,7 +7549,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>263</v>
       </c>
@@ -7489,7 +7602,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>266</v>
       </c>
@@ -7542,7 +7655,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>269</v>
       </c>
@@ -7595,7 +7708,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>272</v>
       </c>
@@ -7648,7 +7761,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>275</v>
       </c>
@@ -7701,7 +7814,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>278</v>
       </c>
@@ -7754,7 +7867,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>281</v>
       </c>
@@ -7807,7 +7920,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>284</v>
       </c>
@@ -7860,7 +7973,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>287</v>
       </c>
@@ -7913,7 +8026,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>290</v>
       </c>
@@ -7966,7 +8079,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>293</v>
       </c>
@@ -8019,7 +8132,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>298</v>
       </c>
@@ -8072,7 +8185,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>301</v>
       </c>
@@ -8125,7 +8238,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>306</v>
       </c>
@@ -8178,7 +8291,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>309</v>
       </c>
@@ -8231,7 +8344,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>312</v>
       </c>
@@ -8284,7 +8397,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>312</v>
       </c>
@@ -8337,7 +8450,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>315</v>
       </c>
@@ -8390,7 +8503,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>318</v>
       </c>
@@ -8443,7 +8556,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>321</v>
       </c>
@@ -8496,7 +8609,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>324</v>
       </c>
@@ -8549,7 +8662,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>327</v>
       </c>
@@ -8614,7 +8727,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>327</v>
       </c>
@@ -8679,7 +8792,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>327</v>
       </c>
@@ -8753,7 +8866,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>336</v>
       </c>
@@ -8818,7 +8931,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>336</v>
       </c>
@@ -8892,7 +9005,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>341</v>
       </c>
@@ -8966,7 +9079,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>352</v>
       </c>
@@ -9040,7 +9153,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>360</v>
       </c>
@@ -9105,7 +9218,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>360</v>
       </c>
@@ -9179,7 +9292,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>366</v>
       </c>
@@ -9253,7 +9366,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>373</v>
       </c>
@@ -9327,7 +9440,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>379</v>
       </c>
@@ -9392,7 +9505,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>379</v>
       </c>
@@ -9466,7 +9579,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>384</v>
       </c>
@@ -9540,7 +9653,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>392</v>
       </c>
@@ -9605,7 +9718,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>392</v>
       </c>
@@ -9679,7 +9792,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>399</v>
       </c>
@@ -9732,7 +9845,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>406</v>
       </c>
@@ -9785,7 +9898,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>411</v>
       </c>
@@ -9838,7 +9951,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
         <v>416</v>
       </c>
@@ -9888,7 +10001,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
         <v>421</v>
       </c>
@@ -9938,7 +10051,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
         <v>422</v>
       </c>
@@ -9988,7 +10101,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
         <v>424</v>
       </c>
@@ -10038,7 +10151,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
         <v>426</v>
       </c>
@@ -10088,7 +10201,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
         <v>429</v>
       </c>
@@ -10138,7 +10251,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>431</v>
       </c>
@@ -10212,7 +10325,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>439</v>
       </c>
@@ -10286,7 +10399,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>445</v>
       </c>
@@ -10360,7 +10473,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>452</v>
       </c>
@@ -10434,7 +10547,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>458</v>
       </c>
@@ -10508,7 +10621,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>466</v>
       </c>
@@ -10573,7 +10686,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>466</v>
       </c>
@@ -10638,7 +10751,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>466</v>
       </c>
@@ -10712,7 +10825,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>476</v>
       </c>
@@ -10786,7 +10899,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>483</v>
       </c>
@@ -10860,7 +10973,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>490</v>
       </c>
@@ -10934,7 +11047,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
         <v>495</v>
       </c>
@@ -10984,7 +11097,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
         <v>496</v>
       </c>
@@ -11034,7 +11147,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
         <v>497</v>
       </c>
@@ -11084,7 +11197,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
         <v>500</v>
       </c>
@@ -11134,7 +11247,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
         <v>501</v>
       </c>
@@ -11184,7 +11297,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
         <v>502</v>
       </c>
@@ -11234,7 +11347,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
         <v>504</v>
       </c>
@@ -11284,7 +11397,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="129" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
         <v>505</v>
       </c>
@@ -11334,7 +11447,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="130" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
         <v>507</v>
       </c>
@@ -11384,7 +11497,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="131" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
         <v>508</v>
       </c>
@@ -11434,7 +11547,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="132" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
         <v>509</v>
       </c>
@@ -11484,7 +11597,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="133" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
         <v>511</v>
       </c>
@@ -11534,7 +11647,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="134" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
         <v>512</v>
       </c>
@@ -11584,7 +11697,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="135" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B135" t="s">
         <v>513</v>
       </c>
@@ -11634,7 +11747,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="136" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
         <v>514</v>
       </c>
@@ -11684,7 +11797,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="137" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
         <v>515</v>
       </c>
@@ -11734,7 +11847,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="138" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
         <v>516</v>
       </c>
@@ -11784,7 +11897,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="139" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B139" t="s">
         <v>517</v>
       </c>
@@ -11834,7 +11947,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="140" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B140" t="s">
         <v>520</v>
       </c>
@@ -11884,7 +11997,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="141" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
         <v>521</v>
       </c>
@@ -11934,7 +12047,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="142" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
         <v>522</v>
       </c>
@@ -11984,7 +12097,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="143" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
         <v>523</v>
       </c>
@@ -12034,7 +12147,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="144" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B144" t="s">
         <v>524</v>
       </c>
@@ -12084,7 +12197,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
         <v>525</v>
       </c>
@@ -12134,7 +12247,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B146" t="s">
         <v>526</v>
       </c>
@@ -12184,7 +12297,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B147" t="s">
         <v>530</v>
       </c>
@@ -12234,7 +12347,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B148" t="s">
         <v>531</v>
       </c>
@@ -12284,7 +12397,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>533</v>
       </c>
@@ -12337,7 +12450,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>533</v>
       </c>
@@ -12390,7 +12503,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>537</v>
       </c>
@@ -12455,7 +12568,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>537</v>
       </c>
@@ -12520,7 +12633,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>537</v>
       </c>
@@ -12594,7 +12707,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>542</v>
       </c>
@@ -12656,7 +12769,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>542</v>
       </c>
@@ -12718,7 +12831,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>542</v>
       </c>
@@ -12780,7 +12893,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>542</v>
       </c>
@@ -12851,7 +12964,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>549</v>
       </c>
@@ -12904,7 +13017,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>552</v>
       </c>
@@ -12969,7 +13082,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>552</v>
       </c>
@@ -13043,7 +13156,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>560</v>
       </c>
@@ -13117,7 +13230,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>564</v>
       </c>
@@ -13191,7 +13304,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>570</v>
       </c>
@@ -13265,7 +13378,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>576</v>
       </c>
@@ -13339,7 +13452,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>581</v>
       </c>
@@ -13413,7 +13526,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>587</v>
       </c>
@@ -13487,7 +13600,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>592</v>
       </c>
@@ -13561,7 +13674,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>598</v>
       </c>
@@ -13635,7 +13748,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>602</v>
       </c>
@@ -13700,7 +13813,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>602</v>
       </c>
@@ -13765,7 +13878,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>602</v>
       </c>
@@ -13839,7 +13952,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>610</v>
       </c>
@@ -13859,7 +13972,7 @@
         <v>45951</v>
       </c>
       <c r="G172" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="H172">
         <v>1</v>
@@ -13874,7 +13987,7 @@
         <v>346</v>
       </c>
       <c r="L172" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M172" t="s">
         <v>29</v>
@@ -13895,7 +14008,7 @@
         <v>555</v>
       </c>
       <c r="S172" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="T172" t="s">
         <v>349</v>
@@ -13904,7 +14017,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>610</v>
       </c>
@@ -13960,16 +14073,16 @@
         <v>555</v>
       </c>
       <c r="S173" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="T173" t="s">
         <v>349</v>
       </c>
       <c r="U173" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="V173" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="X173" t="s">
         <v>333</v>
@@ -13978,18 +14091,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B174" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C174" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D174" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E174" t="s">
         <v>29</v>
@@ -14022,7 +14135,7 @@
         <v>32</v>
       </c>
       <c r="O174" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P174" t="s">
         <v>33</v>
@@ -14034,16 +14147,16 @@
         <v>357</v>
       </c>
       <c r="S174" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="T174" t="s">
         <v>349</v>
       </c>
       <c r="U174" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="V174" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="X174" t="s">
         <v>333</v>
@@ -14052,18 +14165,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B175" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C175" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D175" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E175" t="s">
         <v>29</v>
@@ -14072,7 +14185,7 @@
         <v>45951</v>
       </c>
       <c r="G175" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H175">
         <v>1</v>
@@ -14087,7 +14200,7 @@
         <v>346</v>
       </c>
       <c r="L175" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M175" t="s">
         <v>29</v>
@@ -14096,7 +14209,7 @@
         <v>32</v>
       </c>
       <c r="O175" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P175" t="s">
         <v>33</v>
@@ -14108,7 +14221,7 @@
         <v>357</v>
       </c>
       <c r="S175" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="T175" t="s">
         <v>349</v>
@@ -14129,18 +14242,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B176" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C176" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D176" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E176" t="s">
         <v>29</v>
@@ -14173,7 +14286,7 @@
         <v>32</v>
       </c>
       <c r="O176" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P176" t="s">
         <v>33</v>
@@ -14185,7 +14298,7 @@
         <v>357</v>
       </c>
       <c r="S176" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="T176" t="s">
         <v>349</v>
@@ -14203,7 +14316,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B177" t="s">
         <v>632</v>
       </c>
@@ -14253,7 +14366,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
         <v>633</v>
       </c>
@@ -14303,7 +14416,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B179" t="s">
         <v>634</v>
       </c>
@@ -14353,7 +14466,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
         <v>637</v>
       </c>
@@ -14403,7 +14516,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B181" t="s">
         <v>638</v>
       </c>
@@ -14453,7 +14566,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
         <v>639</v>
       </c>
@@ -14503,7 +14616,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B183" t="s">
         <v>640</v>
       </c>
@@ -14553,7 +14666,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B184" t="s">
         <v>643</v>
       </c>
@@ -14603,7 +14716,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B185" t="s">
         <v>644</v>
       </c>
@@ -14653,7 +14766,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B186" t="s">
         <v>647</v>
       </c>
@@ -14703,7 +14816,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
         <v>648</v>
       </c>
@@ -14753,7 +14866,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
         <v>649</v>
       </c>
@@ -14803,7 +14916,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>650</v>
       </c>
@@ -14868,7 +14981,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>650</v>
       </c>
@@ -14942,7 +15055,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B191" t="s">
         <v>653</v>
       </c>
@@ -14992,7 +15105,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B192" t="s">
         <v>655</v>
       </c>
@@ -15054,7 +15167,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B193" t="s">
         <v>656</v>
       </c>
@@ -15104,7 +15217,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>659</v>
       </c>
@@ -15169,7 +15282,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>659</v>
       </c>
@@ -15243,7 +15356,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B196" t="s">
         <v>664</v>
       </c>
@@ -15293,7 +15406,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B197" t="s">
         <v>665</v>
       </c>
@@ -15343,7 +15456,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B198" t="s">
         <v>666</v>
       </c>
@@ -15393,7 +15506,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B199" t="s">
         <v>667</v>
       </c>
@@ -15443,7 +15556,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>668</v>
       </c>
@@ -15496,7 +15609,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>672</v>
       </c>
@@ -15549,7 +15662,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>676</v>
       </c>
@@ -15602,7 +15715,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>680</v>
       </c>
@@ -15667,7 +15780,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>680</v>
       </c>
@@ -15687,7 +15800,7 @@
         <v>45962</v>
       </c>
       <c r="G204" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H204">
         <v>1</v>
@@ -15702,7 +15815,7 @@
         <v>346</v>
       </c>
       <c r="L204" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M204" t="s">
         <v>29</v>
@@ -15741,7 +15854,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="205" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>680</v>
       </c>
@@ -15815,7 +15928,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="206" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>688</v>
       </c>
@@ -15868,7 +15981,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="207" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>692</v>
       </c>
@@ -15888,7 +16001,7 @@
         <v>45963</v>
       </c>
       <c r="G207" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H207">
         <v>1</v>
@@ -15903,7 +16016,7 @@
         <v>346</v>
       </c>
       <c r="L207" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M207" t="s">
         <v>29</v>
@@ -15942,7 +16055,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>698</v>
       </c>
@@ -15962,7 +16075,7 @@
         <v>45963</v>
       </c>
       <c r="G208" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H208">
         <v>1</v>
@@ -15977,7 +16090,7 @@
         <v>346</v>
       </c>
       <c r="L208" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M208" t="s">
         <v>29</v>
@@ -16019,7 +16132,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="209" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>706</v>
       </c>
@@ -16039,7 +16152,7 @@
         <v>45963</v>
       </c>
       <c r="G209" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H209">
         <v>1</v>
@@ -16054,7 +16167,7 @@
         <v>346</v>
       </c>
       <c r="L209" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M209" t="s">
         <v>29</v>
@@ -16096,7 +16209,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="210" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>712</v>
       </c>
@@ -16116,7 +16229,7 @@
         <v>45963</v>
       </c>
       <c r="G210" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H210">
         <v>1</v>
@@ -16131,7 +16244,7 @@
         <v>346</v>
       </c>
       <c r="L210" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M210" t="s">
         <v>29</v>
@@ -16173,7 +16286,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="211" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>721</v>
       </c>
@@ -16193,7 +16306,7 @@
         <v>45963</v>
       </c>
       <c r="G211" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H211">
         <v>1</v>
@@ -16208,7 +16321,7 @@
         <v>346</v>
       </c>
       <c r="L211" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M211" t="s">
         <v>29</v>
@@ -16250,7 +16363,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="212" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>727</v>
       </c>
@@ -16270,7 +16383,7 @@
         <v>45963</v>
       </c>
       <c r="G212" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H212">
         <v>1</v>
@@ -16285,7 +16398,7 @@
         <v>346</v>
       </c>
       <c r="L212" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M212" t="s">
         <v>29</v>
@@ -16327,7 +16440,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="213" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>734</v>
       </c>
@@ -16347,7 +16460,7 @@
         <v>45963</v>
       </c>
       <c r="G213" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H213">
         <v>1</v>
@@ -16362,7 +16475,7 @@
         <v>346</v>
       </c>
       <c r="L213" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M213" t="s">
         <v>29</v>
@@ -16404,7 +16517,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="214" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>741</v>
       </c>
@@ -16424,7 +16537,7 @@
         <v>45963</v>
       </c>
       <c r="G214" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H214">
         <v>1</v>
@@ -16439,7 +16552,7 @@
         <v>346</v>
       </c>
       <c r="L214" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M214" t="s">
         <v>29</v>
@@ -16481,7 +16594,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="215" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>748</v>
       </c>
@@ -16501,7 +16614,7 @@
         <v>45963</v>
       </c>
       <c r="G215" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H215">
         <v>1</v>
@@ -16516,7 +16629,7 @@
         <v>346</v>
       </c>
       <c r="L215" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M215" t="s">
         <v>29</v>
@@ -16558,7 +16671,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="216" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>754</v>
       </c>
@@ -16578,7 +16691,7 @@
         <v>45963</v>
       </c>
       <c r="G216" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H216">
         <v>1</v>
@@ -16593,7 +16706,7 @@
         <v>346</v>
       </c>
       <c r="L216" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M216" t="s">
         <v>29</v>
@@ -16635,7 +16748,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="217" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>761</v>
       </c>
@@ -16709,7 +16822,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="218" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>761</v>
       </c>
@@ -16783,7 +16896,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>761</v>
       </c>
@@ -16803,7 +16916,7 @@
         <v>45963</v>
       </c>
       <c r="G219" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H219">
         <v>1</v>
@@ -16818,7 +16931,7 @@
         <v>346</v>
       </c>
       <c r="L219" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M219" t="s">
         <v>29</v>
@@ -16860,7 +16973,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="220" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>761</v>
       </c>
@@ -16934,7 +17047,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="221" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>769</v>
       </c>
@@ -16954,7 +17067,7 @@
         <v>45963</v>
       </c>
       <c r="G221" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H221">
         <v>1</v>
@@ -16969,7 +17082,7 @@
         <v>346</v>
       </c>
       <c r="L221" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M221" t="s">
         <v>29</v>
@@ -17011,7 +17124,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="222" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>774</v>
       </c>
@@ -17031,7 +17144,7 @@
         <v>45963</v>
       </c>
       <c r="G222" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H222">
         <v>1</v>
@@ -17046,7 +17159,7 @@
         <v>346</v>
       </c>
       <c r="L222" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M222" t="s">
         <v>29</v>
@@ -17088,7 +17201,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="223" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>782</v>
       </c>
@@ -17108,7 +17221,7 @@
         <v>45963</v>
       </c>
       <c r="G223" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H223">
         <v>1</v>
@@ -17123,7 +17236,7 @@
         <v>346</v>
       </c>
       <c r="L223" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M223" t="s">
         <v>29</v>
@@ -17162,7 +17275,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="224" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>782</v>
       </c>
@@ -17224,7 +17337,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="225" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>787</v>
       </c>
@@ -17244,7 +17357,7 @@
         <v>45963</v>
       </c>
       <c r="G225" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H225">
         <v>1</v>
@@ -17259,7 +17372,7 @@
         <v>346</v>
       </c>
       <c r="L225" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M225" t="s">
         <v>29</v>
@@ -17301,7 +17414,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="226" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B226" t="s">
         <v>792</v>
       </c>
@@ -17351,7 +17464,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="227" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B227" t="s">
         <v>793</v>
       </c>
@@ -17401,7 +17514,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="228" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B228" t="s">
         <v>794</v>
       </c>
@@ -17451,7 +17564,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="229" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B229" t="s">
         <v>795</v>
       </c>
@@ -17501,7 +17614,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="230" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>796</v>
       </c>
@@ -17566,7 +17679,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="231" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>796</v>
       </c>
@@ -17640,7 +17753,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="232" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B232" t="s">
         <v>800</v>
       </c>
@@ -17690,7 +17803,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="233" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B233" t="s">
         <v>801</v>
       </c>
@@ -17740,7 +17853,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="234" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B234" t="s">
         <v>802</v>
       </c>
@@ -17790,7 +17903,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="235" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>803</v>
       </c>
@@ -17825,7 +17938,7 @@
         <v>346</v>
       </c>
       <c r="L235" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M235" t="s">
         <v>642</v>
@@ -17864,7 +17977,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="236" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>811</v>
       </c>
@@ -17899,7 +18012,7 @@
         <v>346</v>
       </c>
       <c r="L236" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M236" t="s">
         <v>642</v>
@@ -17941,7 +18054,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="237" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>819</v>
       </c>
@@ -17976,7 +18089,7 @@
         <v>346</v>
       </c>
       <c r="L237" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M237" t="s">
         <v>642</v>
@@ -18018,7 +18131,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="238" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>825</v>
       </c>
@@ -18053,7 +18166,7 @@
         <v>346</v>
       </c>
       <c r="L238" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M238" t="s">
         <v>642</v>
@@ -18083,7 +18196,7 @@
         <v>829</v>
       </c>
       <c r="V238" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="W238" t="s">
         <v>704</v>
@@ -18095,7 +18208,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="239" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>830</v>
       </c>
@@ -18130,7 +18243,7 @@
         <v>346</v>
       </c>
       <c r="L239" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M239" t="s">
         <v>642</v>
@@ -18172,7 +18285,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="240" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>836</v>
       </c>
@@ -18207,7 +18320,7 @@
         <v>346</v>
       </c>
       <c r="L240" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M240" t="s">
         <v>642</v>
@@ -18249,7 +18362,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="241" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>843</v>
       </c>
@@ -18284,7 +18397,7 @@
         <v>346</v>
       </c>
       <c r="L241" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M241" t="s">
         <v>642</v>
@@ -18326,7 +18439,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="242" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>848</v>
       </c>
@@ -18361,7 +18474,7 @@
         <v>346</v>
       </c>
       <c r="L242" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M242" t="s">
         <v>642</v>
@@ -18403,7 +18516,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="243" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>854</v>
       </c>
@@ -18438,7 +18551,7 @@
         <v>346</v>
       </c>
       <c r="L243" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M243" t="s">
         <v>642</v>
@@ -18480,7 +18593,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="244" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>861</v>
       </c>
@@ -18515,7 +18628,7 @@
         <v>346</v>
       </c>
       <c r="L244" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M244" t="s">
         <v>642</v>
@@ -18557,7 +18670,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="245" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>865</v>
       </c>
@@ -18592,7 +18705,7 @@
         <v>346</v>
       </c>
       <c r="L245" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M245" t="s">
         <v>642</v>
@@ -18634,7 +18747,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="246" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>873</v>
       </c>
@@ -18669,7 +18782,7 @@
         <v>346</v>
       </c>
       <c r="L246" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M246" t="s">
         <v>642</v>
@@ -18711,7 +18824,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="247" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>879</v>
       </c>
@@ -18746,7 +18859,7 @@
         <v>346</v>
       </c>
       <c r="L247" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M247" t="s">
         <v>642</v>
@@ -18788,7 +18901,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="248" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>885</v>
       </c>
@@ -18823,7 +18936,7 @@
         <v>346</v>
       </c>
       <c r="L248" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M248" t="s">
         <v>642</v>
@@ -18865,7 +18978,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="249" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>892</v>
       </c>
@@ -18900,7 +19013,7 @@
         <v>346</v>
       </c>
       <c r="L249" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M249" t="s">
         <v>642</v>
@@ -18942,7 +19055,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="250" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>897</v>
       </c>
@@ -18977,7 +19090,7 @@
         <v>346</v>
       </c>
       <c r="L250" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M250" t="s">
         <v>642</v>
@@ -19019,7 +19132,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="251" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>903</v>
       </c>
@@ -19054,7 +19167,7 @@
         <v>346</v>
       </c>
       <c r="L251" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M251" t="s">
         <v>642</v>
@@ -19096,7 +19209,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="252" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>911</v>
       </c>
@@ -19131,7 +19244,7 @@
         <v>346</v>
       </c>
       <c r="L252" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M252" t="s">
         <v>642</v>
@@ -19173,7 +19286,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="253" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>919</v>
       </c>
@@ -19208,7 +19321,7 @@
         <v>346</v>
       </c>
       <c r="L253" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M253" t="s">
         <v>922</v>
@@ -19250,7 +19363,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="254" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>925</v>
       </c>
@@ -19285,7 +19398,7 @@
         <v>346</v>
       </c>
       <c r="L254" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M254" t="s">
         <v>922</v>
@@ -19327,7 +19440,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="255" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>932</v>
       </c>
@@ -19362,7 +19475,7 @@
         <v>346</v>
       </c>
       <c r="L255" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M255" t="s">
         <v>922</v>
@@ -19404,7 +19517,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="256" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>938</v>
       </c>
@@ -19439,7 +19552,7 @@
         <v>346</v>
       </c>
       <c r="L256" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M256" t="s">
         <v>922</v>
@@ -19478,7 +19591,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="257" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>943</v>
       </c>
@@ -19513,7 +19626,7 @@
         <v>346</v>
       </c>
       <c r="L257" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M257" t="s">
         <v>922</v>
@@ -19555,7 +19668,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="258" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>948</v>
       </c>
@@ -19590,7 +19703,7 @@
         <v>346</v>
       </c>
       <c r="L258" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M258" t="s">
         <v>922</v>
@@ -19632,7 +19745,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="259" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>952</v>
       </c>
@@ -19667,7 +19780,7 @@
         <v>346</v>
       </c>
       <c r="L259" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M259" t="s">
         <v>922</v>
@@ -19709,7 +19822,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="260" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>959</v>
       </c>
@@ -19744,7 +19857,7 @@
         <v>346</v>
       </c>
       <c r="L260" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M260" t="s">
         <v>922</v>
@@ -19786,7 +19899,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="261" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>963</v>
       </c>
@@ -19821,7 +19934,7 @@
         <v>346</v>
       </c>
       <c r="L261" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M261" t="s">
         <v>922</v>
@@ -19863,7 +19976,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="262" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>968</v>
       </c>
@@ -19898,7 +20011,7 @@
         <v>346</v>
       </c>
       <c r="L262" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M262" t="s">
         <v>922</v>
@@ -19940,7 +20053,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="263" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>974</v>
       </c>
@@ -19975,7 +20088,7 @@
         <v>346</v>
       </c>
       <c r="L263" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M263" t="s">
         <v>922</v>
@@ -20017,7 +20130,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="264" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>979</v>
       </c>
@@ -20052,7 +20165,7 @@
         <v>346</v>
       </c>
       <c r="L264" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M264" t="s">
         <v>922</v>
@@ -20094,7 +20207,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="265" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>984</v>
       </c>
@@ -20129,7 +20242,7 @@
         <v>346</v>
       </c>
       <c r="L265" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M265" t="s">
         <v>922</v>
@@ -20171,7 +20284,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="266" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>990</v>
       </c>
@@ -20206,7 +20319,7 @@
         <v>346</v>
       </c>
       <c r="L266" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M266" t="s">
         <v>922</v>
@@ -20248,7 +20361,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="267" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>999</v>
       </c>
@@ -20283,7 +20396,7 @@
         <v>346</v>
       </c>
       <c r="L267" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M267" t="s">
         <v>922</v>
@@ -20325,7 +20438,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="268" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>1004</v>
       </c>
@@ -20360,7 +20473,7 @@
         <v>346</v>
       </c>
       <c r="L268" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M268" t="s">
         <v>922</v>
@@ -20402,7 +20515,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="269" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>1008</v>
       </c>
@@ -20437,7 +20550,7 @@
         <v>346</v>
       </c>
       <c r="L269" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M269" t="s">
         <v>922</v>
@@ -20479,7 +20592,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="270" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>1014</v>
       </c>
@@ -20514,7 +20627,7 @@
         <v>346</v>
       </c>
       <c r="L270" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M270" t="s">
         <v>922</v>
@@ -20556,7 +20669,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="271" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>1020</v>
       </c>
@@ -20621,7 +20734,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="272" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>1024</v>
       </c>
@@ -20686,7 +20799,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="273" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>1028</v>
       </c>
@@ -20751,7 +20864,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="274" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>1033</v>
       </c>
@@ -20816,7 +20929,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="275" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>1033</v>
       </c>
@@ -20881,7 +20994,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="276" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>1036</v>
       </c>
@@ -20946,7 +21059,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="277" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>1039</v>
       </c>
@@ -21011,7 +21124,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="278" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>1039</v>
       </c>
@@ -21076,7 +21189,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="279" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>1043</v>
       </c>
@@ -21141,7 +21254,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="280" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>1043</v>
       </c>
@@ -21206,7 +21319,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="281" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>1046</v>
       </c>
@@ -21271,7 +21384,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="282" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>1049</v>
       </c>
@@ -21336,7 +21449,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="283" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>1053</v>
       </c>
@@ -21401,7 +21514,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="284" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>1057</v>
       </c>
@@ -21466,7 +21579,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="285" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>1057</v>
       </c>
@@ -21540,7 +21653,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="286" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>1057</v>
       </c>
@@ -21605,7 +21718,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="287" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>1062</v>
       </c>
@@ -21670,7 +21783,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="288" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>1065</v>
       </c>
@@ -21735,7 +21848,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="289" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>1070</v>
       </c>
@@ -21800,7 +21913,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="290" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>1073</v>
       </c>
@@ -21865,7 +21978,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="291" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>1077</v>
       </c>
@@ -21930,7 +22043,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="292" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>1081</v>
       </c>
@@ -21995,7 +22108,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="293" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>1085</v>
       </c>
@@ -22060,7 +22173,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="294" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>1090</v>
       </c>
@@ -22125,7 +22238,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="295" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>1093</v>
       </c>
@@ -22190,7 +22303,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="296" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>1097</v>
       </c>
@@ -22255,7 +22368,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="297" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>1101</v>
       </c>
@@ -22320,7 +22433,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="298" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>1105</v>
       </c>
@@ -22385,7 +22498,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="299" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>1109</v>
       </c>
@@ -22450,7 +22563,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="300" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>1113</v>
       </c>
@@ -22515,7 +22628,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="301" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>1117</v>
       </c>
@@ -22580,7 +22693,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="302" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>1122</v>
       </c>
@@ -22799,7 +22912,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="305" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>1138</v>
       </c>
@@ -22864,7 +22977,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="306" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>1138</v>
       </c>
@@ -22929,7 +23042,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="307" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>1138</v>
       </c>
@@ -22994,7 +23107,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="308" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>1138</v>
       </c>
@@ -23156,7 +23269,7 @@
         <v>1146</v>
       </c>
       <c r="D310" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E310" t="s">
         <v>29</v>
@@ -23189,7 +23302,7 @@
         <v>32</v>
       </c>
       <c r="O310" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P310" t="s">
         <v>33</v>
@@ -23527,6 +23640,1095 @@
         <v>489</v>
       </c>
       <c r="Y314" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="315" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B315" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C315">
+        <v>81230020673</v>
+      </c>
+      <c r="D315" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E315" t="s">
+        <v>29</v>
+      </c>
+      <c r="F315" s="1">
+        <v>46047</v>
+      </c>
+      <c r="G315" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H315">
+        <v>1</v>
+      </c>
+      <c r="I315">
+        <v>2026</v>
+      </c>
+      <c r="J315">
+        <v>1</v>
+      </c>
+      <c r="K315" t="s">
+        <v>346</v>
+      </c>
+      <c r="L315" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M315" t="s">
+        <v>29</v>
+      </c>
+      <c r="N315" t="s">
+        <v>44</v>
+      </c>
+      <c r="O315" t="s">
+        <v>201</v>
+      </c>
+      <c r="P315" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q315">
+        <v>35</v>
+      </c>
+      <c r="R315" t="s">
+        <v>555</v>
+      </c>
+      <c r="S315" t="s">
+        <v>1176</v>
+      </c>
+      <c r="T315" t="s">
+        <v>108</v>
+      </c>
+      <c r="V315" t="s">
+        <v>333</v>
+      </c>
+      <c r="W315" t="s">
+        <v>1177</v>
+      </c>
+      <c r="X315" t="s">
+        <v>1131</v>
+      </c>
+      <c r="Y315" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="316" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B316" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C316">
+        <v>82311966136</v>
+      </c>
+      <c r="D316" t="s">
+        <v>29</v>
+      </c>
+      <c r="E316" t="s">
+        <v>29</v>
+      </c>
+      <c r="F316" s="1">
+        <v>46047</v>
+      </c>
+      <c r="G316" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H316">
+        <v>1</v>
+      </c>
+      <c r="I316">
+        <v>2026</v>
+      </c>
+      <c r="J316">
+        <v>1</v>
+      </c>
+      <c r="K316" t="s">
+        <v>346</v>
+      </c>
+      <c r="L316" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M316" t="s">
+        <v>29</v>
+      </c>
+      <c r="N316" t="s">
+        <v>32</v>
+      </c>
+      <c r="O316" t="s">
+        <v>29</v>
+      </c>
+      <c r="P316" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q316">
+        <v>52</v>
+      </c>
+      <c r="R316" t="s">
+        <v>106</v>
+      </c>
+      <c r="S316" t="s">
+        <v>540</v>
+      </c>
+      <c r="T316" t="s">
+        <v>349</v>
+      </c>
+      <c r="V316" t="s">
+        <v>333</v>
+      </c>
+      <c r="W316" t="s">
+        <v>537</v>
+      </c>
+      <c r="X316" t="s">
+        <v>705</v>
+      </c>
+      <c r="Y316" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="317" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B317" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C317">
+        <v>81321437731</v>
+      </c>
+      <c r="D317" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E317" t="s">
+        <v>29</v>
+      </c>
+      <c r="F317" s="1">
+        <v>46047</v>
+      </c>
+      <c r="G317" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H317">
+        <v>1</v>
+      </c>
+      <c r="I317">
+        <v>2026</v>
+      </c>
+      <c r="J317">
+        <v>1</v>
+      </c>
+      <c r="K317" t="s">
+        <v>346</v>
+      </c>
+      <c r="L317" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M317" t="s">
+        <v>29</v>
+      </c>
+      <c r="N317" t="s">
+        <v>32</v>
+      </c>
+      <c r="O317" t="s">
+        <v>695</v>
+      </c>
+      <c r="P317" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q317">
+        <v>51</v>
+      </c>
+      <c r="R317" t="s">
+        <v>106</v>
+      </c>
+      <c r="S317" t="s">
+        <v>567</v>
+      </c>
+      <c r="T317" t="s">
+        <v>349</v>
+      </c>
+      <c r="V317" t="s">
+        <v>333</v>
+      </c>
+      <c r="W317" t="s">
+        <v>711</v>
+      </c>
+      <c r="X317" t="s">
+        <v>705</v>
+      </c>
+      <c r="Y317" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="318" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B318" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C318">
+        <v>8121566357</v>
+      </c>
+      <c r="D318" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E318" t="s">
+        <v>29</v>
+      </c>
+      <c r="F318" s="1">
+        <v>46047</v>
+      </c>
+      <c r="G318" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H318">
+        <v>1</v>
+      </c>
+      <c r="I318">
+        <v>2026</v>
+      </c>
+      <c r="J318">
+        <v>1</v>
+      </c>
+      <c r="K318" t="s">
+        <v>346</v>
+      </c>
+      <c r="L318" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M318" t="s">
+        <v>29</v>
+      </c>
+      <c r="N318" t="s">
+        <v>32</v>
+      </c>
+      <c r="O318" t="s">
+        <v>1185</v>
+      </c>
+      <c r="Q318">
+        <v>43</v>
+      </c>
+      <c r="R318" t="s">
+        <v>357</v>
+      </c>
+      <c r="S318" t="s">
+        <v>1186</v>
+      </c>
+      <c r="T318" t="s">
+        <v>349</v>
+      </c>
+      <c r="V318" t="s">
+        <v>333</v>
+      </c>
+      <c r="W318" t="s">
+        <v>537</v>
+      </c>
+      <c r="X318" t="s">
+        <v>705</v>
+      </c>
+      <c r="Y318" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="319" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>341</v>
+      </c>
+      <c r="B319" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C319">
+        <v>81228128338</v>
+      </c>
+      <c r="D319" t="s">
+        <v>297</v>
+      </c>
+      <c r="E319" t="s">
+        <v>29</v>
+      </c>
+      <c r="F319" s="1">
+        <v>46047</v>
+      </c>
+      <c r="G319" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H319">
+        <v>1</v>
+      </c>
+      <c r="I319">
+        <v>2026</v>
+      </c>
+      <c r="J319">
+        <v>1</v>
+      </c>
+      <c r="K319" t="s">
+        <v>346</v>
+      </c>
+      <c r="L319" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M319" t="s">
+        <v>29</v>
+      </c>
+      <c r="N319" t="s">
+        <v>32</v>
+      </c>
+      <c r="O319" t="s">
+        <v>297</v>
+      </c>
+      <c r="P319" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q319">
+        <v>50</v>
+      </c>
+      <c r="R319" t="s">
+        <v>106</v>
+      </c>
+      <c r="S319" t="s">
+        <v>1188</v>
+      </c>
+      <c r="T319" t="s">
+        <v>349</v>
+      </c>
+      <c r="V319" t="s">
+        <v>333</v>
+      </c>
+      <c r="W319" t="s">
+        <v>711</v>
+      </c>
+      <c r="X319" t="s">
+        <v>705</v>
+      </c>
+      <c r="Y319" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="320" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="B320" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C320">
+        <v>82231033238</v>
+      </c>
+      <c r="E320" t="s">
+        <v>29</v>
+      </c>
+      <c r="F320" s="1">
+        <v>46047</v>
+      </c>
+      <c r="G320" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H320">
+        <v>1</v>
+      </c>
+      <c r="I320">
+        <v>2026</v>
+      </c>
+      <c r="J320">
+        <v>1</v>
+      </c>
+      <c r="K320" t="s">
+        <v>346</v>
+      </c>
+      <c r="L320" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M320" t="s">
+        <v>29</v>
+      </c>
+      <c r="N320" t="s">
+        <v>32</v>
+      </c>
+      <c r="S320" t="s">
+        <v>473</v>
+      </c>
+      <c r="T320" t="s">
+        <v>349</v>
+      </c>
+      <c r="V320" t="s">
+        <v>333</v>
+      </c>
+      <c r="X320" t="s">
+        <v>489</v>
+      </c>
+      <c r="Y320" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="321" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>769</v>
+      </c>
+      <c r="B321" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C321">
+        <v>81215458600</v>
+      </c>
+      <c r="D321" t="s">
+        <v>757</v>
+      </c>
+      <c r="E321" t="s">
+        <v>29</v>
+      </c>
+      <c r="F321" s="1">
+        <v>46047</v>
+      </c>
+      <c r="G321" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H321">
+        <v>1</v>
+      </c>
+      <c r="I321">
+        <v>2026</v>
+      </c>
+      <c r="J321">
+        <v>1</v>
+      </c>
+      <c r="K321" t="s">
+        <v>346</v>
+      </c>
+      <c r="L321" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M321" t="s">
+        <v>29</v>
+      </c>
+      <c r="N321" t="s">
+        <v>44</v>
+      </c>
+      <c r="O321" t="s">
+        <v>29</v>
+      </c>
+      <c r="P321" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q321">
+        <v>50</v>
+      </c>
+      <c r="R321" t="s">
+        <v>106</v>
+      </c>
+      <c r="S321" t="s">
+        <v>1191</v>
+      </c>
+      <c r="T321" t="s">
+        <v>349</v>
+      </c>
+      <c r="V321" t="s">
+        <v>333</v>
+      </c>
+      <c r="W321" t="s">
+        <v>711</v>
+      </c>
+      <c r="X321" t="s">
+        <v>705</v>
+      </c>
+      <c r="Y321" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="322" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B322" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C322">
+        <v>811656464</v>
+      </c>
+      <c r="D322" t="s">
+        <v>499</v>
+      </c>
+      <c r="E322" t="s">
+        <v>410</v>
+      </c>
+      <c r="F322" s="1">
+        <v>46068</v>
+      </c>
+      <c r="G322" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H322">
+        <v>1</v>
+      </c>
+      <c r="I322">
+        <v>2026</v>
+      </c>
+      <c r="J322">
+        <v>2</v>
+      </c>
+      <c r="K322" t="s">
+        <v>346</v>
+      </c>
+      <c r="L322" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M322" t="s">
+        <v>410</v>
+      </c>
+      <c r="N322" t="s">
+        <v>32</v>
+      </c>
+      <c r="O322" t="s">
+        <v>499</v>
+      </c>
+      <c r="P322" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q322">
+        <v>60</v>
+      </c>
+      <c r="R322" t="s">
+        <v>339</v>
+      </c>
+      <c r="S322" t="s">
+        <v>764</v>
+      </c>
+      <c r="T322" t="s">
+        <v>349</v>
+      </c>
+      <c r="V322" t="s">
+        <v>333</v>
+      </c>
+      <c r="W322" t="s">
+        <v>1193</v>
+      </c>
+      <c r="X322" t="s">
+        <v>1131</v>
+      </c>
+      <c r="Y322" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="323" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B323" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C323">
+        <v>81384123334</v>
+      </c>
+      <c r="D323" t="s">
+        <v>80</v>
+      </c>
+      <c r="E323" t="s">
+        <v>410</v>
+      </c>
+      <c r="F323" s="1">
+        <v>46068</v>
+      </c>
+      <c r="G323" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H323">
+        <v>1</v>
+      </c>
+      <c r="I323">
+        <v>2026</v>
+      </c>
+      <c r="J323">
+        <v>2</v>
+      </c>
+      <c r="K323" t="s">
+        <v>346</v>
+      </c>
+      <c r="L323" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M323" t="s">
+        <v>410</v>
+      </c>
+      <c r="N323" t="s">
+        <v>32</v>
+      </c>
+      <c r="O323" t="s">
+        <v>80</v>
+      </c>
+      <c r="P323" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q323">
+        <v>41</v>
+      </c>
+      <c r="R323" t="s">
+        <v>357</v>
+      </c>
+      <c r="S323" t="s">
+        <v>579</v>
+      </c>
+      <c r="T323" t="s">
+        <v>349</v>
+      </c>
+      <c r="V323" t="s">
+        <v>333</v>
+      </c>
+      <c r="W323" t="s">
+        <v>1194</v>
+      </c>
+      <c r="X323" t="s">
+        <v>489</v>
+      </c>
+      <c r="Y323" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>581</v>
+      </c>
+      <c r="B324" t="s">
+        <v>582</v>
+      </c>
+      <c r="C324">
+        <v>81294770550</v>
+      </c>
+      <c r="D324" t="s">
+        <v>257</v>
+      </c>
+      <c r="E324" t="s">
+        <v>410</v>
+      </c>
+      <c r="F324" s="1">
+        <v>46068</v>
+      </c>
+      <c r="G324" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H324">
+        <v>1</v>
+      </c>
+      <c r="I324">
+        <v>2026</v>
+      </c>
+      <c r="J324">
+        <v>2</v>
+      </c>
+      <c r="K324" t="s">
+        <v>346</v>
+      </c>
+      <c r="L324" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M324" t="s">
+        <v>410</v>
+      </c>
+      <c r="N324" t="s">
+        <v>44</v>
+      </c>
+      <c r="O324" t="s">
+        <v>257</v>
+      </c>
+      <c r="P324" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q324">
+        <v>28</v>
+      </c>
+      <c r="R324" t="s">
+        <v>555</v>
+      </c>
+      <c r="S324" t="s">
+        <v>584</v>
+      </c>
+      <c r="T324" t="s">
+        <v>108</v>
+      </c>
+      <c r="V324" t="s">
+        <v>333</v>
+      </c>
+      <c r="W324" t="s">
+        <v>537</v>
+      </c>
+      <c r="X324" t="s">
+        <v>705</v>
+      </c>
+      <c r="Y324" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B325" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C325">
+        <v>8176345818</v>
+      </c>
+      <c r="D325" t="s">
+        <v>499</v>
+      </c>
+      <c r="E325" t="s">
+        <v>410</v>
+      </c>
+      <c r="F325" s="1">
+        <v>46068</v>
+      </c>
+      <c r="G325" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H325">
+        <v>1</v>
+      </c>
+      <c r="I325">
+        <v>2026</v>
+      </c>
+      <c r="J325">
+        <v>2</v>
+      </c>
+      <c r="K325" t="s">
+        <v>346</v>
+      </c>
+      <c r="L325" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M325" t="s">
+        <v>410</v>
+      </c>
+      <c r="N325" t="s">
+        <v>32</v>
+      </c>
+      <c r="O325" t="s">
+        <v>499</v>
+      </c>
+      <c r="P325" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q325">
+        <v>45</v>
+      </c>
+      <c r="R325" t="s">
+        <v>357</v>
+      </c>
+      <c r="S325" t="s">
+        <v>443</v>
+      </c>
+      <c r="T325" t="s">
+        <v>330</v>
+      </c>
+      <c r="V325" t="s">
+        <v>333</v>
+      </c>
+      <c r="W325" t="s">
+        <v>711</v>
+      </c>
+      <c r="X325" t="s">
+        <v>705</v>
+      </c>
+      <c r="Y325" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B326" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C326">
+        <v>8128414134</v>
+      </c>
+      <c r="D326" t="s">
+        <v>405</v>
+      </c>
+      <c r="E326" t="s">
+        <v>410</v>
+      </c>
+      <c r="F326" s="1">
+        <v>46068</v>
+      </c>
+      <c r="G326" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H326">
+        <v>1</v>
+      </c>
+      <c r="I326">
+        <v>2026</v>
+      </c>
+      <c r="J326">
+        <v>2</v>
+      </c>
+      <c r="K326" t="s">
+        <v>346</v>
+      </c>
+      <c r="L326" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M326" t="s">
+        <v>410</v>
+      </c>
+      <c r="N326" t="s">
+        <v>32</v>
+      </c>
+      <c r="O326" t="s">
+        <v>405</v>
+      </c>
+      <c r="P326" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q326">
+        <v>47</v>
+      </c>
+      <c r="R326" t="s">
+        <v>106</v>
+      </c>
+      <c r="S326" t="s">
+        <v>1197</v>
+      </c>
+      <c r="T326" t="s">
+        <v>349</v>
+      </c>
+      <c r="V326" t="s">
+        <v>333</v>
+      </c>
+      <c r="W326" t="s">
+        <v>1198</v>
+      </c>
+      <c r="X326" t="s">
+        <v>1131</v>
+      </c>
+      <c r="Y326" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="327" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B327" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C327">
+        <v>81290172229</v>
+      </c>
+      <c r="D327" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E327" t="s">
+        <v>410</v>
+      </c>
+      <c r="F327" s="1">
+        <v>46068</v>
+      </c>
+      <c r="G327" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H327">
+        <v>1</v>
+      </c>
+      <c r="I327">
+        <v>2026</v>
+      </c>
+      <c r="J327">
+        <v>2</v>
+      </c>
+      <c r="K327" t="s">
+        <v>346</v>
+      </c>
+      <c r="L327" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M327" t="s">
+        <v>410</v>
+      </c>
+      <c r="N327" t="s">
+        <v>32</v>
+      </c>
+      <c r="O327" t="s">
+        <v>257</v>
+      </c>
+      <c r="P327" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q327">
+        <v>53</v>
+      </c>
+      <c r="R327" t="s">
+        <v>106</v>
+      </c>
+      <c r="S327" t="s">
+        <v>709</v>
+      </c>
+      <c r="T327" t="s">
+        <v>349</v>
+      </c>
+      <c r="V327" t="s">
+        <v>333</v>
+      </c>
+      <c r="W327" t="s">
+        <v>711</v>
+      </c>
+      <c r="X327" t="s">
+        <v>705</v>
+      </c>
+      <c r="Y327" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="328" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B328" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C328">
+        <v>81298099979</v>
+      </c>
+      <c r="D328" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E328" t="s">
+        <v>410</v>
+      </c>
+      <c r="F328" s="1">
+        <v>46068</v>
+      </c>
+      <c r="G328" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H328">
+        <v>1</v>
+      </c>
+      <c r="I328">
+        <v>2026</v>
+      </c>
+      <c r="J328">
+        <v>2</v>
+      </c>
+      <c r="K328" t="s">
+        <v>346</v>
+      </c>
+      <c r="L328" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M328" t="s">
+        <v>410</v>
+      </c>
+      <c r="N328" t="s">
+        <v>32</v>
+      </c>
+      <c r="O328" t="s">
+        <v>1202</v>
+      </c>
+      <c r="P328" t="s">
+        <v>1203</v>
+      </c>
+      <c r="Q328">
+        <v>46</v>
+      </c>
+      <c r="R328" t="s">
+        <v>106</v>
+      </c>
+      <c r="S328" t="s">
+        <v>1204</v>
+      </c>
+      <c r="T328" t="s">
+        <v>349</v>
+      </c>
+      <c r="V328" t="s">
+        <v>333</v>
+      </c>
+      <c r="W328" t="s">
+        <v>704</v>
+      </c>
+      <c r="X328" t="s">
+        <v>489</v>
+      </c>
+      <c r="Y328" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="329" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B329" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C329">
+        <v>81338510445</v>
+      </c>
+      <c r="D329" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E329" t="s">
+        <v>29</v>
+      </c>
+      <c r="F329" s="1">
+        <v>45808</v>
+      </c>
+      <c r="G329" t="s">
+        <v>345</v>
+      </c>
+      <c r="H329">
+        <v>1</v>
+      </c>
+      <c r="I329">
+        <v>2025</v>
+      </c>
+      <c r="J329">
+        <v>5</v>
+      </c>
+      <c r="K329" t="s">
+        <v>346</v>
+      </c>
+      <c r="L329" t="s">
+        <v>347</v>
+      </c>
+      <c r="M329" t="s">
+        <v>29</v>
+      </c>
+      <c r="N329" t="s">
+        <v>32</v>
+      </c>
+      <c r="O329" t="s">
+        <v>621</v>
+      </c>
+      <c r="P329" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q329">
+        <v>45</v>
+      </c>
+      <c r="R329" t="s">
+        <v>357</v>
+      </c>
+      <c r="S329" t="s">
+        <v>1147</v>
+      </c>
+      <c r="T329" t="s">
+        <v>349</v>
+      </c>
+      <c r="U329" t="s">
+        <v>1206</v>
+      </c>
+      <c r="V329" t="s">
+        <v>475</v>
+      </c>
+      <c r="W329" t="s">
+        <v>537</v>
+      </c>
+      <c r="X329" t="s">
+        <v>705</v>
+      </c>
+      <c r="Y329" t="s">
         <v>33</v>
       </c>
     </row>

--- a/data_clean/data_merged.xlsx
+++ b/data_clean/data_merged.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Documents\All Work Files\1. PE New Report\data_clean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9443D9D5-D5DF-4343-A659-D61C994BC1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F706E593-D877-4600-B9F2-D34491C61C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5073" uniqueCount="1207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6090" uniqueCount="1331">
   <si>
     <t>Email</t>
   </si>
@@ -3646,6 +3646,378 @@
   </si>
   <si>
     <t xml:space="preserve">menambah ilmu untuk bisa berbagi dengan para member yoga yang memiliki keluhan tentang syaraf kejepit. </t>
+  </si>
+  <si>
+    <t>Workshop yang Diikuti</t>
+  </si>
+  <si>
+    <t>Nanda.chrisna@gmail.com</t>
+  </si>
+  <si>
+    <t>Anak Agung Sagung Nandaswari Chrisna</t>
+  </si>
+  <si>
+    <t>Denpasar Bali</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>Workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lebih mengerti tentang anatomy tubuh </t>
+  </si>
+  <si>
+    <t>Anatomi, Gerak &amp; Postur Tubuh, Menambah Pengetahuan &amp; Wawasan</t>
+  </si>
+  <si>
+    <t>Functional Anatomy</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>Biomechanics Movement</t>
+  </si>
+  <si>
+    <t>kdastuti99@gmail.com</t>
+  </si>
+  <si>
+    <t>Kadek Windy Astuti</t>
+  </si>
+  <si>
+    <t>Nurse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bisa memahami postur diri sendiri </t>
+  </si>
+  <si>
+    <t>Anatomi, Gerak &amp; Postur Tubuh, Menambah Pengetahuan &amp; Wawasan, Penerapan untuk Diri Sendiri &amp; Keluarga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mietamarzuki@gmail.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rahmieta Marzuki </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horne maker- mat pilates teacher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pemahaman lebih dalam dikedua subject diatas </t>
+  </si>
+  <si>
+    <t>agussuwiddnyana@gmail.com</t>
+  </si>
+  <si>
+    <t>I Putu Agus Suwidnyana</t>
+  </si>
+  <si>
+    <t>Dapat memahami fungsi anatomi dan pergerakan yang benar &amp; tanpa cedera</t>
+  </si>
+  <si>
+    <t>Anatomi, Gerak &amp; Postur Tubuh, Menambah Pengetahuan &amp; Wawasan, Penanganan Cedera &amp; Keluhan</t>
+  </si>
+  <si>
+    <t>unikindrawsto06@gmail.com</t>
+  </si>
+  <si>
+    <t>Nikki</t>
+  </si>
+  <si>
+    <t>Yoga teacher and plantbased chef</t>
+  </si>
+  <si>
+    <t>Memahami lebih jauh tentang anatomi tubuh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ayu.trisna56@yahoo.com </t>
+  </si>
+  <si>
+    <t>I Dewa Ayu Trisna Dewi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingin belajar Anatomy </t>
+  </si>
+  <si>
+    <t>Lidyaphar.ly@gmail.com</t>
+  </si>
+  <si>
+    <t>Lidya Yaphar</t>
+  </si>
+  <si>
+    <t>Mataram, lombok</t>
+  </si>
+  <si>
+    <t>Freelance pilates instructor</t>
+  </si>
+  <si>
+    <t>Lebih memahami anatomi tubuh manusia dan prinsip gerak utk menghindari cidera</t>
+  </si>
+  <si>
+    <t>indri.putu@gmail.com</t>
+  </si>
+  <si>
+    <t>Putu Indriyati</t>
+  </si>
+  <si>
+    <t>Belajar lebih jauh mengenai anatomy dan biomechanical movement karena memiliki beberapa kendala latihan dan sering cedera walaupun sudah didampingi PT</t>
+  </si>
+  <si>
+    <t>azariazena@gmail.com</t>
+  </si>
+  <si>
+    <t>Zena Azaria</t>
+  </si>
+  <si>
+    <t>widyamey.82@gmail.com</t>
+  </si>
+  <si>
+    <t>Mediyawati</t>
+  </si>
+  <si>
+    <t>2026-04-12</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instruktur pilates </t>
+  </si>
+  <si>
+    <t xml:space="preserve">meningkatkan pemahaman tentang struktur tubuh serta mekanika gerak untuk diaplikasikan dalam pencegahan cedera, rehabilitasi yang lebih efektif,menambah knowledge saya sebagai instruktur pilates </t>
+  </si>
+  <si>
+    <t>Anatomi, Gerak &amp; Postur Tubuh, Menambah Pengetahuan &amp; Wawasan, Penanganan Cedera &amp; Keluhan, Pengembangan Profesi &amp; Berbagi Ilmu</t>
+  </si>
+  <si>
+    <t>2026-04-19</t>
+  </si>
+  <si>
+    <t>skolastika.cynthia@gmail.com</t>
+  </si>
+  <si>
+    <t>Skolastika cynthia</t>
+  </si>
+  <si>
+    <t>Tangsel</t>
+  </si>
+  <si>
+    <t>Instruktur aerial hammock</t>
+  </si>
+  <si>
+    <t>Paham functional anatomy dan biomechanics, terutama gerakan yang normal/memungkinkan tergantung dari tipe badan orang. Paham postur yang baik terutama bagian ribs sampai hips dan dada</t>
+  </si>
+  <si>
+    <t>yurizapratiwi@gmail.com</t>
+  </si>
+  <si>
+    <t>Yuriza Pratiwi</t>
+  </si>
+  <si>
+    <t>Jakarta Timur</t>
+  </si>
+  <si>
+    <t>bisa lebih memahami biomekanik &amp; konsep dasar function anatamoi tubuh sehingga bisa menerapkan dalam program latihan pilates</t>
+  </si>
+  <si>
+    <t>Anatomi, Gerak &amp; Postur Tubuh, Menambah Pengetahuan &amp; Wawasan, Pengembangan Profesi &amp; Berbagi Ilmu</t>
+  </si>
+  <si>
+    <t>herdirinananies@gmail.com</t>
+  </si>
+  <si>
+    <t>Nanies Nuraini Herdirina</t>
+  </si>
+  <si>
+    <t>Mat Pilates Instruktur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingin lebih memahami setiap detil gerakan dalam mat pilates yg digunakan otot tulang sendi apa saja, serta manfaatnya. Ingin belajar lebih dalam mengenai anatomi dan biomekanik agar mempermudah memberi cue pada klien. </t>
+  </si>
+  <si>
+    <t>Janet.nlimang@gmail.com</t>
+  </si>
+  <si>
+    <t>Janet Nadia Limang</t>
+  </si>
+  <si>
+    <t>Tutor dan instruktur pilates</t>
+  </si>
+  <si>
+    <t>Bisa lebih memahami gerak tubuh yang benar saat mengajar pilates</t>
+  </si>
+  <si>
+    <t>shintasubowo@gmail.com</t>
+  </si>
+  <si>
+    <t>Wahyuni Shinta Kramadibrata</t>
+  </si>
+  <si>
+    <t>Deep understanding of body anatomy and the connection with pilates exercise</t>
+  </si>
+  <si>
+    <t>afiastefika.er@gmail.com</t>
+  </si>
+  <si>
+    <t>Afia Stefika</t>
+  </si>
+  <si>
+    <t>Dapat menjadi instruktur yg lebih mantap</t>
+  </si>
+  <si>
+    <t>nunungbengkel74@gmail.com</t>
+  </si>
+  <si>
+    <t>NUNUNG NURJANAH</t>
+  </si>
+  <si>
+    <t>Jawabarat</t>
+  </si>
+  <si>
+    <t>Menambah wawasan dlm mengajar</t>
+  </si>
+  <si>
+    <t>rr.permatasari@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raden Ranti Permatasari </t>
+  </si>
+  <si>
+    <t>Perkici XI Blok EB 2 No 59 Bintaro Sektor 5 Tangerang Selatan</t>
+  </si>
+  <si>
+    <t>Karyawan / Guru yoga</t>
+  </si>
+  <si>
+    <t>Mendapatkan ilmu untuk belajar mengaplikasikan dalam proses mengajar yoga</t>
+  </si>
+  <si>
+    <t>miss.gartina@gmail.com</t>
+  </si>
+  <si>
+    <t>Mira Gartina Sumawijaya</t>
+  </si>
+  <si>
+    <t>Jakarta Pusat</t>
+  </si>
+  <si>
+    <t>Instruktur Yoga Anak &amp; Individu Autisme</t>
+  </si>
+  <si>
+    <t>mendapatkan tambahan ilmu dan lingkungan baru.</t>
+  </si>
+  <si>
+    <t>henychamelia262191@gmail.com</t>
+  </si>
+  <si>
+    <t>Heny chamelia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dapat ilmu baru </t>
+  </si>
+  <si>
+    <t>asihhizkia@gmail.com</t>
+  </si>
+  <si>
+    <t>Mintarsih ( Asih )</t>
+  </si>
+  <si>
+    <t>Instruktur pilates &amp; Yoga</t>
+  </si>
+  <si>
+    <t>Untuk mengajar member bisa lebih aman dan terarah serta efektif</t>
+  </si>
+  <si>
+    <t>contrologyofjov@gmail.com</t>
+  </si>
+  <si>
+    <t>Jovanka Aurellia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instruktur Pilates </t>
+  </si>
+  <si>
+    <t>Bisa belajar lebih banyak tentang tubuh manusia dan bisa membantu diri sendiri dan orang sekitar</t>
+  </si>
+  <si>
+    <t>rinariens73@gmail.com</t>
+  </si>
+  <si>
+    <t>Rina Rahmawati</t>
+  </si>
+  <si>
+    <t>Sawangan - Depok - Jabar</t>
+  </si>
+  <si>
+    <t>Yoga teacher</t>
+  </si>
+  <si>
+    <t>Mengenal lebih dalam tentang anatomy tubuh</t>
+  </si>
+  <si>
+    <t>rindranti@gmail.com</t>
+  </si>
+  <si>
+    <t>Sari Indrayanti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menambah wawasan </t>
+  </si>
+  <si>
+    <t>gemini83.lady98@gmail.com</t>
+  </si>
+  <si>
+    <t>Monalisa Sakarias</t>
+  </si>
+  <si>
+    <t>Yoga TC</t>
+  </si>
+  <si>
+    <t>Semoga bisa menambah wawasan dan ilmu mengenai biomechanics movement.</t>
+  </si>
+  <si>
+    <t>aryanisitorus@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aryani mei juventina sitorus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bisa lebih paham biomecanic movement </t>
+  </si>
+  <si>
+    <t>kangrams82@gmail.com</t>
+  </si>
+  <si>
+    <t>Muhamad Ramdan</t>
+  </si>
+  <si>
+    <t>Teacher Yoga dan Pilates</t>
+  </si>
+  <si>
+    <t>Bisa membantu murid yang membutuhkan latihan yg tepat sesuai anatomi tubunya</t>
+  </si>
+  <si>
+    <t>corneliapsp@gmail.com</t>
+  </si>
+  <si>
+    <t>cornelia puspa dewi</t>
+  </si>
+  <si>
+    <t>Bekasi Barat</t>
+  </si>
+  <si>
+    <t>Pilates Instractor</t>
+  </si>
+  <si>
+    <t>Dapat memahami prinsip dasar anatomi fungsional agar bisa menerapkan konsep anatomi pada desain program latihan dan koreksi postur dalam pilates</t>
   </si>
 </sst>
 </file>
@@ -3653,9 +4025,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3667,6 +4039,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3702,10 +4080,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -3713,6 +4094,23 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -3741,23 +4139,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3772,22 +4153,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1FEC11E-D3BA-4A29-8078-C55E67B1880B}" name="Table1" displayName="Table1" ref="A1:Y329" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="2" tableBorderDxfId="3">
-  <autoFilter ref="A1:Y329" xr:uid="{B1FEC11E-D3BA-4A29-8078-C55E67B1880B}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="Workshop Metabolic"/>
-        <filter val="Workshop Metabolic Semarang"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <tableColumns count="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1FEC11E-D3BA-4A29-8078-C55E67B1880B}" name="Table1" displayName="Table1" ref="A1:Z380" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
+  <autoFilter ref="A1:Z380" xr:uid="{B1FEC11E-D3BA-4A29-8078-C55E67B1880B}"/>
+  <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{EA585163-F1F2-4F30-8ED1-A555BC239611}" name="Email"/>
     <tableColumn id="2" xr3:uid="{DCC1A6A3-5827-4923-8AF7-ABEE0C6FD304}" name="Nama"/>
     <tableColumn id="3" xr3:uid="{63061C45-E91E-4C23-8076-E25A30A1B3DC}" name="No WhatsApp"/>
     <tableColumn id="4" xr3:uid="{324AD86D-A8D4-48E1-B73A-C29695BAD991}" name="Kota - Provinsi"/>
     <tableColumn id="5" xr3:uid="{D3606A7C-C97B-4E9D-9B6C-32331A1E2745}" name="Tempat Kegiatan"/>
-    <tableColumn id="6" xr3:uid="{F35F162C-92F2-4C07-8447-70AD9B2ABB10}" name="Tanggal" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{F35F162C-92F2-4C07-8447-70AD9B2ABB10}" name="Tanggal" dataDxfId="0"/>
     <tableColumn id="7" xr3:uid="{C4DA2298-94F2-46E3-B723-2E4EAD3178B0}" name="Sesi"/>
     <tableColumn id="8" xr3:uid="{E0083422-FF72-44A1-BB4D-263B051D6DE4}" name="Jumlah Sesi"/>
     <tableColumn id="9" xr3:uid="{D1FF56DF-DE65-489A-9637-2D66DA05A2B8}" name="Tahun"/>
@@ -3807,6 +4181,7 @@
     <tableColumn id="23" xr3:uid="{AA8E2D21-6847-4E1A-ADE6-054E407D45CE}" name="Keluhan (Asli)"/>
     <tableColumn id="24" xr3:uid="{B4903E4C-909D-459A-A5BD-894DA3ED7E42}" name="Topik Keluhan"/>
     <tableColumn id="25" xr3:uid="{BCA29B92-B444-43CB-B676-79C6462435F3}" name="Wilayah"/>
+    <tableColumn id="27" xr3:uid="{7F1415CA-3B99-4F46-8EBD-371375798FC6}" name="Workshop yang Diikuti"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4097,7 +4472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y329"/>
+  <dimension ref="A1:Z380"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="14.453125" customWidth="1"/>
@@ -4119,9 +4494,10 @@
     <col min="23" max="23" width="14.26953125" customWidth="1"/>
     <col min="24" max="24" width="14.7265625" customWidth="1"/>
     <col min="25" max="25" width="9.54296875" customWidth="1"/>
+    <col min="26" max="26" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4197,8 +4573,11 @@
       <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+      <c r="Z1" s="3" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -4251,7 +4630,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -4304,7 +4683,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -4357,7 +4736,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -4410,7 +4789,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -4463,7 +4842,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -4516,7 +4895,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -4569,7 +4948,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -4622,7 +5001,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>59</v>
       </c>
@@ -4675,7 +5054,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -4728,7 +5107,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -4781,7 +5160,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>68</v>
       </c>
@@ -4834,7 +5213,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>71</v>
       </c>
@@ -4887,7 +5266,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -4940,7 +5319,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -4993,7 +5372,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>85</v>
       </c>
@@ -5046,7 +5425,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -5099,7 +5478,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>91</v>
       </c>
@@ -5152,7 +5531,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>94</v>
       </c>
@@ -5205,7 +5584,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>101</v>
       </c>
@@ -5270,7 +5649,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>109</v>
       </c>
@@ -5323,7 +5702,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>114</v>
       </c>
@@ -5376,7 +5755,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -5429,7 +5808,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>120</v>
       </c>
@@ -5482,7 +5861,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>123</v>
       </c>
@@ -5535,7 +5914,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>126</v>
       </c>
@@ -5588,7 +5967,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>131</v>
       </c>
@@ -5641,7 +6020,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>134</v>
       </c>
@@ -5694,7 +6073,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>137</v>
       </c>
@@ -5747,7 +6126,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>140</v>
       </c>
@@ -5800,7 +6179,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>143</v>
       </c>
@@ -5853,7 +6232,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>146</v>
       </c>
@@ -5906,7 +6285,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>149</v>
       </c>
@@ -5959,7 +6338,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>152</v>
       </c>
@@ -6012,7 +6391,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>157</v>
       </c>
@@ -6065,7 +6444,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>160</v>
       </c>
@@ -6118,7 +6497,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>163</v>
       </c>
@@ -6171,7 +6550,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>168</v>
       </c>
@@ -6224,7 +6603,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>171</v>
       </c>
@@ -6277,7 +6656,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>176</v>
       </c>
@@ -6330,7 +6709,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>179</v>
       </c>
@@ -6383,7 +6762,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>182</v>
       </c>
@@ -6436,7 +6815,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>185</v>
       </c>
@@ -6489,7 +6868,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>188</v>
       </c>
@@ -6542,7 +6921,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>191</v>
       </c>
@@ -6595,7 +6974,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>196</v>
       </c>
@@ -6648,7 +7027,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>203</v>
       </c>
@@ -6701,7 +7080,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>208</v>
       </c>
@@ -6754,7 +7133,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>213</v>
       </c>
@@ -6807,7 +7186,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>216</v>
       </c>
@@ -6860,7 +7239,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>221</v>
       </c>
@@ -6913,7 +7292,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="53" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>224</v>
       </c>
@@ -6966,7 +7345,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>227</v>
       </c>
@@ -7019,7 +7398,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>230</v>
       </c>
@@ -7072,7 +7451,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>233</v>
       </c>
@@ -7125,7 +7504,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="57" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>236</v>
       </c>
@@ -7178,7 +7557,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>239</v>
       </c>
@@ -7231,7 +7610,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="59" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>242</v>
       </c>
@@ -7284,7 +7663,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="60" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>245</v>
       </c>
@@ -7337,7 +7716,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="61" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>245</v>
       </c>
@@ -7390,7 +7769,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>253</v>
       </c>
@@ -7443,7 +7822,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>259</v>
       </c>
@@ -7496,7 +7875,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>259</v>
       </c>
@@ -7549,7 +7928,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>263</v>
       </c>
@@ -7602,7 +7981,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>266</v>
       </c>
@@ -7655,7 +8034,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>269</v>
       </c>
@@ -7708,7 +8087,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>272</v>
       </c>
@@ -7761,7 +8140,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>275</v>
       </c>
@@ -7814,7 +8193,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>278</v>
       </c>
@@ -7867,7 +8246,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>281</v>
       </c>
@@ -7920,7 +8299,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>284</v>
       </c>
@@ -7973,7 +8352,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>287</v>
       </c>
@@ -8026,7 +8405,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>290</v>
       </c>
@@ -8079,7 +8458,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>293</v>
       </c>
@@ -8132,7 +8511,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>298</v>
       </c>
@@ -8185,7 +8564,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>301</v>
       </c>
@@ -8238,7 +8617,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>306</v>
       </c>
@@ -8291,7 +8670,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>309</v>
       </c>
@@ -8344,7 +8723,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>312</v>
       </c>
@@ -8397,7 +8776,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>312</v>
       </c>
@@ -8450,7 +8829,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>315</v>
       </c>
@@ -8503,7 +8882,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>318</v>
       </c>
@@ -8556,7 +8935,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>321</v>
       </c>
@@ -8609,7 +8988,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>324</v>
       </c>
@@ -8662,7 +9041,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>327</v>
       </c>
@@ -8727,7 +9106,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>327</v>
       </c>
@@ -8792,7 +9171,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>327</v>
       </c>
@@ -8866,7 +9245,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>336</v>
       </c>
@@ -8931,7 +9310,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>336</v>
       </c>
@@ -9005,7 +9384,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>341</v>
       </c>
@@ -9079,7 +9458,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="92" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>352</v>
       </c>
@@ -9153,7 +9532,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>360</v>
       </c>
@@ -9218,7 +9597,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>360</v>
       </c>
@@ -9292,7 +9671,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>366</v>
       </c>
@@ -9366,7 +9745,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>373</v>
       </c>
@@ -9440,7 +9819,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="97" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>379</v>
       </c>
@@ -9505,7 +9884,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="98" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>379</v>
       </c>
@@ -9579,7 +9958,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="99" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>384</v>
       </c>
@@ -9653,7 +10032,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="100" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>392</v>
       </c>
@@ -9718,7 +10097,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="101" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>392</v>
       </c>
@@ -9792,7 +10171,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>399</v>
       </c>
@@ -9845,7 +10224,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="103" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>406</v>
       </c>
@@ -9898,7 +10277,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="104" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>411</v>
       </c>
@@ -9951,7 +10330,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="105" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
         <v>416</v>
       </c>
@@ -10001,7 +10380,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="106" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
         <v>421</v>
       </c>
@@ -10051,7 +10430,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="107" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
         <v>422</v>
       </c>
@@ -10101,7 +10480,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="108" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
         <v>424</v>
       </c>
@@ -10151,7 +10530,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="109" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
         <v>426</v>
       </c>
@@ -10201,7 +10580,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="110" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
         <v>429</v>
       </c>
@@ -10251,7 +10630,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="111" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>431</v>
       </c>
@@ -10325,7 +10704,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="112" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>439</v>
       </c>
@@ -10399,7 +10778,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="113" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>445</v>
       </c>
@@ -10473,7 +10852,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="114" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>452</v>
       </c>
@@ -10547,7 +10926,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="115" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>458</v>
       </c>
@@ -10621,7 +11000,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="116" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>466</v>
       </c>
@@ -10686,7 +11065,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="117" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>466</v>
       </c>
@@ -10751,7 +11130,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>466</v>
       </c>
@@ -10825,7 +11204,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="119" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>476</v>
       </c>
@@ -10899,7 +11278,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="120" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>483</v>
       </c>
@@ -10973,7 +11352,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="121" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>490</v>
       </c>
@@ -11047,7 +11426,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
         <v>495</v>
       </c>
@@ -11097,7 +11476,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="123" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
         <v>496</v>
       </c>
@@ -11147,7 +11526,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="124" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
         <v>497</v>
       </c>
@@ -11197,7 +11576,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="125" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
         <v>500</v>
       </c>
@@ -11247,7 +11626,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="126" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
         <v>501</v>
       </c>
@@ -11297,7 +11676,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="127" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
         <v>502</v>
       </c>
@@ -11347,7 +11726,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="128" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
         <v>504</v>
       </c>
@@ -11397,7 +11776,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="129" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
         <v>505</v>
       </c>
@@ -11447,7 +11826,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="130" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
         <v>507</v>
       </c>
@@ -11497,7 +11876,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="131" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
         <v>508</v>
       </c>
@@ -11547,7 +11926,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="132" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
         <v>509</v>
       </c>
@@ -11597,7 +11976,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="133" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
         <v>511</v>
       </c>
@@ -11647,7 +12026,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="134" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
         <v>512</v>
       </c>
@@ -11697,7 +12076,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="135" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B135" t="s">
         <v>513</v>
       </c>
@@ -11747,7 +12126,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="136" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
         <v>514</v>
       </c>
@@ -11797,7 +12176,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="137" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
         <v>515</v>
       </c>
@@ -11847,7 +12226,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="138" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
         <v>516</v>
       </c>
@@ -11897,7 +12276,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="139" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B139" t="s">
         <v>517</v>
       </c>
@@ -11947,7 +12326,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="140" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B140" t="s">
         <v>520</v>
       </c>
@@ -11997,7 +12376,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="141" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
         <v>521</v>
       </c>
@@ -12047,7 +12426,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="142" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
         <v>522</v>
       </c>
@@ -12097,7 +12476,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="143" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
         <v>523</v>
       </c>
@@ -12147,7 +12526,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="144" spans="2:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B144" t="s">
         <v>524</v>
       </c>
@@ -12197,7 +12576,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
         <v>525</v>
       </c>
@@ -12247,7 +12626,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B146" t="s">
         <v>526</v>
       </c>
@@ -12297,7 +12676,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B147" t="s">
         <v>530</v>
       </c>
@@ -12347,7 +12726,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B148" t="s">
         <v>531</v>
       </c>
@@ -12397,7 +12776,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>533</v>
       </c>
@@ -12450,7 +12829,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>533</v>
       </c>
@@ -12503,7 +12882,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>537</v>
       </c>
@@ -12568,7 +12947,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>537</v>
       </c>
@@ -12633,7 +13012,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>537</v>
       </c>
@@ -12707,7 +13086,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>542</v>
       </c>
@@ -12769,7 +13148,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>542</v>
       </c>
@@ -12831,7 +13210,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>542</v>
       </c>
@@ -12893,7 +13272,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>542</v>
       </c>
@@ -12964,7 +13343,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>549</v>
       </c>
@@ -13017,7 +13396,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>552</v>
       </c>
@@ -13082,7 +13461,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>552</v>
       </c>
@@ -13156,7 +13535,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>560</v>
       </c>
@@ -13230,7 +13609,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>564</v>
       </c>
@@ -13304,7 +13683,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>570</v>
       </c>
@@ -13378,7 +13757,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>576</v>
       </c>
@@ -13452,7 +13831,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>581</v>
       </c>
@@ -13526,7 +13905,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>587</v>
       </c>
@@ -13600,7 +13979,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>592</v>
       </c>
@@ -13674,7 +14053,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>598</v>
       </c>
@@ -13748,7 +14127,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>602</v>
       </c>
@@ -13813,7 +14192,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>602</v>
       </c>
@@ -13878,7 +14257,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>602</v>
       </c>
@@ -13952,7 +14331,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>610</v>
       </c>
@@ -14017,7 +14396,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>610</v>
       </c>
@@ -14091,7 +14470,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>617</v>
       </c>
@@ -14165,7 +14544,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>617</v>
       </c>
@@ -14242,7 +14621,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>617</v>
       </c>
@@ -14316,7 +14695,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B177" t="s">
         <v>632</v>
       </c>
@@ -14366,7 +14745,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
         <v>633</v>
       </c>
@@ -14416,7 +14795,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B179" t="s">
         <v>634</v>
       </c>
@@ -14466,7 +14845,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
         <v>637</v>
       </c>
@@ -14516,7 +14895,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B181" t="s">
         <v>638</v>
       </c>
@@ -14566,7 +14945,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
         <v>639</v>
       </c>
@@ -14616,7 +14995,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B183" t="s">
         <v>640</v>
       </c>
@@ -14666,7 +15045,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B184" t="s">
         <v>643</v>
       </c>
@@ -14716,7 +15095,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B185" t="s">
         <v>644</v>
       </c>
@@ -14766,7 +15145,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B186" t="s">
         <v>647</v>
       </c>
@@ -14816,7 +15195,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
         <v>648</v>
       </c>
@@ -14866,7 +15245,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
         <v>649</v>
       </c>
@@ -14916,7 +15295,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>650</v>
       </c>
@@ -14981,7 +15360,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>650</v>
       </c>
@@ -15055,7 +15434,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B191" t="s">
         <v>653</v>
       </c>
@@ -15105,7 +15484,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B192" t="s">
         <v>655</v>
       </c>
@@ -15167,7 +15546,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B193" t="s">
         <v>656</v>
       </c>
@@ -15217,7 +15596,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>659</v>
       </c>
@@ -15282,7 +15661,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>659</v>
       </c>
@@ -15356,7 +15735,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="196" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B196" t="s">
         <v>664</v>
       </c>
@@ -15406,7 +15785,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="197" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B197" t="s">
         <v>665</v>
       </c>
@@ -15456,7 +15835,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="198" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B198" t="s">
         <v>666</v>
       </c>
@@ -15506,7 +15885,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="199" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B199" t="s">
         <v>667</v>
       </c>
@@ -15556,7 +15935,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="200" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>668</v>
       </c>
@@ -15609,7 +15988,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="201" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>672</v>
       </c>
@@ -15662,7 +16041,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="202" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>676</v>
       </c>
@@ -15715,7 +16094,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>680</v>
       </c>
@@ -15780,7 +16159,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>680</v>
       </c>
@@ -15854,7 +16233,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>680</v>
       </c>
@@ -15928,7 +16307,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>688</v>
       </c>
@@ -15981,7 +16360,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>692</v>
       </c>
@@ -16055,7 +16434,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>698</v>
       </c>
@@ -16132,7 +16511,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>706</v>
       </c>
@@ -16209,7 +16588,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>712</v>
       </c>
@@ -16286,7 +16665,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>721</v>
       </c>
@@ -16363,7 +16742,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>727</v>
       </c>
@@ -16440,7 +16819,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>734</v>
       </c>
@@ -16517,7 +16896,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>741</v>
       </c>
@@ -16594,7 +16973,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>748</v>
       </c>
@@ -16671,7 +17050,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>754</v>
       </c>
@@ -16748,7 +17127,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>761</v>
       </c>
@@ -16822,7 +17201,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>761</v>
       </c>
@@ -16896,7 +17275,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>761</v>
       </c>
@@ -16973,7 +17352,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>761</v>
       </c>
@@ -17047,7 +17426,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>769</v>
       </c>
@@ -17124,7 +17503,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>774</v>
       </c>
@@ -17201,7 +17580,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>782</v>
       </c>
@@ -17275,7 +17654,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>782</v>
       </c>
@@ -17337,7 +17716,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>787</v>
       </c>
@@ -17414,7 +17793,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B226" t="s">
         <v>792</v>
       </c>
@@ -17464,7 +17843,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B227" t="s">
         <v>793</v>
       </c>
@@ -17514,7 +17893,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B228" t="s">
         <v>794</v>
       </c>
@@ -17564,7 +17943,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B229" t="s">
         <v>795</v>
       </c>
@@ -17614,7 +17993,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>796</v>
       </c>
@@ -17679,7 +18058,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>796</v>
       </c>
@@ -17753,7 +18132,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B232" t="s">
         <v>800</v>
       </c>
@@ -17803,7 +18182,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="233" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B233" t="s">
         <v>801</v>
       </c>
@@ -17853,7 +18232,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="234" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B234" t="s">
         <v>802</v>
       </c>
@@ -17903,7 +18282,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="235" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>803</v>
       </c>
@@ -17977,7 +18356,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="236" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>811</v>
       </c>
@@ -18054,7 +18433,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="237" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>819</v>
       </c>
@@ -18131,7 +18510,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="238" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>825</v>
       </c>
@@ -18208,7 +18587,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="239" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>830</v>
       </c>
@@ -18285,7 +18664,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="240" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>836</v>
       </c>
@@ -18362,7 +18741,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="241" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>843</v>
       </c>
@@ -18439,7 +18818,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="242" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>848</v>
       </c>
@@ -18516,7 +18895,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="243" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>854</v>
       </c>
@@ -18593,7 +18972,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="244" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>861</v>
       </c>
@@ -18670,7 +19049,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="245" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>865</v>
       </c>
@@ -18747,7 +19126,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="246" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>873</v>
       </c>
@@ -18824,7 +19203,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="247" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>879</v>
       </c>
@@ -18901,7 +19280,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="248" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>885</v>
       </c>
@@ -18978,7 +19357,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="249" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>892</v>
       </c>
@@ -19055,7 +19434,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="250" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>897</v>
       </c>
@@ -19132,7 +19511,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="251" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>903</v>
       </c>
@@ -19209,7 +19588,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>911</v>
       </c>
@@ -19286,7 +19665,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>919</v>
       </c>
@@ -19363,7 +19742,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>925</v>
       </c>
@@ -19440,7 +19819,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>932</v>
       </c>
@@ -19517,7 +19896,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>938</v>
       </c>
@@ -19591,7 +19970,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="257" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>943</v>
       </c>
@@ -19668,7 +20047,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>948</v>
       </c>
@@ -19745,7 +20124,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>952</v>
       </c>
@@ -19822,7 +20201,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>959</v>
       </c>
@@ -19899,7 +20278,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>963</v>
       </c>
@@ -19976,7 +20355,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>968</v>
       </c>
@@ -20053,7 +20432,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>974</v>
       </c>
@@ -20130,7 +20509,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>979</v>
       </c>
@@ -20207,7 +20586,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>984</v>
       </c>
@@ -20284,7 +20663,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>990</v>
       </c>
@@ -20361,7 +20740,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>999</v>
       </c>
@@ -20438,7 +20817,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>1004</v>
       </c>
@@ -20515,7 +20894,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>1008</v>
       </c>
@@ -20592,7 +20971,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>1014</v>
       </c>
@@ -20669,7 +21048,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>1020</v>
       </c>
@@ -20734,7 +21113,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>1024</v>
       </c>
@@ -20799,7 +21178,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>1028</v>
       </c>
@@ -20864,7 +21243,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>1033</v>
       </c>
@@ -20929,7 +21308,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>1033</v>
       </c>
@@ -20994,7 +21373,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>1036</v>
       </c>
@@ -21059,7 +21438,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>1039</v>
       </c>
@@ -21124,7 +21503,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>1039</v>
       </c>
@@ -21189,7 +21568,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>1043</v>
       </c>
@@ -21254,7 +21633,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>1043</v>
       </c>
@@ -21319,7 +21698,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>1046</v>
       </c>
@@ -21384,7 +21763,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>1049</v>
       </c>
@@ -21449,7 +21828,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>1053</v>
       </c>
@@ -21514,7 +21893,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="284" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>1057</v>
       </c>
@@ -21579,7 +21958,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>1057</v>
       </c>
@@ -21653,7 +22032,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>1057</v>
       </c>
@@ -21718,7 +22097,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="287" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>1062</v>
       </c>
@@ -21783,7 +22162,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>1065</v>
       </c>
@@ -21848,7 +22227,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>1070</v>
       </c>
@@ -21913,7 +22292,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>1073</v>
       </c>
@@ -21978,7 +22357,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>1077</v>
       </c>
@@ -22043,7 +22422,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="292" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>1081</v>
       </c>
@@ -22108,7 +22487,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>1085</v>
       </c>
@@ -22173,7 +22552,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>1090</v>
       </c>
@@ -22238,7 +22617,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>1093</v>
       </c>
@@ -22303,7 +22682,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>1097</v>
       </c>
@@ -22368,7 +22747,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>1101</v>
       </c>
@@ -22433,7 +22812,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>1105</v>
       </c>
@@ -22498,7 +22877,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>1109</v>
       </c>
@@ -22563,7 +22942,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>1113</v>
       </c>
@@ -22628,7 +23007,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>1117</v>
       </c>
@@ -22693,7 +23072,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>1122</v>
       </c>
@@ -22912,7 +23291,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="305" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>1138</v>
       </c>
@@ -22977,7 +23356,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="306" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>1138</v>
       </c>
@@ -23042,7 +23421,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="307" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>1138</v>
       </c>
@@ -23107,7 +23486,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>1138</v>
       </c>
@@ -24063,7 +24442,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="321" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>769</v>
       </c>
@@ -24137,7 +24516,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="322" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>1033</v>
       </c>
@@ -24211,7 +24590,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="323" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>1057</v>
       </c>
@@ -24285,7 +24664,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>581</v>
       </c>
@@ -24359,7 +24738,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>1046</v>
       </c>
@@ -24433,7 +24812,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>1113</v>
       </c>
@@ -24507,7 +24886,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="327" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>1020</v>
       </c>
@@ -24581,7 +24960,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="328" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>1200</v>
       </c>
@@ -24655,7 +25034,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="329" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>1144</v>
       </c>
@@ -24730,6 +25109,3762 @@
       </c>
       <c r="Y329" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="330" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B330" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C330">
+        <v>81936068968</v>
+      </c>
+      <c r="D330" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E330" t="s">
+        <v>922</v>
+      </c>
+      <c r="F330" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G330" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H330">
+        <v>1</v>
+      </c>
+      <c r="I330">
+        <v>2026</v>
+      </c>
+      <c r="J330" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K330" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L330" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M330" t="s">
+        <v>922</v>
+      </c>
+      <c r="N330" t="s">
+        <v>32</v>
+      </c>
+      <c r="O330" t="s">
+        <v>928</v>
+      </c>
+      <c r="P330" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q330">
+        <v>37</v>
+      </c>
+      <c r="R330" t="s">
+        <v>357</v>
+      </c>
+      <c r="S330" t="s">
+        <v>709</v>
+      </c>
+      <c r="T330" t="s">
+        <v>349</v>
+      </c>
+      <c r="U330" t="s">
+        <v>1214</v>
+      </c>
+      <c r="V330" t="s">
+        <v>1215</v>
+      </c>
+      <c r="Y330" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z330" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="331" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B331" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C331">
+        <v>81936068968</v>
+      </c>
+      <c r="D331" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E331" t="s">
+        <v>922</v>
+      </c>
+      <c r="F331" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G331" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H331">
+        <v>1</v>
+      </c>
+      <c r="I331">
+        <v>2026</v>
+      </c>
+      <c r="J331" t="s">
+        <v>1218</v>
+      </c>
+      <c r="K331" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L331" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M331" t="s">
+        <v>922</v>
+      </c>
+      <c r="N331" t="s">
+        <v>32</v>
+      </c>
+      <c r="O331" t="s">
+        <v>928</v>
+      </c>
+      <c r="P331" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q331">
+        <v>37</v>
+      </c>
+      <c r="R331" t="s">
+        <v>357</v>
+      </c>
+      <c r="S331" t="s">
+        <v>709</v>
+      </c>
+      <c r="T331" t="s">
+        <v>349</v>
+      </c>
+      <c r="U331" t="s">
+        <v>1214</v>
+      </c>
+      <c r="V331" t="s">
+        <v>1215</v>
+      </c>
+      <c r="Y331" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z331" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="332" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B332" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C332">
+        <v>895633180703</v>
+      </c>
+      <c r="D332" t="s">
+        <v>928</v>
+      </c>
+      <c r="E332" t="s">
+        <v>922</v>
+      </c>
+      <c r="F332" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G332" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H332">
+        <v>1</v>
+      </c>
+      <c r="I332">
+        <v>2026</v>
+      </c>
+      <c r="J332" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K332" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L332" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M332" t="s">
+        <v>922</v>
+      </c>
+      <c r="N332" t="s">
+        <v>32</v>
+      </c>
+      <c r="O332" t="s">
+        <v>928</v>
+      </c>
+      <c r="P332" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q332">
+        <v>26</v>
+      </c>
+      <c r="R332" t="s">
+        <v>555</v>
+      </c>
+      <c r="S332" t="s">
+        <v>1222</v>
+      </c>
+      <c r="T332" t="s">
+        <v>389</v>
+      </c>
+      <c r="U332" t="s">
+        <v>1223</v>
+      </c>
+      <c r="V332" t="s">
+        <v>1224</v>
+      </c>
+      <c r="Y332" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z332" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="333" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B333" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C333">
+        <v>895633180703</v>
+      </c>
+      <c r="D333" t="s">
+        <v>928</v>
+      </c>
+      <c r="E333" t="s">
+        <v>922</v>
+      </c>
+      <c r="F333" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G333" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H333">
+        <v>1</v>
+      </c>
+      <c r="I333">
+        <v>2026</v>
+      </c>
+      <c r="J333" t="s">
+        <v>1218</v>
+      </c>
+      <c r="K333" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L333" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M333" t="s">
+        <v>922</v>
+      </c>
+      <c r="N333" t="s">
+        <v>32</v>
+      </c>
+      <c r="O333" t="s">
+        <v>928</v>
+      </c>
+      <c r="P333" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q333">
+        <v>26</v>
+      </c>
+      <c r="R333" t="s">
+        <v>555</v>
+      </c>
+      <c r="S333" t="s">
+        <v>1222</v>
+      </c>
+      <c r="T333" t="s">
+        <v>389</v>
+      </c>
+      <c r="U333" t="s">
+        <v>1223</v>
+      </c>
+      <c r="V333" t="s">
+        <v>1224</v>
+      </c>
+      <c r="Y333" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z333" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="334" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B334" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C334">
+        <v>8119181841</v>
+      </c>
+      <c r="D334" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E334" t="s">
+        <v>922</v>
+      </c>
+      <c r="F334" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G334" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H334">
+        <v>1</v>
+      </c>
+      <c r="I334">
+        <v>2026</v>
+      </c>
+      <c r="J334" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K334" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L334" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M334" t="s">
+        <v>922</v>
+      </c>
+      <c r="N334" t="s">
+        <v>32</v>
+      </c>
+      <c r="O334" t="s">
+        <v>928</v>
+      </c>
+      <c r="P334" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q334">
+        <v>53</v>
+      </c>
+      <c r="R334" t="s">
+        <v>106</v>
+      </c>
+      <c r="S334" t="s">
+        <v>1227</v>
+      </c>
+      <c r="T334" t="s">
+        <v>349</v>
+      </c>
+      <c r="U334" t="s">
+        <v>1228</v>
+      </c>
+      <c r="V334" t="s">
+        <v>351</v>
+      </c>
+      <c r="Y334" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z334" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="335" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B335" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C335">
+        <v>8119181841</v>
+      </c>
+      <c r="D335" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E335" t="s">
+        <v>922</v>
+      </c>
+      <c r="F335" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G335" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H335">
+        <v>1</v>
+      </c>
+      <c r="I335">
+        <v>2026</v>
+      </c>
+      <c r="J335" t="s">
+        <v>1218</v>
+      </c>
+      <c r="K335" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L335" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M335" t="s">
+        <v>922</v>
+      </c>
+      <c r="N335" t="s">
+        <v>32</v>
+      </c>
+      <c r="O335" t="s">
+        <v>928</v>
+      </c>
+      <c r="P335" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q335">
+        <v>53</v>
+      </c>
+      <c r="R335" t="s">
+        <v>106</v>
+      </c>
+      <c r="S335" t="s">
+        <v>1227</v>
+      </c>
+      <c r="T335" t="s">
+        <v>349</v>
+      </c>
+      <c r="U335" t="s">
+        <v>1228</v>
+      </c>
+      <c r="V335" t="s">
+        <v>351</v>
+      </c>
+      <c r="Y335" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z335" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="336" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B336" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C336">
+        <v>81239172976</v>
+      </c>
+      <c r="D336" t="s">
+        <v>922</v>
+      </c>
+      <c r="E336" t="s">
+        <v>922</v>
+      </c>
+      <c r="F336" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G336" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H336">
+        <v>1</v>
+      </c>
+      <c r="I336">
+        <v>2026</v>
+      </c>
+      <c r="J336" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K336" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L336" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M336" t="s">
+        <v>922</v>
+      </c>
+      <c r="N336" t="s">
+        <v>44</v>
+      </c>
+      <c r="O336" t="s">
+        <v>928</v>
+      </c>
+      <c r="P336" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q336">
+        <v>33</v>
+      </c>
+      <c r="R336" t="s">
+        <v>555</v>
+      </c>
+      <c r="S336" t="s">
+        <v>946</v>
+      </c>
+      <c r="T336" t="s">
+        <v>389</v>
+      </c>
+      <c r="U336" t="s">
+        <v>1231</v>
+      </c>
+      <c r="V336" t="s">
+        <v>1232</v>
+      </c>
+      <c r="Y336" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z336" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="337" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B337" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C337">
+        <v>81239172976</v>
+      </c>
+      <c r="D337" t="s">
+        <v>922</v>
+      </c>
+      <c r="E337" t="s">
+        <v>922</v>
+      </c>
+      <c r="F337" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G337" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H337">
+        <v>1</v>
+      </c>
+      <c r="I337">
+        <v>2026</v>
+      </c>
+      <c r="J337" t="s">
+        <v>1218</v>
+      </c>
+      <c r="K337" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L337" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M337" t="s">
+        <v>922</v>
+      </c>
+      <c r="N337" t="s">
+        <v>44</v>
+      </c>
+      <c r="O337" t="s">
+        <v>928</v>
+      </c>
+      <c r="P337" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q337">
+        <v>33</v>
+      </c>
+      <c r="R337" t="s">
+        <v>555</v>
+      </c>
+      <c r="S337" t="s">
+        <v>946</v>
+      </c>
+      <c r="T337" t="s">
+        <v>389</v>
+      </c>
+      <c r="U337" t="s">
+        <v>1231</v>
+      </c>
+      <c r="V337" t="s">
+        <v>1232</v>
+      </c>
+      <c r="Y337" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z337" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="338" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B338" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C338">
+        <v>81353641636</v>
+      </c>
+      <c r="D338" t="s">
+        <v>928</v>
+      </c>
+      <c r="E338" t="s">
+        <v>922</v>
+      </c>
+      <c r="F338" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G338" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H338">
+        <v>1</v>
+      </c>
+      <c r="I338">
+        <v>2026</v>
+      </c>
+      <c r="J338" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K338" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L338" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M338" t="s">
+        <v>922</v>
+      </c>
+      <c r="N338" t="s">
+        <v>32</v>
+      </c>
+      <c r="O338" t="s">
+        <v>928</v>
+      </c>
+      <c r="P338" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q338">
+        <v>48</v>
+      </c>
+      <c r="R338" t="s">
+        <v>106</v>
+      </c>
+      <c r="S338" t="s">
+        <v>1235</v>
+      </c>
+      <c r="T338" t="s">
+        <v>349</v>
+      </c>
+      <c r="U338" t="s">
+        <v>1236</v>
+      </c>
+      <c r="V338" t="s">
+        <v>1215</v>
+      </c>
+      <c r="Y338" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z338" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="339" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B339" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C339">
+        <v>81353641636</v>
+      </c>
+      <c r="D339" t="s">
+        <v>928</v>
+      </c>
+      <c r="E339" t="s">
+        <v>922</v>
+      </c>
+      <c r="F339" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G339" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H339">
+        <v>1</v>
+      </c>
+      <c r="I339">
+        <v>2026</v>
+      </c>
+      <c r="J339" t="s">
+        <v>1218</v>
+      </c>
+      <c r="K339" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L339" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M339" t="s">
+        <v>922</v>
+      </c>
+      <c r="N339" t="s">
+        <v>32</v>
+      </c>
+      <c r="O339" t="s">
+        <v>928</v>
+      </c>
+      <c r="P339" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q339">
+        <v>48</v>
+      </c>
+      <c r="R339" t="s">
+        <v>106</v>
+      </c>
+      <c r="S339" t="s">
+        <v>1235</v>
+      </c>
+      <c r="T339" t="s">
+        <v>349</v>
+      </c>
+      <c r="U339" t="s">
+        <v>1236</v>
+      </c>
+      <c r="V339" t="s">
+        <v>1215</v>
+      </c>
+      <c r="Y339" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z339" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="340" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B340" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C340">
+        <v>87860841408</v>
+      </c>
+      <c r="D340" t="s">
+        <v>922</v>
+      </c>
+      <c r="E340" t="s">
+        <v>922</v>
+      </c>
+      <c r="F340" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G340" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H340">
+        <v>1</v>
+      </c>
+      <c r="I340">
+        <v>2026</v>
+      </c>
+      <c r="J340" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K340" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L340" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M340" t="s">
+        <v>922</v>
+      </c>
+      <c r="N340" t="s">
+        <v>44</v>
+      </c>
+      <c r="O340" t="s">
+        <v>928</v>
+      </c>
+      <c r="P340" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q340">
+        <v>29</v>
+      </c>
+      <c r="R340" t="s">
+        <v>555</v>
+      </c>
+      <c r="S340" t="s">
+        <v>473</v>
+      </c>
+      <c r="T340" t="s">
+        <v>349</v>
+      </c>
+      <c r="U340" t="s">
+        <v>1239</v>
+      </c>
+      <c r="V340" t="s">
+        <v>1215</v>
+      </c>
+      <c r="Y340" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z340" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="341" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B341" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C341">
+        <v>87851550728</v>
+      </c>
+      <c r="D341" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E341" t="s">
+        <v>922</v>
+      </c>
+      <c r="F341" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G341" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H341">
+        <v>1</v>
+      </c>
+      <c r="I341">
+        <v>2026</v>
+      </c>
+      <c r="J341" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K341" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L341" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M341" t="s">
+        <v>922</v>
+      </c>
+      <c r="N341" t="s">
+        <v>32</v>
+      </c>
+      <c r="O341" t="s">
+        <v>994</v>
+      </c>
+      <c r="P341" t="s">
+        <v>995</v>
+      </c>
+      <c r="Q341">
+        <v>35</v>
+      </c>
+      <c r="R341" t="s">
+        <v>555</v>
+      </c>
+      <c r="S341" t="s">
+        <v>1243</v>
+      </c>
+      <c r="T341" t="s">
+        <v>349</v>
+      </c>
+      <c r="U341" t="s">
+        <v>1244</v>
+      </c>
+      <c r="V341" t="s">
+        <v>1232</v>
+      </c>
+      <c r="Y341" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z341" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="342" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B342" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C342">
+        <v>87851550728</v>
+      </c>
+      <c r="D342" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E342" t="s">
+        <v>922</v>
+      </c>
+      <c r="F342" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G342" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H342">
+        <v>1</v>
+      </c>
+      <c r="I342">
+        <v>2026</v>
+      </c>
+      <c r="J342" t="s">
+        <v>1218</v>
+      </c>
+      <c r="K342" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L342" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M342" t="s">
+        <v>922</v>
+      </c>
+      <c r="N342" t="s">
+        <v>32</v>
+      </c>
+      <c r="O342" t="s">
+        <v>994</v>
+      </c>
+      <c r="P342" t="s">
+        <v>995</v>
+      </c>
+      <c r="Q342">
+        <v>35</v>
+      </c>
+      <c r="R342" t="s">
+        <v>555</v>
+      </c>
+      <c r="S342" t="s">
+        <v>1243</v>
+      </c>
+      <c r="T342" t="s">
+        <v>349</v>
+      </c>
+      <c r="U342" t="s">
+        <v>1244</v>
+      </c>
+      <c r="V342" t="s">
+        <v>1232</v>
+      </c>
+      <c r="Y342" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z342" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="343" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B343" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C343">
+        <v>818343977</v>
+      </c>
+      <c r="D343" t="s">
+        <v>928</v>
+      </c>
+      <c r="E343" t="s">
+        <v>922</v>
+      </c>
+      <c r="F343" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G343" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H343">
+        <v>1</v>
+      </c>
+      <c r="I343">
+        <v>2026</v>
+      </c>
+      <c r="J343" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K343" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L343" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M343" t="s">
+        <v>922</v>
+      </c>
+      <c r="N343" t="s">
+        <v>32</v>
+      </c>
+      <c r="O343" t="s">
+        <v>928</v>
+      </c>
+      <c r="P343" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q343">
+        <v>49</v>
+      </c>
+      <c r="R343" t="s">
+        <v>106</v>
+      </c>
+      <c r="S343" t="s">
+        <v>1134</v>
+      </c>
+      <c r="T343" t="s">
+        <v>108</v>
+      </c>
+      <c r="U343" t="s">
+        <v>1247</v>
+      </c>
+      <c r="V343" t="s">
+        <v>1232</v>
+      </c>
+      <c r="Y343" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z343" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="344" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B344" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C344">
+        <v>818343977</v>
+      </c>
+      <c r="D344" t="s">
+        <v>928</v>
+      </c>
+      <c r="E344" t="s">
+        <v>922</v>
+      </c>
+      <c r="F344" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G344" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H344">
+        <v>1</v>
+      </c>
+      <c r="I344">
+        <v>2026</v>
+      </c>
+      <c r="J344" t="s">
+        <v>1218</v>
+      </c>
+      <c r="K344" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L344" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M344" t="s">
+        <v>922</v>
+      </c>
+      <c r="N344" t="s">
+        <v>32</v>
+      </c>
+      <c r="O344" t="s">
+        <v>928</v>
+      </c>
+      <c r="P344" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q344">
+        <v>49</v>
+      </c>
+      <c r="R344" t="s">
+        <v>106</v>
+      </c>
+      <c r="S344" t="s">
+        <v>1134</v>
+      </c>
+      <c r="T344" t="s">
+        <v>108</v>
+      </c>
+      <c r="U344" t="s">
+        <v>1247</v>
+      </c>
+      <c r="V344" t="s">
+        <v>1232</v>
+      </c>
+      <c r="Y344" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z344" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="345" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B345" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C345">
+        <v>81999232420</v>
+      </c>
+      <c r="D345" t="s">
+        <v>928</v>
+      </c>
+      <c r="E345" t="s">
+        <v>922</v>
+      </c>
+      <c r="F345" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G345" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H345">
+        <v>1</v>
+      </c>
+      <c r="I345">
+        <v>2026</v>
+      </c>
+      <c r="J345" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K345" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L345" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M345" t="s">
+        <v>922</v>
+      </c>
+      <c r="N345" t="s">
+        <v>32</v>
+      </c>
+      <c r="O345" t="s">
+        <v>928</v>
+      </c>
+      <c r="P345" t="s">
+        <v>922</v>
+      </c>
+      <c r="S345" t="s">
+        <v>716</v>
+      </c>
+      <c r="T345" t="s">
+        <v>717</v>
+      </c>
+      <c r="V345" t="s">
+        <v>333</v>
+      </c>
+      <c r="Y345" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z345" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="346" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B346" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C346">
+        <v>81999232420</v>
+      </c>
+      <c r="D346" t="s">
+        <v>928</v>
+      </c>
+      <c r="E346" t="s">
+        <v>922</v>
+      </c>
+      <c r="F346" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G346" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H346">
+        <v>1</v>
+      </c>
+      <c r="I346">
+        <v>2026</v>
+      </c>
+      <c r="J346" t="s">
+        <v>1218</v>
+      </c>
+      <c r="K346" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L346" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M346" t="s">
+        <v>922</v>
+      </c>
+      <c r="N346" t="s">
+        <v>32</v>
+      </c>
+      <c r="O346" t="s">
+        <v>928</v>
+      </c>
+      <c r="P346" t="s">
+        <v>922</v>
+      </c>
+      <c r="S346" t="s">
+        <v>716</v>
+      </c>
+      <c r="T346" t="s">
+        <v>717</v>
+      </c>
+      <c r="V346" t="s">
+        <v>333</v>
+      </c>
+      <c r="Y346" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z346" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="347" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B347" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C347">
+        <v>85893608348</v>
+      </c>
+      <c r="D347" t="s">
+        <v>410</v>
+      </c>
+      <c r="E347" t="s">
+        <v>410</v>
+      </c>
+      <c r="F347" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G347" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H347">
+        <v>1</v>
+      </c>
+      <c r="I347">
+        <v>2026</v>
+      </c>
+      <c r="J347" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K347" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L347" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M347" t="s">
+        <v>410</v>
+      </c>
+      <c r="N347" t="s">
+        <v>32</v>
+      </c>
+      <c r="O347" t="s">
+        <v>410</v>
+      </c>
+      <c r="P347" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q347">
+        <v>47</v>
+      </c>
+      <c r="R347" t="s">
+        <v>106</v>
+      </c>
+      <c r="S347" t="s">
+        <v>1254</v>
+      </c>
+      <c r="T347" t="s">
+        <v>349</v>
+      </c>
+      <c r="U347" t="s">
+        <v>1255</v>
+      </c>
+      <c r="V347" t="s">
+        <v>1256</v>
+      </c>
+      <c r="Y347" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z347" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="348" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B348" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C348">
+        <v>85893608348</v>
+      </c>
+      <c r="D348" t="s">
+        <v>410</v>
+      </c>
+      <c r="E348" t="s">
+        <v>410</v>
+      </c>
+      <c r="F348" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G348" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H348">
+        <v>1</v>
+      </c>
+      <c r="I348">
+        <v>2026</v>
+      </c>
+      <c r="J348" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K348" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L348" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M348" t="s">
+        <v>410</v>
+      </c>
+      <c r="N348" t="s">
+        <v>32</v>
+      </c>
+      <c r="O348" t="s">
+        <v>410</v>
+      </c>
+      <c r="P348" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q348">
+        <v>47</v>
+      </c>
+      <c r="R348" t="s">
+        <v>106</v>
+      </c>
+      <c r="S348" t="s">
+        <v>1254</v>
+      </c>
+      <c r="T348" t="s">
+        <v>349</v>
+      </c>
+      <c r="U348" t="s">
+        <v>1255</v>
+      </c>
+      <c r="V348" t="s">
+        <v>1256</v>
+      </c>
+      <c r="Y348" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z348" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="349" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B349" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C349">
+        <v>8176060414</v>
+      </c>
+      <c r="D349" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E349" t="s">
+        <v>410</v>
+      </c>
+      <c r="F349" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G349" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H349">
+        <v>1</v>
+      </c>
+      <c r="I349">
+        <v>2026</v>
+      </c>
+      <c r="J349" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K349" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L349" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M349" t="s">
+        <v>410</v>
+      </c>
+      <c r="N349" t="s">
+        <v>32</v>
+      </c>
+      <c r="O349" t="s">
+        <v>405</v>
+      </c>
+      <c r="P349" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q349">
+        <v>27</v>
+      </c>
+      <c r="R349" t="s">
+        <v>555</v>
+      </c>
+      <c r="S349" t="s">
+        <v>1261</v>
+      </c>
+      <c r="T349" t="s">
+        <v>349</v>
+      </c>
+      <c r="U349" t="s">
+        <v>1262</v>
+      </c>
+      <c r="V349" t="s">
+        <v>1215</v>
+      </c>
+      <c r="Y349" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z349" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="350" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C350">
+        <v>8176060414</v>
+      </c>
+      <c r="D350" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E350" t="s">
+        <v>410</v>
+      </c>
+      <c r="F350" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G350" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H350">
+        <v>1</v>
+      </c>
+      <c r="I350">
+        <v>2026</v>
+      </c>
+      <c r="J350" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K350" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L350" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M350" t="s">
+        <v>410</v>
+      </c>
+      <c r="N350" t="s">
+        <v>32</v>
+      </c>
+      <c r="O350" t="s">
+        <v>405</v>
+      </c>
+      <c r="P350" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q350">
+        <v>27</v>
+      </c>
+      <c r="R350" t="s">
+        <v>555</v>
+      </c>
+      <c r="S350" t="s">
+        <v>1261</v>
+      </c>
+      <c r="T350" t="s">
+        <v>349</v>
+      </c>
+      <c r="U350" t="s">
+        <v>1262</v>
+      </c>
+      <c r="V350" t="s">
+        <v>1215</v>
+      </c>
+      <c r="Y350" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z350" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="351" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B351" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C351">
+        <v>81977104084</v>
+      </c>
+      <c r="D351" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E351" t="s">
+        <v>410</v>
+      </c>
+      <c r="F351" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G351" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H351">
+        <v>1</v>
+      </c>
+      <c r="I351">
+        <v>2026</v>
+      </c>
+      <c r="J351" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K351" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L351" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M351" t="s">
+        <v>410</v>
+      </c>
+      <c r="N351" t="s">
+        <v>32</v>
+      </c>
+      <c r="O351" t="s">
+        <v>1265</v>
+      </c>
+      <c r="P351" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q351">
+        <v>37</v>
+      </c>
+      <c r="R351" t="s">
+        <v>357</v>
+      </c>
+      <c r="S351" t="s">
+        <v>790</v>
+      </c>
+      <c r="T351" t="s">
+        <v>349</v>
+      </c>
+      <c r="U351" t="s">
+        <v>1266</v>
+      </c>
+      <c r="V351" t="s">
+        <v>1267</v>
+      </c>
+      <c r="Y351" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z351" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="352" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B352" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C352">
+        <v>81977104084</v>
+      </c>
+      <c r="D352" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E352" t="s">
+        <v>410</v>
+      </c>
+      <c r="F352" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G352" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H352">
+        <v>1</v>
+      </c>
+      <c r="I352">
+        <v>2026</v>
+      </c>
+      <c r="J352" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K352" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L352" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M352" t="s">
+        <v>410</v>
+      </c>
+      <c r="N352" t="s">
+        <v>32</v>
+      </c>
+      <c r="O352" t="s">
+        <v>1265</v>
+      </c>
+      <c r="P352" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q352">
+        <v>37</v>
+      </c>
+      <c r="R352" t="s">
+        <v>357</v>
+      </c>
+      <c r="S352" t="s">
+        <v>790</v>
+      </c>
+      <c r="T352" t="s">
+        <v>349</v>
+      </c>
+      <c r="U352" t="s">
+        <v>1266</v>
+      </c>
+      <c r="V352" t="s">
+        <v>1267</v>
+      </c>
+      <c r="Y352" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z352" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="353" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B353" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C353">
+        <v>819674066</v>
+      </c>
+      <c r="D353" t="s">
+        <v>410</v>
+      </c>
+      <c r="E353" t="s">
+        <v>410</v>
+      </c>
+      <c r="F353" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G353" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H353">
+        <v>1</v>
+      </c>
+      <c r="I353">
+        <v>2026</v>
+      </c>
+      <c r="J353" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K353" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L353" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M353" t="s">
+        <v>410</v>
+      </c>
+      <c r="N353" t="s">
+        <v>32</v>
+      </c>
+      <c r="O353" t="s">
+        <v>410</v>
+      </c>
+      <c r="P353" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q353">
+        <v>39</v>
+      </c>
+      <c r="R353" t="s">
+        <v>357</v>
+      </c>
+      <c r="S353" t="s">
+        <v>1270</v>
+      </c>
+      <c r="T353" t="s">
+        <v>349</v>
+      </c>
+      <c r="U353" t="s">
+        <v>1271</v>
+      </c>
+      <c r="V353" t="s">
+        <v>1267</v>
+      </c>
+      <c r="Y353" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z353" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="354" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B354" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C354">
+        <v>819674066</v>
+      </c>
+      <c r="D354" t="s">
+        <v>410</v>
+      </c>
+      <c r="E354" t="s">
+        <v>410</v>
+      </c>
+      <c r="F354" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G354" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H354">
+        <v>1</v>
+      </c>
+      <c r="I354">
+        <v>2026</v>
+      </c>
+      <c r="J354" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K354" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L354" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M354" t="s">
+        <v>410</v>
+      </c>
+      <c r="N354" t="s">
+        <v>32</v>
+      </c>
+      <c r="O354" t="s">
+        <v>410</v>
+      </c>
+      <c r="P354" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q354">
+        <v>39</v>
+      </c>
+      <c r="R354" t="s">
+        <v>357</v>
+      </c>
+      <c r="S354" t="s">
+        <v>1270</v>
+      </c>
+      <c r="T354" t="s">
+        <v>349</v>
+      </c>
+      <c r="U354" t="s">
+        <v>1271</v>
+      </c>
+      <c r="V354" t="s">
+        <v>1267</v>
+      </c>
+      <c r="Y354" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z354" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="355" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B355" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C355">
+        <v>85156922599</v>
+      </c>
+      <c r="D355" t="s">
+        <v>562</v>
+      </c>
+      <c r="E355" t="s">
+        <v>410</v>
+      </c>
+      <c r="F355" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G355" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H355">
+        <v>1</v>
+      </c>
+      <c r="I355">
+        <v>2026</v>
+      </c>
+      <c r="J355" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K355" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L355" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M355" t="s">
+        <v>410</v>
+      </c>
+      <c r="N355" t="s">
+        <v>32</v>
+      </c>
+      <c r="O355" t="s">
+        <v>554</v>
+      </c>
+      <c r="P355" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q355">
+        <v>26</v>
+      </c>
+      <c r="R355" t="s">
+        <v>555</v>
+      </c>
+      <c r="S355" t="s">
+        <v>1274</v>
+      </c>
+      <c r="T355" t="s">
+        <v>349</v>
+      </c>
+      <c r="U355" t="s">
+        <v>1275</v>
+      </c>
+      <c r="V355" t="s">
+        <v>1267</v>
+      </c>
+      <c r="Y355" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z355" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="356" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B356" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C356">
+        <v>85156922599</v>
+      </c>
+      <c r="D356" t="s">
+        <v>562</v>
+      </c>
+      <c r="E356" t="s">
+        <v>410</v>
+      </c>
+      <c r="F356" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G356" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H356">
+        <v>1</v>
+      </c>
+      <c r="I356">
+        <v>2026</v>
+      </c>
+      <c r="J356" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K356" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L356" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M356" t="s">
+        <v>410</v>
+      </c>
+      <c r="N356" t="s">
+        <v>32</v>
+      </c>
+      <c r="O356" t="s">
+        <v>554</v>
+      </c>
+      <c r="P356" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q356">
+        <v>26</v>
+      </c>
+      <c r="R356" t="s">
+        <v>555</v>
+      </c>
+      <c r="S356" t="s">
+        <v>1274</v>
+      </c>
+      <c r="T356" t="s">
+        <v>349</v>
+      </c>
+      <c r="U356" t="s">
+        <v>1275</v>
+      </c>
+      <c r="V356" t="s">
+        <v>1267</v>
+      </c>
+      <c r="Y356" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z356" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="357" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B357" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C357">
+        <v>61406754067</v>
+      </c>
+      <c r="D357" t="s">
+        <v>251</v>
+      </c>
+      <c r="E357" t="s">
+        <v>410</v>
+      </c>
+      <c r="F357" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G357" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H357">
+        <v>1</v>
+      </c>
+      <c r="I357">
+        <v>2026</v>
+      </c>
+      <c r="J357" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K357" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L357" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M357" t="s">
+        <v>410</v>
+      </c>
+      <c r="N357" t="s">
+        <v>32</v>
+      </c>
+      <c r="O357" t="s">
+        <v>251</v>
+      </c>
+      <c r="P357" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q357">
+        <v>40</v>
+      </c>
+      <c r="R357" t="s">
+        <v>357</v>
+      </c>
+      <c r="S357" t="s">
+        <v>1042</v>
+      </c>
+      <c r="T357" t="s">
+        <v>349</v>
+      </c>
+      <c r="U357" t="s">
+        <v>1278</v>
+      </c>
+      <c r="V357" t="s">
+        <v>1215</v>
+      </c>
+      <c r="Y357" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z357" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="358" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B358" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C358">
+        <v>8816755454</v>
+      </c>
+      <c r="D358" t="s">
+        <v>257</v>
+      </c>
+      <c r="E358" t="s">
+        <v>410</v>
+      </c>
+      <c r="F358" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G358" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H358">
+        <v>1</v>
+      </c>
+      <c r="I358">
+        <v>2026</v>
+      </c>
+      <c r="J358" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K358" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L358" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M358" t="s">
+        <v>410</v>
+      </c>
+      <c r="N358" t="s">
+        <v>32</v>
+      </c>
+      <c r="O358" t="s">
+        <v>257</v>
+      </c>
+      <c r="P358" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q358">
+        <v>44</v>
+      </c>
+      <c r="R358" t="s">
+        <v>357</v>
+      </c>
+      <c r="S358" t="s">
+        <v>1042</v>
+      </c>
+      <c r="T358" t="s">
+        <v>349</v>
+      </c>
+      <c r="U358" t="s">
+        <v>1281</v>
+      </c>
+      <c r="V358" t="s">
+        <v>569</v>
+      </c>
+      <c r="Y358" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z358" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="359" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B359" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C359">
+        <v>8816755454</v>
+      </c>
+      <c r="D359" t="s">
+        <v>257</v>
+      </c>
+      <c r="E359" t="s">
+        <v>410</v>
+      </c>
+      <c r="F359" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G359" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H359">
+        <v>1</v>
+      </c>
+      <c r="I359">
+        <v>2026</v>
+      </c>
+      <c r="J359" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K359" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L359" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M359" t="s">
+        <v>410</v>
+      </c>
+      <c r="N359" t="s">
+        <v>32</v>
+      </c>
+      <c r="O359" t="s">
+        <v>257</v>
+      </c>
+      <c r="P359" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q359">
+        <v>44</v>
+      </c>
+      <c r="R359" t="s">
+        <v>357</v>
+      </c>
+      <c r="S359" t="s">
+        <v>1042</v>
+      </c>
+      <c r="T359" t="s">
+        <v>349</v>
+      </c>
+      <c r="U359" t="s">
+        <v>1281</v>
+      </c>
+      <c r="V359" t="s">
+        <v>569</v>
+      </c>
+      <c r="Y359" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z359" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="360" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B360" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C360">
+        <v>81294973639</v>
+      </c>
+      <c r="D360" t="s">
+        <v>257</v>
+      </c>
+      <c r="E360" t="s">
+        <v>410</v>
+      </c>
+      <c r="F360" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G360" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H360">
+        <v>1</v>
+      </c>
+      <c r="I360">
+        <v>2026</v>
+      </c>
+      <c r="J360" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K360" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L360" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M360" t="s">
+        <v>410</v>
+      </c>
+      <c r="N360" t="s">
+        <v>32</v>
+      </c>
+      <c r="O360" t="s">
+        <v>257</v>
+      </c>
+      <c r="P360" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q360">
+        <v>52</v>
+      </c>
+      <c r="R360" t="s">
+        <v>106</v>
+      </c>
+      <c r="S360" t="s">
+        <v>1284</v>
+      </c>
+      <c r="T360" t="s">
+        <v>108</v>
+      </c>
+      <c r="U360" t="s">
+        <v>1285</v>
+      </c>
+      <c r="V360" t="s">
+        <v>1149</v>
+      </c>
+      <c r="Y360" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z360" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="361" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B361" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C361">
+        <v>81294973639</v>
+      </c>
+      <c r="D361" t="s">
+        <v>257</v>
+      </c>
+      <c r="E361" t="s">
+        <v>410</v>
+      </c>
+      <c r="F361" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G361" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H361">
+        <v>1</v>
+      </c>
+      <c r="I361">
+        <v>2026</v>
+      </c>
+      <c r="J361" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K361" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L361" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M361" t="s">
+        <v>410</v>
+      </c>
+      <c r="N361" t="s">
+        <v>32</v>
+      </c>
+      <c r="O361" t="s">
+        <v>257</v>
+      </c>
+      <c r="P361" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q361">
+        <v>52</v>
+      </c>
+      <c r="R361" t="s">
+        <v>106</v>
+      </c>
+      <c r="S361" t="s">
+        <v>1284</v>
+      </c>
+      <c r="T361" t="s">
+        <v>108</v>
+      </c>
+      <c r="U361" t="s">
+        <v>1285</v>
+      </c>
+      <c r="V361" t="s">
+        <v>1149</v>
+      </c>
+      <c r="Y361" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z361" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="362" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B362" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C362">
+        <v>81287153815</v>
+      </c>
+      <c r="D362" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E362" t="s">
+        <v>410</v>
+      </c>
+      <c r="F362" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G362" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H362">
+        <v>1</v>
+      </c>
+      <c r="I362">
+        <v>2026</v>
+      </c>
+      <c r="J362" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K362" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L362" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M362" t="s">
+        <v>410</v>
+      </c>
+      <c r="N362" t="s">
+        <v>32</v>
+      </c>
+      <c r="O362" t="s">
+        <v>405</v>
+      </c>
+      <c r="P362" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q362">
+        <v>37</v>
+      </c>
+      <c r="R362" t="s">
+        <v>357</v>
+      </c>
+      <c r="S362" t="s">
+        <v>1289</v>
+      </c>
+      <c r="T362" t="s">
+        <v>349</v>
+      </c>
+      <c r="U362" t="s">
+        <v>1290</v>
+      </c>
+      <c r="V362" t="s">
+        <v>1149</v>
+      </c>
+      <c r="Y362" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z362" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="363" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B363" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C363">
+        <v>81287153815</v>
+      </c>
+      <c r="D363" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E363" t="s">
+        <v>410</v>
+      </c>
+      <c r="F363" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G363" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H363">
+        <v>1</v>
+      </c>
+      <c r="I363">
+        <v>2026</v>
+      </c>
+      <c r="J363" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K363" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L363" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M363" t="s">
+        <v>410</v>
+      </c>
+      <c r="N363" t="s">
+        <v>32</v>
+      </c>
+      <c r="O363" t="s">
+        <v>405</v>
+      </c>
+      <c r="P363" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q363">
+        <v>37</v>
+      </c>
+      <c r="R363" t="s">
+        <v>357</v>
+      </c>
+      <c r="S363" t="s">
+        <v>1289</v>
+      </c>
+      <c r="T363" t="s">
+        <v>349</v>
+      </c>
+      <c r="U363" t="s">
+        <v>1290</v>
+      </c>
+      <c r="V363" t="s">
+        <v>1149</v>
+      </c>
+      <c r="Y363" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z363" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="364" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B364" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C364">
+        <v>82123566486</v>
+      </c>
+      <c r="D364" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E364" t="s">
+        <v>410</v>
+      </c>
+      <c r="F364" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G364" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H364">
+        <v>1</v>
+      </c>
+      <c r="I364">
+        <v>2026</v>
+      </c>
+      <c r="J364" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K364" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L364" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M364" t="s">
+        <v>410</v>
+      </c>
+      <c r="N364" t="s">
+        <v>32</v>
+      </c>
+      <c r="O364" t="s">
+        <v>1293</v>
+      </c>
+      <c r="P364" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q364">
+        <v>39</v>
+      </c>
+      <c r="R364" t="s">
+        <v>357</v>
+      </c>
+      <c r="S364" t="s">
+        <v>1294</v>
+      </c>
+      <c r="T364" t="s">
+        <v>349</v>
+      </c>
+      <c r="U364" t="s">
+        <v>1295</v>
+      </c>
+      <c r="V364" t="s">
+        <v>359</v>
+      </c>
+      <c r="Y364" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z364" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="365" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B365" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C365">
+        <v>82123566486</v>
+      </c>
+      <c r="D365" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E365" t="s">
+        <v>410</v>
+      </c>
+      <c r="F365" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G365" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H365">
+        <v>1</v>
+      </c>
+      <c r="I365">
+        <v>2026</v>
+      </c>
+      <c r="J365" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K365" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L365" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M365" t="s">
+        <v>410</v>
+      </c>
+      <c r="N365" t="s">
+        <v>32</v>
+      </c>
+      <c r="O365" t="s">
+        <v>1293</v>
+      </c>
+      <c r="P365" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q365">
+        <v>39</v>
+      </c>
+      <c r="R365" t="s">
+        <v>357</v>
+      </c>
+      <c r="S365" t="s">
+        <v>1294</v>
+      </c>
+      <c r="T365" t="s">
+        <v>349</v>
+      </c>
+      <c r="U365" t="s">
+        <v>1295</v>
+      </c>
+      <c r="V365" t="s">
+        <v>359</v>
+      </c>
+      <c r="Y365" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z365" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="366" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B366" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C366">
+        <v>89505630900</v>
+      </c>
+      <c r="D366" t="s">
+        <v>410</v>
+      </c>
+      <c r="E366" t="s">
+        <v>410</v>
+      </c>
+      <c r="F366" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G366" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H366">
+        <v>1</v>
+      </c>
+      <c r="I366">
+        <v>2026</v>
+      </c>
+      <c r="J366" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K366" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L366" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M366" t="s">
+        <v>410</v>
+      </c>
+      <c r="N366" t="s">
+        <v>32</v>
+      </c>
+      <c r="O366" t="s">
+        <v>410</v>
+      </c>
+      <c r="P366" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q366">
+        <v>34</v>
+      </c>
+      <c r="R366" t="s">
+        <v>555</v>
+      </c>
+      <c r="S366" t="s">
+        <v>709</v>
+      </c>
+      <c r="T366" t="s">
+        <v>349</v>
+      </c>
+      <c r="U366" t="s">
+        <v>1298</v>
+      </c>
+      <c r="V366" t="s">
+        <v>359</v>
+      </c>
+      <c r="Y366" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z366" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="367" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B367" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C367">
+        <v>89505630900</v>
+      </c>
+      <c r="D367" t="s">
+        <v>410</v>
+      </c>
+      <c r="E367" t="s">
+        <v>410</v>
+      </c>
+      <c r="F367" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G367" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H367">
+        <v>1</v>
+      </c>
+      <c r="I367">
+        <v>2026</v>
+      </c>
+      <c r="J367" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K367" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L367" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M367" t="s">
+        <v>410</v>
+      </c>
+      <c r="N367" t="s">
+        <v>32</v>
+      </c>
+      <c r="O367" t="s">
+        <v>410</v>
+      </c>
+      <c r="P367" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q367">
+        <v>34</v>
+      </c>
+      <c r="R367" t="s">
+        <v>555</v>
+      </c>
+      <c r="S367" t="s">
+        <v>709</v>
+      </c>
+      <c r="T367" t="s">
+        <v>349</v>
+      </c>
+      <c r="U367" t="s">
+        <v>1298</v>
+      </c>
+      <c r="V367" t="s">
+        <v>359</v>
+      </c>
+      <c r="Y367" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z367" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="368" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B368" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C368">
+        <v>81384668727</v>
+      </c>
+      <c r="D368" t="s">
+        <v>415</v>
+      </c>
+      <c r="E368" t="s">
+        <v>410</v>
+      </c>
+      <c r="F368" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G368" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H368">
+        <v>1</v>
+      </c>
+      <c r="I368">
+        <v>2026</v>
+      </c>
+      <c r="J368" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K368" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L368" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M368" t="s">
+        <v>410</v>
+      </c>
+      <c r="N368" t="s">
+        <v>32</v>
+      </c>
+      <c r="O368" t="s">
+        <v>415</v>
+      </c>
+      <c r="P368" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q368">
+        <v>50</v>
+      </c>
+      <c r="R368" t="s">
+        <v>106</v>
+      </c>
+      <c r="S368" t="s">
+        <v>1301</v>
+      </c>
+      <c r="T368" t="s">
+        <v>349</v>
+      </c>
+      <c r="U368" t="s">
+        <v>1302</v>
+      </c>
+      <c r="V368" t="s">
+        <v>482</v>
+      </c>
+      <c r="Y368" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z368" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="369" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A369" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B369" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C369">
+        <v>81384668727</v>
+      </c>
+      <c r="D369" t="s">
+        <v>415</v>
+      </c>
+      <c r="E369" t="s">
+        <v>410</v>
+      </c>
+      <c r="F369" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G369" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H369">
+        <v>1</v>
+      </c>
+      <c r="I369">
+        <v>2026</v>
+      </c>
+      <c r="J369" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K369" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L369" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M369" t="s">
+        <v>410</v>
+      </c>
+      <c r="N369" t="s">
+        <v>32</v>
+      </c>
+      <c r="O369" t="s">
+        <v>415</v>
+      </c>
+      <c r="P369" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q369">
+        <v>50</v>
+      </c>
+      <c r="R369" t="s">
+        <v>106</v>
+      </c>
+      <c r="S369" t="s">
+        <v>1301</v>
+      </c>
+      <c r="T369" t="s">
+        <v>349</v>
+      </c>
+      <c r="U369" t="s">
+        <v>1302</v>
+      </c>
+      <c r="V369" t="s">
+        <v>482</v>
+      </c>
+      <c r="Y369" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z369" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="370" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A370" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B370" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C370">
+        <v>89522840942</v>
+      </c>
+      <c r="D370" t="s">
+        <v>251</v>
+      </c>
+      <c r="E370" t="s">
+        <v>410</v>
+      </c>
+      <c r="F370" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G370" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H370">
+        <v>1</v>
+      </c>
+      <c r="I370">
+        <v>2026</v>
+      </c>
+      <c r="J370" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K370" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L370" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M370" t="s">
+        <v>410</v>
+      </c>
+      <c r="N370" t="s">
+        <v>32</v>
+      </c>
+      <c r="O370" t="s">
+        <v>251</v>
+      </c>
+      <c r="P370" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q370">
+        <v>20</v>
+      </c>
+      <c r="R370" t="s">
+        <v>715</v>
+      </c>
+      <c r="S370" t="s">
+        <v>1305</v>
+      </c>
+      <c r="T370" t="s">
+        <v>349</v>
+      </c>
+      <c r="U370" t="s">
+        <v>1306</v>
+      </c>
+      <c r="V370" t="s">
+        <v>372</v>
+      </c>
+      <c r="Y370" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z370" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="371" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A371" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B371" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C371">
+        <v>89522840942</v>
+      </c>
+      <c r="D371" t="s">
+        <v>251</v>
+      </c>
+      <c r="E371" t="s">
+        <v>410</v>
+      </c>
+      <c r="F371" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G371" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H371">
+        <v>1</v>
+      </c>
+      <c r="I371">
+        <v>2026</v>
+      </c>
+      <c r="J371" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K371" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L371" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M371" t="s">
+        <v>410</v>
+      </c>
+      <c r="N371" t="s">
+        <v>32</v>
+      </c>
+      <c r="O371" t="s">
+        <v>251</v>
+      </c>
+      <c r="P371" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q371">
+        <v>20</v>
+      </c>
+      <c r="R371" t="s">
+        <v>715</v>
+      </c>
+      <c r="S371" t="s">
+        <v>1305</v>
+      </c>
+      <c r="T371" t="s">
+        <v>349</v>
+      </c>
+      <c r="U371" t="s">
+        <v>1306</v>
+      </c>
+      <c r="V371" t="s">
+        <v>372</v>
+      </c>
+      <c r="Y371" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z371" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="372" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A372" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B372" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C372">
+        <v>8561778098</v>
+      </c>
+      <c r="D372" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E372" t="s">
+        <v>410</v>
+      </c>
+      <c r="F372" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G372" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H372">
+        <v>1</v>
+      </c>
+      <c r="I372">
+        <v>2026</v>
+      </c>
+      <c r="J372" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K372" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L372" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M372" t="s">
+        <v>410</v>
+      </c>
+      <c r="N372" t="s">
+        <v>32</v>
+      </c>
+      <c r="O372" t="s">
+        <v>415</v>
+      </c>
+      <c r="P372" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q372">
+        <v>52</v>
+      </c>
+      <c r="R372" t="s">
+        <v>106</v>
+      </c>
+      <c r="S372" t="s">
+        <v>1310</v>
+      </c>
+      <c r="T372" t="s">
+        <v>349</v>
+      </c>
+      <c r="U372" t="s">
+        <v>1311</v>
+      </c>
+      <c r="V372" t="s">
+        <v>957</v>
+      </c>
+      <c r="Y372" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z372" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="373" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B373" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C373">
+        <v>8561778098</v>
+      </c>
+      <c r="D373" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E373" t="s">
+        <v>410</v>
+      </c>
+      <c r="F373" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G373" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H373">
+        <v>1</v>
+      </c>
+      <c r="I373">
+        <v>2026</v>
+      </c>
+      <c r="J373" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K373" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L373" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M373" t="s">
+        <v>410</v>
+      </c>
+      <c r="N373" t="s">
+        <v>32</v>
+      </c>
+      <c r="O373" t="s">
+        <v>415</v>
+      </c>
+      <c r="P373" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q373">
+        <v>52</v>
+      </c>
+      <c r="R373" t="s">
+        <v>106</v>
+      </c>
+      <c r="S373" t="s">
+        <v>1310</v>
+      </c>
+      <c r="T373" t="s">
+        <v>349</v>
+      </c>
+      <c r="U373" t="s">
+        <v>1311</v>
+      </c>
+      <c r="V373" t="s">
+        <v>957</v>
+      </c>
+      <c r="Y373" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z373" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="374" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B374" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C374">
+        <v>81280304626</v>
+      </c>
+      <c r="D374" t="s">
+        <v>499</v>
+      </c>
+      <c r="E374" t="s">
+        <v>410</v>
+      </c>
+      <c r="F374" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G374" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H374">
+        <v>1</v>
+      </c>
+      <c r="I374">
+        <v>2026</v>
+      </c>
+      <c r="J374" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K374" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L374" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M374" t="s">
+        <v>410</v>
+      </c>
+      <c r="N374" t="s">
+        <v>32</v>
+      </c>
+      <c r="O374" t="s">
+        <v>499</v>
+      </c>
+      <c r="P374" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q374">
+        <v>46</v>
+      </c>
+      <c r="R374" t="s">
+        <v>106</v>
+      </c>
+      <c r="S374" t="s">
+        <v>330</v>
+      </c>
+      <c r="T374" t="s">
+        <v>330</v>
+      </c>
+      <c r="U374" t="s">
+        <v>1314</v>
+      </c>
+      <c r="V374" t="s">
+        <v>359</v>
+      </c>
+      <c r="Y374" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z374" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="375" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B375" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C375">
+        <v>81280304626</v>
+      </c>
+      <c r="D375" t="s">
+        <v>499</v>
+      </c>
+      <c r="E375" t="s">
+        <v>410</v>
+      </c>
+      <c r="F375" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G375" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H375">
+        <v>1</v>
+      </c>
+      <c r="I375">
+        <v>2026</v>
+      </c>
+      <c r="J375" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K375" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L375" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M375" t="s">
+        <v>410</v>
+      </c>
+      <c r="N375" t="s">
+        <v>32</v>
+      </c>
+      <c r="O375" t="s">
+        <v>499</v>
+      </c>
+      <c r="P375" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q375">
+        <v>46</v>
+      </c>
+      <c r="R375" t="s">
+        <v>106</v>
+      </c>
+      <c r="S375" t="s">
+        <v>330</v>
+      </c>
+      <c r="T375" t="s">
+        <v>330</v>
+      </c>
+      <c r="U375" t="s">
+        <v>1314</v>
+      </c>
+      <c r="V375" t="s">
+        <v>359</v>
+      </c>
+      <c r="Y375" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z375" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="376" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B376" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C376">
+        <v>8117408398</v>
+      </c>
+      <c r="D376" t="s">
+        <v>415</v>
+      </c>
+      <c r="E376" t="s">
+        <v>410</v>
+      </c>
+      <c r="F376" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G376" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H376">
+        <v>1</v>
+      </c>
+      <c r="I376">
+        <v>2026</v>
+      </c>
+      <c r="J376" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K376" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L376" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M376" t="s">
+        <v>410</v>
+      </c>
+      <c r="N376" t="s">
+        <v>32</v>
+      </c>
+      <c r="O376" t="s">
+        <v>415</v>
+      </c>
+      <c r="P376" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q376">
+        <v>42</v>
+      </c>
+      <c r="R376" t="s">
+        <v>357</v>
+      </c>
+      <c r="S376" t="s">
+        <v>1317</v>
+      </c>
+      <c r="T376" t="s">
+        <v>349</v>
+      </c>
+      <c r="U376" t="s">
+        <v>1318</v>
+      </c>
+      <c r="V376" t="s">
+        <v>1215</v>
+      </c>
+      <c r="Y376" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z376" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="377" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B377" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C377">
+        <v>8114991122</v>
+      </c>
+      <c r="D377" t="s">
+        <v>428</v>
+      </c>
+      <c r="E377" t="s">
+        <v>410</v>
+      </c>
+      <c r="F377" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G377" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H377">
+        <v>1</v>
+      </c>
+      <c r="I377">
+        <v>2026</v>
+      </c>
+      <c r="J377" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K377" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L377" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M377" t="s">
+        <v>410</v>
+      </c>
+      <c r="N377" t="s">
+        <v>32</v>
+      </c>
+      <c r="O377" t="s">
+        <v>428</v>
+      </c>
+      <c r="P377" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q377">
+        <v>29</v>
+      </c>
+      <c r="R377" t="s">
+        <v>555</v>
+      </c>
+      <c r="S377" t="s">
+        <v>709</v>
+      </c>
+      <c r="T377" t="s">
+        <v>349</v>
+      </c>
+      <c r="U377" t="s">
+        <v>1321</v>
+      </c>
+      <c r="V377" t="s">
+        <v>359</v>
+      </c>
+      <c r="Y377" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z377" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="378" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B378" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C378">
+        <v>82123431967</v>
+      </c>
+      <c r="D378" t="s">
+        <v>499</v>
+      </c>
+      <c r="E378" t="s">
+        <v>410</v>
+      </c>
+      <c r="F378" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G378" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H378">
+        <v>1</v>
+      </c>
+      <c r="I378">
+        <v>2026</v>
+      </c>
+      <c r="J378" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K378" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L378" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M378" t="s">
+        <v>410</v>
+      </c>
+      <c r="N378" t="s">
+        <v>44</v>
+      </c>
+      <c r="O378" t="s">
+        <v>499</v>
+      </c>
+      <c r="P378" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q378">
+        <v>43</v>
+      </c>
+      <c r="R378" t="s">
+        <v>357</v>
+      </c>
+      <c r="S378" t="s">
+        <v>1324</v>
+      </c>
+      <c r="T378" t="s">
+        <v>349</v>
+      </c>
+      <c r="U378" t="s">
+        <v>1325</v>
+      </c>
+      <c r="V378" t="s">
+        <v>616</v>
+      </c>
+      <c r="Y378" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z378" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="379" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B379" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C379">
+        <v>82123431967</v>
+      </c>
+      <c r="D379" t="s">
+        <v>499</v>
+      </c>
+      <c r="E379" t="s">
+        <v>410</v>
+      </c>
+      <c r="F379" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G379" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H379">
+        <v>1</v>
+      </c>
+      <c r="I379">
+        <v>2026</v>
+      </c>
+      <c r="J379" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K379" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L379" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M379" t="s">
+        <v>410</v>
+      </c>
+      <c r="N379" t="s">
+        <v>44</v>
+      </c>
+      <c r="O379" t="s">
+        <v>499</v>
+      </c>
+      <c r="P379" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q379">
+        <v>43</v>
+      </c>
+      <c r="R379" t="s">
+        <v>357</v>
+      </c>
+      <c r="S379" t="s">
+        <v>1324</v>
+      </c>
+      <c r="T379" t="s">
+        <v>349</v>
+      </c>
+      <c r="U379" t="s">
+        <v>1325</v>
+      </c>
+      <c r="V379" t="s">
+        <v>616</v>
+      </c>
+      <c r="Y379" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z379" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="380" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B380" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C380">
+        <v>82119235230</v>
+      </c>
+      <c r="D380" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E380" t="s">
+        <v>410</v>
+      </c>
+      <c r="F380" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G380" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H380">
+        <v>1</v>
+      </c>
+      <c r="I380">
+        <v>2026</v>
+      </c>
+      <c r="J380" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K380" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L380" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M380" t="s">
+        <v>410</v>
+      </c>
+      <c r="N380" t="s">
+        <v>32</v>
+      </c>
+      <c r="O380" t="s">
+        <v>257</v>
+      </c>
+      <c r="P380" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q380">
+        <v>28</v>
+      </c>
+      <c r="R380" t="s">
+        <v>555</v>
+      </c>
+      <c r="S380" t="s">
+        <v>1329</v>
+      </c>
+      <c r="T380" t="s">
+        <v>349</v>
+      </c>
+      <c r="U380" t="s">
+        <v>1330</v>
+      </c>
+      <c r="V380" t="s">
+        <v>1267</v>
+      </c>
+      <c r="Y380" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z380" t="s">
+        <v>1216</v>
       </c>
     </row>
   </sheetData>
